--- a/research/traditional_assets/database/data/kazakhstan/kazakhstan_oilfield_svcs_equip.xlsx
+++ b/research/traditional_assets/database/data/kazakhstan/kazakhstan_oilfield_svcs_equip.xlsx
@@ -647,10 +647,10 @@
         <v>0.07921282257565444</v>
       </c>
       <c r="X2">
-        <v>0.1173395702861399</v>
+        <v>0.1173202144419773</v>
       </c>
       <c r="Y2">
-        <v>-0.03812674771048551</v>
+        <v>-0.03810739186632291</v>
       </c>
       <c r="Z2">
         <v>0.6106344758707745</v>
@@ -659,10 +659,10 @@
         <v>0.0456665504875281</v>
       </c>
       <c r="AB2">
-        <v>0.09928980312041319</v>
+        <v>0.09927672695291574</v>
       </c>
       <c r="AC2">
-        <v>-0.05362325263288509</v>
+        <v>-0.05361017646538764</v>
       </c>
       <c r="AD2">
         <v>8165.3</v>
@@ -781,10 +781,10 @@
         <v>0.07921282257565444</v>
       </c>
       <c r="X3">
-        <v>0.1173395702861399</v>
+        <v>0.1173202144419773</v>
       </c>
       <c r="Y3">
-        <v>-0.03812674771048551</v>
+        <v>-0.03810739186632291</v>
       </c>
       <c r="Z3">
         <v>0.6106344758707745</v>
@@ -793,10 +793,10 @@
         <v>0.0456665504875281</v>
       </c>
       <c r="AB3">
-        <v>0.09928980312041319</v>
+        <v>0.09927672695291574</v>
       </c>
       <c r="AC3">
-        <v>-0.05362325263288509</v>
+        <v>-0.05361017646538764</v>
       </c>
       <c r="AD3">
         <v>8165.3</v>
@@ -1133,7 +1133,7 @@
         <v>3.01094829038235</v>
       </c>
       <c r="F2">
-        <v>9.08903443745683</v>
+        <v>9.28145028615817</v>
       </c>
       <c r="G2">
         <v>2.51945447252306</v>
@@ -1151,13 +1151,13 @@
         <v>17002.6</v>
       </c>
       <c r="L2">
-        <v>22780.2201229997</v>
+        <v>22822.911100783</v>
       </c>
       <c r="M2">
         <v>22538.9</v>
       </c>
       <c r="N2">
-        <v>23171.3681229997</v>
+        <v>23214.059100783</v>
       </c>
       <c r="O2">
         <v>8165.3</v>
@@ -1166,16 +1166,16 @@
         <v>3020.148</v>
       </c>
       <c r="Q2">
-        <v>0.0992898031204132</v>
+        <v>0.0992767269529158</v>
       </c>
       <c r="R2">
-        <v>0.0972298954661462</v>
+        <v>0.09708184756015931</v>
       </c>
       <c r="S2">
         <v>0.0617047822134061</v>
       </c>
       <c r="T2">
-        <v>0.0540247822134061</v>
+        <v>0.0529047822134061</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.11733957028614</v>
+        <v>0.117320214441977</v>
       </c>
       <c r="X2">
-        <v>0.103121501818793</v>
+        <v>0.103105992834717</v>
       </c>
       <c r="Y2">
         <v>1.10639497126353</v>
@@ -1230,7 +1230,7 @@
         <v>17002.6</v>
       </c>
       <c r="AK2">
-        <v>0.0646600645739018</v>
+        <v>0.06464257005823122</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1418,13 +1418,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.09748332131202606</v>
+        <v>0.09746933780179359</v>
       </c>
       <c r="C2">
-        <v>25720.64872316126</v>
+        <v>25720.9399046332</v>
       </c>
       <c r="D2">
-        <v>23091.64872316126</v>
+        <v>23091.9399046332</v>
       </c>
       <c r="E2">
         <v>-8165.300000000001</v>
@@ -1469,19 +1469,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.09748332131202606</v>
+        <v>0.09746933780179359</v>
       </c>
       <c r="T2">
         <v>0.7993082229751833</v>
       </c>
       <c r="U2">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V2">
         <v>0.2</v>
       </c>
       <c r="W2">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1500,13 +1500,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.09746220249153607</v>
+        <v>0.09743704694832407</v>
       </c>
       <c r="C3">
-        <v>25475.59204938583</v>
+        <v>25479.38840929598</v>
       </c>
       <c r="D3">
-        <v>23098.27104938583</v>
+        <v>23102.06740929598</v>
       </c>
       <c r="E3">
         <v>-7913.621000000001</v>
@@ -1533,37 +1533,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M3">
-        <v>16.99612895335978</v>
+        <v>16.64377835335978</v>
       </c>
       <c r="N3">
-        <v>1836.744687373171</v>
+        <v>1837.097037973171</v>
       </c>
       <c r="O3">
-        <v>367.3489374746342</v>
+        <v>367.4194075946342</v>
       </c>
       <c r="P3">
-        <v>1469.395749898537</v>
+        <v>1469.677630378537</v>
       </c>
       <c r="Q3">
-        <v>2922.695749898537</v>
+        <v>2922.977630378537</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.09790096431252729</v>
+        <v>0.09788686780423234</v>
       </c>
       <c r="T3">
         <v>0.8057672793224576</v>
       </c>
       <c r="U3">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V3">
         <v>0.2</v>
       </c>
       <c r="W3">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>109.068413249482</v>
+        <v>111.377403433898</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1582,13 +1582,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.09744108367104608</v>
+        <v>0.09740475609485454</v>
       </c>
       <c r="C4">
-        <v>25230.53917506066</v>
+        <v>25237.84580115955</v>
       </c>
       <c r="D4">
-        <v>23104.89717506066</v>
+        <v>23112.20380115955</v>
       </c>
       <c r="E4">
         <v>-7661.942000000001</v>
@@ -1615,37 +1615,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M4">
-        <v>33.99225790671957</v>
+        <v>33.28755670671956</v>
       </c>
       <c r="N4">
-        <v>1819.748558419811</v>
+        <v>1820.453259619811</v>
       </c>
       <c r="O4">
-        <v>363.9497116839623</v>
+        <v>364.0906519239622</v>
       </c>
       <c r="P4">
-        <v>1455.798846735849</v>
+        <v>1456.362607695849</v>
       </c>
       <c r="Q4">
-        <v>2909.098846735849</v>
+        <v>2909.662607695849</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.09832713063956934</v>
+        <v>0.098312918827129</v>
       </c>
       <c r="T4">
         <v>0.8123581531462067</v>
       </c>
       <c r="U4">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V4">
         <v>0.2</v>
       </c>
       <c r="W4">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>54.534206624741</v>
+        <v>55.68870171694899</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1664,13 +1664,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.09741996485055608</v>
+        <v>0.09737246524138501</v>
       </c>
       <c r="C5">
-        <v>24985.49010345648</v>
+        <v>24996.31209192724</v>
       </c>
       <c r="D5">
-        <v>23111.52710345648</v>
+        <v>23122.34909192724</v>
       </c>
       <c r="E5">
         <v>-7410.263000000001</v>
@@ -1697,37 +1697,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M5">
-        <v>50.98838686007934</v>
+        <v>49.93133506007935</v>
       </c>
       <c r="N5">
-        <v>1802.752429466451</v>
+        <v>1803.809481266451</v>
       </c>
       <c r="O5">
-        <v>360.5504858932903</v>
+        <v>360.7618962532903</v>
       </c>
       <c r="P5">
-        <v>1442.201943573161</v>
+        <v>1443.047585013161</v>
       </c>
       <c r="Q5">
-        <v>2895.501943573161</v>
+        <v>2896.347585013161</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.09876208390118958</v>
+        <v>0.0987477544071988</v>
       </c>
       <c r="T5">
         <v>0.8190849212756002</v>
       </c>
       <c r="U5">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V5">
         <v>0.2</v>
       </c>
       <c r="W5">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>36.35613774982733</v>
+        <v>37.12580114463266</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1746,13 +1746,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.09739884603006609</v>
+        <v>0.09734017438791548</v>
       </c>
       <c r="C6">
-        <v>24740.44483784779</v>
+        <v>24754.78729332293</v>
       </c>
       <c r="D6">
-        <v>23118.16083784779</v>
+        <v>23132.50329332293</v>
       </c>
       <c r="E6">
         <v>-7158.584000000001</v>
@@ -1779,37 +1779,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M6">
-        <v>67.98451581343913</v>
+        <v>66.57511341343913</v>
       </c>
       <c r="N6">
-        <v>1785.756300513091</v>
+        <v>1787.165702913092</v>
       </c>
       <c r="O6">
-        <v>357.1512601026183</v>
+        <v>357.4331405826183</v>
       </c>
       <c r="P6">
-        <v>1428.605040410473</v>
+        <v>1429.732562330473</v>
       </c>
       <c r="Q6">
-        <v>2881.905040410473</v>
+        <v>2883.032562330473</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.09920609868909359</v>
+        <v>0.09919164906185338</v>
       </c>
       <c r="T6">
         <v>0.8259518304076895</v>
       </c>
       <c r="U6">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V6">
         <v>0.2</v>
       </c>
       <c r="W6">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>27.2671033123705</v>
+        <v>27.8443508584745</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1828,13 +1828,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.09737772720957608</v>
+        <v>0.09730788353444596</v>
       </c>
       <c r="C7">
-        <v>24495.40338151286</v>
+        <v>24513.27141709112</v>
       </c>
       <c r="D7">
-        <v>23124.79838151286</v>
+        <v>23142.66641709112</v>
       </c>
       <c r="E7">
         <v>-6906.905000000001</v>
@@ -1861,37 +1861,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M7">
-        <v>84.98064476679892</v>
+        <v>83.21889176679892</v>
       </c>
       <c r="N7">
-        <v>1768.760171559732</v>
+        <v>1770.521924559732</v>
       </c>
       <c r="O7">
-        <v>353.7520343119464</v>
+        <v>354.1043849119464</v>
       </c>
       <c r="P7">
-        <v>1415.008137247785</v>
+        <v>1416.417539647785</v>
       </c>
       <c r="Q7">
-        <v>2868.308137247785</v>
+        <v>2869.717539647785</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.09965946115674293</v>
+        <v>0.09964488886713227</v>
       </c>
       <c r="T7">
         <v>0.8329633060478225</v>
       </c>
       <c r="U7">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V7">
         <v>0.2</v>
       </c>
       <c r="W7">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>21.8136826498964</v>
+        <v>22.27548068677959</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1910,13 +1910,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.09735660838908611</v>
+        <v>0.09727559268097644</v>
       </c>
       <c r="C8">
-        <v>24250.36573773371</v>
+        <v>24271.76447499694</v>
       </c>
       <c r="D8">
-        <v>23131.43973773371</v>
+        <v>23152.83847499694</v>
       </c>
       <c r="E8">
         <v>-6655.226000000001</v>
@@ -1943,37 +1943,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M8">
-        <v>101.9767737201587</v>
+        <v>99.8626701201587</v>
       </c>
       <c r="N8">
-        <v>1751.764042606372</v>
+        <v>1753.878146206372</v>
       </c>
       <c r="O8">
-        <v>350.3528085212744</v>
+        <v>350.7756292412744</v>
       </c>
       <c r="P8">
-        <v>1401.411234085097</v>
+        <v>1403.102516965097</v>
       </c>
       <c r="Q8">
-        <v>2854.711234085097</v>
+        <v>2856.402516965098</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.1001224696343423</v>
+        <v>0.1001077720725235</v>
       </c>
       <c r="T8">
         <v>0.8401239620207247</v>
       </c>
       <c r="U8">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V8">
         <v>0.2</v>
       </c>
       <c r="W8">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>18.17806887491367</v>
+        <v>18.56290057231633</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1992,13 +1992,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.09733548956859611</v>
+        <v>0.0972433018275069</v>
       </c>
       <c r="C9">
-        <v>24005.33190979615</v>
+        <v>24030.26647882622</v>
       </c>
       <c r="D9">
-        <v>23138.08490979615</v>
+        <v>23163.01947882622</v>
       </c>
       <c r="E9">
         <v>-6403.547</v>
@@ -2025,37 +2025,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M9">
-        <v>118.9729026735185</v>
+        <v>116.5064484735185</v>
       </c>
       <c r="N9">
-        <v>1734.767913653012</v>
+        <v>1737.234367853012</v>
       </c>
       <c r="O9">
-        <v>346.9535827306024</v>
+        <v>347.4468735706025</v>
       </c>
       <c r="P9">
-        <v>1387.81433092241</v>
+        <v>1389.78749428241</v>
       </c>
       <c r="Q9">
-        <v>2841.11433092241</v>
+        <v>2843.087494282409</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.1005954352835029</v>
+        <v>0.10058060975545</v>
       </c>
       <c r="T9">
         <v>0.8474386105951944</v>
       </c>
       <c r="U9">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V9">
         <v>0.2</v>
       </c>
       <c r="W9">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>15.58120189278314</v>
+        <v>15.911057633414</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2074,13 +2074,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.09731437074810613</v>
+        <v>0.09721101097403738</v>
       </c>
       <c r="C10">
-        <v>23760.30190098974</v>
+        <v>23788.77744038554</v>
       </c>
       <c r="D10">
-        <v>23144.73390098974</v>
+        <v>23173.20944038554</v>
       </c>
       <c r="E10">
         <v>-6151.868</v>
@@ -2107,37 +2107,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M10">
-        <v>135.9690316268783</v>
+        <v>133.1502268268783</v>
       </c>
       <c r="N10">
-        <v>1717.771784699652</v>
+        <v>1720.590589499652</v>
       </c>
       <c r="O10">
-        <v>343.5543569399305</v>
+        <v>344.1181178999305</v>
       </c>
       <c r="P10">
-        <v>1374.217427759722</v>
+        <v>1376.472471599722</v>
       </c>
       <c r="Q10">
-        <v>2827.517427759722</v>
+        <v>2829.772471599722</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.1010786827946018</v>
+        <v>0.1010637265184401</v>
       </c>
       <c r="T10">
         <v>0.8549122732691091</v>
       </c>
       <c r="U10">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V10">
         <v>0.2</v>
       </c>
       <c r="W10">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>13.63355165618525</v>
+        <v>13.92217542923725</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2156,13 +2156,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.09729325192761615</v>
+        <v>0.09717872012056784</v>
       </c>
       <c r="C11">
-        <v>23515.27571460785</v>
+        <v>23547.29737150225</v>
       </c>
       <c r="D11">
-        <v>23151.38671460785</v>
+        <v>23183.40837150225</v>
       </c>
       <c r="E11">
         <v>-5900.189000000001</v>
@@ -2189,37 +2189,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M11">
-        <v>152.965160580238</v>
+        <v>149.794005180238</v>
       </c>
       <c r="N11">
-        <v>1700.775655746293</v>
+        <v>1703.946811146293</v>
       </c>
       <c r="O11">
-        <v>340.1551311492585</v>
+        <v>340.7893622292586</v>
       </c>
       <c r="P11">
-        <v>1360.620524597034</v>
+        <v>1363.157448917034</v>
       </c>
       <c r="Q11">
-        <v>2813.920524597034</v>
+        <v>2816.457448917034</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.1015725511301204</v>
+        <v>0.1015574612322652</v>
       </c>
       <c r="T11">
         <v>0.8625501922655274</v>
       </c>
       <c r="U11">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V11">
         <v>0.2</v>
       </c>
       <c r="W11">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>12.11871258327578</v>
+        <v>12.37526704821089</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2238,13 +2238,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.09727213310712615</v>
+        <v>0.09714642926709832</v>
       </c>
       <c r="C12">
-        <v>23270.25335394762</v>
+        <v>23305.82628402455</v>
       </c>
       <c r="D12">
-        <v>23158.04335394762</v>
+        <v>23193.61628402455</v>
       </c>
       <c r="E12">
         <v>-5648.51</v>
@@ -2271,37 +2271,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M12">
-        <v>169.9612895335978</v>
+        <v>166.4377835335978</v>
       </c>
       <c r="N12">
-        <v>1683.779526792933</v>
+        <v>1687.303032792933</v>
       </c>
       <c r="O12">
-        <v>336.7559053585866</v>
+        <v>337.4606065585866</v>
       </c>
       <c r="P12">
-        <v>1347.023621434346</v>
+        <v>1349.842426234346</v>
       </c>
       <c r="Q12">
-        <v>2800.323621434346</v>
+        <v>2803.142426234346</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.1020773943175395</v>
+        <v>0.1020621678286197</v>
       </c>
       <c r="T12">
         <v>0.8703578427951998</v>
       </c>
       <c r="U12">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V12">
         <v>0.2</v>
       </c>
       <c r="W12">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>10.9068413249482</v>
+        <v>11.1377403433898</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2320,13 +2320,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.09725101428663614</v>
+        <v>0.09711413841362881</v>
       </c>
       <c r="C13">
-        <v>23025.23482231001</v>
+        <v>23064.36418982148</v>
       </c>
       <c r="D13">
-        <v>23164.70382231001</v>
+        <v>23203.83318982148</v>
       </c>
       <c r="E13">
         <v>-5396.831000000001</v>
@@ -2353,37 +2353,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M13">
-        <v>186.9574184869576</v>
+        <v>183.0815618869576</v>
       </c>
       <c r="N13">
-        <v>1666.783397839573</v>
+        <v>1670.659254439573</v>
       </c>
       <c r="O13">
-        <v>333.3566795679146</v>
+        <v>334.1318508879147</v>
       </c>
       <c r="P13">
-        <v>1333.426718271659</v>
+        <v>1336.527403551658</v>
       </c>
       <c r="Q13">
-        <v>2786.726718271659</v>
+        <v>2789.827403551658</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.102593582295687</v>
+        <v>0.1025782161462406</v>
       </c>
       <c r="T13">
         <v>0.8783409461457632</v>
       </c>
       <c r="U13">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V13">
         <v>0.2</v>
       </c>
       <c r="W13">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>9.915310295407455</v>
+        <v>10.12521849399073</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2402,13 +2402,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.09722989546614616</v>
+        <v>0.09708184756015928</v>
       </c>
       <c r="C14">
-        <v>22780.22012299972</v>
+        <v>22822.91110078305</v>
       </c>
       <c r="D14">
-        <v>23171.36812299972</v>
+        <v>23214.05910078305</v>
       </c>
       <c r="E14">
         <v>-5145.152000000001</v>
@@ -2435,37 +2435,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M14">
-        <v>203.9535474403174</v>
+        <v>199.7253402403174</v>
       </c>
       <c r="N14">
-        <v>1649.787268886213</v>
+        <v>1654.015476086213</v>
       </c>
       <c r="O14">
-        <v>329.9574537772427</v>
+        <v>330.8030952172427</v>
       </c>
       <c r="P14">
-        <v>1319.829815108971</v>
+        <v>1323.212380868971</v>
       </c>
       <c r="Q14">
-        <v>2773.12981510897</v>
+        <v>2776.51238086897</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.1031215018187925</v>
+        <v>0.1031059928347165</v>
       </c>
       <c r="T14">
         <v>0.8865054836633852</v>
       </c>
       <c r="U14">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V14">
         <v>0.2</v>
       </c>
       <c r="W14">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>9.089034437456833</v>
+        <v>9.281450286158165</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2484,13 +2484,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.09732317664565616</v>
+        <v>0.09720555670668973</v>
       </c>
       <c r="C15">
-        <v>22499.13401205554</v>
+        <v>22532.10451803639</v>
       </c>
       <c r="D15">
-        <v>23141.96101205554</v>
+        <v>23174.9315180364</v>
       </c>
       <c r="E15">
         <v>-4893.473000000001</v>
@@ -2517,37 +2517,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M15">
-        <v>224.5486860936772</v>
+        <v>221.2768590936772</v>
       </c>
       <c r="N15">
-        <v>1629.192130232854</v>
+        <v>1632.463957232854</v>
       </c>
       <c r="O15">
-        <v>325.8384260465707</v>
+        <v>326.4927914465707</v>
       </c>
       <c r="P15">
-        <v>1303.353704186283</v>
+        <v>1305.971165786283</v>
       </c>
       <c r="Q15">
-        <v>2756.653704186283</v>
+        <v>2759.271165786283</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.1036615574228889</v>
+        <v>0.1036459023206287</v>
       </c>
       <c r="T15">
         <v>0.8948577116986535</v>
       </c>
       <c r="U15">
-        <v>0.06863097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V15">
         <v>0.2</v>
       </c>
       <c r="W15">
-        <v>0.05490478221340607</v>
+        <v>0.05410478221340607</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>8.255407094892497</v>
+        <v>8.377472564999454</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2566,13 +2566,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.09731085782516619</v>
+        <v>0.09718526585322024</v>
       </c>
       <c r="C16">
-        <v>22251.33427066463</v>
+        <v>22286.83420379862</v>
       </c>
       <c r="D16">
-        <v>23145.84027066463</v>
+        <v>23181.34020379862</v>
       </c>
       <c r="E16">
         <v>-4641.794000000001</v>
@@ -2599,37 +2599,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M16">
-        <v>241.821661947037</v>
+        <v>238.298155947037</v>
       </c>
       <c r="N16">
-        <v>1611.919154379494</v>
+        <v>1615.442660379494</v>
       </c>
       <c r="O16">
-        <v>322.3838308758988</v>
+        <v>323.0885320758987</v>
       </c>
       <c r="P16">
-        <v>1289.535323503595</v>
+        <v>1292.354128303595</v>
       </c>
       <c r="Q16">
-        <v>2742.835323503595</v>
+        <v>2745.654128303595</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.1042141724596388</v>
+        <v>0.104198367841097</v>
       </c>
       <c r="T16">
         <v>0.9034041775952073</v>
       </c>
       <c r="U16">
-        <v>0.06863097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V16">
         <v>0.2</v>
       </c>
       <c r="W16">
-        <v>0.05490478221340607</v>
+        <v>0.05410478221340607</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>7.665735159543032</v>
+        <v>7.779081667499493</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2648,13 +2648,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.09729853900467618</v>
+        <v>0.0971649749997507</v>
       </c>
       <c r="C17">
-        <v>22003.53583004253</v>
+        <v>22041.5674349965</v>
       </c>
       <c r="D17">
-        <v>23149.72083004253</v>
+        <v>23187.7524349965</v>
       </c>
       <c r="E17">
         <v>-4390.115000000002</v>
@@ -2681,37 +2681,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M17">
-        <v>259.0946378003967</v>
+        <v>255.3194528003967</v>
       </c>
       <c r="N17">
-        <v>1594.646178526134</v>
+        <v>1598.421363526134</v>
       </c>
       <c r="O17">
-        <v>318.9292357052268</v>
+        <v>319.6842727052268</v>
       </c>
       <c r="P17">
-        <v>1275.716942820907</v>
+        <v>1278.737090820907</v>
       </c>
       <c r="Q17">
-        <v>2729.016942820907</v>
+        <v>2732.037090820907</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.1047797902031356</v>
+        <v>0.1047638325502821</v>
       </c>
       <c r="T17">
         <v>0.9121517368069739</v>
       </c>
       <c r="U17">
-        <v>0.06863097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V17">
         <v>0.2</v>
       </c>
       <c r="W17">
-        <v>0.05490478221340607</v>
+        <v>0.05410478221340607</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>7.154686148906832</v>
+        <v>7.260476222999528</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2730,13 +2730,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.09756782018418618</v>
+        <v>0.09714468414628116</v>
       </c>
       <c r="C18">
-        <v>21667.32596924919</v>
+        <v>21796.30421457295</v>
       </c>
       <c r="D18">
-        <v>23065.18996924919</v>
+        <v>23194.16821457295</v>
       </c>
       <c r="E18">
         <v>-4138.436000000001</v>
@@ -2763,45 +2763,45 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M18">
-        <v>285.2267144537565</v>
+        <v>272.3407496537565</v>
       </c>
       <c r="N18">
-        <v>1568.514101872774</v>
+        <v>1581.400066672774</v>
       </c>
       <c r="O18">
-        <v>313.7028203745548</v>
+        <v>316.2800133345548</v>
       </c>
       <c r="P18">
-        <v>1254.811281498219</v>
+        <v>1265.120053338219</v>
       </c>
       <c r="Q18">
-        <v>2708.111281498219</v>
+        <v>2718.420053338219</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.1053588750357634</v>
+        <v>0.105342760704924</v>
       </c>
       <c r="T18">
         <v>0.9211075712380683</v>
       </c>
       <c r="U18">
-        <v>0.07083097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V18">
         <v>0.2</v>
       </c>
       <c r="W18">
-        <v>0.05666478221340607</v>
+        <v>0.05410478221340607</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y18">
-        <v>6.499183710322041</v>
+        <v>6.806696459062057</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2812,13 +2812,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.09757310136369619</v>
+        <v>0.09735559329281164</v>
       </c>
       <c r="C19">
-        <v>21413.99531021271</v>
+        <v>21478.11054280756</v>
       </c>
       <c r="D19">
-        <v>23063.53831021271</v>
+        <v>23127.65354280756</v>
       </c>
       <c r="E19">
         <v>-3886.757000000001</v>
@@ -2845,37 +2845,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M19">
-        <v>303.0533841071163</v>
+        <v>296.6355696071163</v>
       </c>
       <c r="N19">
-        <v>1550.687432219414</v>
+        <v>1557.105246719414</v>
       </c>
       <c r="O19">
-        <v>310.1374864438829</v>
+        <v>311.4210493438829</v>
       </c>
       <c r="P19">
-        <v>1240.549945775532</v>
+        <v>1245.684197375532</v>
       </c>
       <c r="Q19">
-        <v>2693.849945775532</v>
+        <v>2698.984197375531</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.1059519137197797</v>
+        <v>0.1059356389355815</v>
       </c>
       <c r="T19">
         <v>0.9302792089084664</v>
       </c>
       <c r="U19">
-        <v>0.07083097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V19">
         <v>0.2</v>
       </c>
       <c r="W19">
-        <v>0.05666478221340607</v>
+        <v>0.05546478221340606</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>6.116878786185451</v>
+        <v>6.249219602294315</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2894,13 +2894,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.09757838254320622</v>
+        <v>0.09734890243934212</v>
       </c>
       <c r="C20">
-        <v>21160.66488770428</v>
+        <v>21228.53578555615</v>
       </c>
       <c r="D20">
-        <v>23061.88688770428</v>
+        <v>23129.75778555614</v>
       </c>
       <c r="E20">
         <v>-3635.078000000001</v>
@@ -2927,37 +2927,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M20">
-        <v>320.880053760476</v>
+        <v>314.084720760476</v>
       </c>
       <c r="N20">
-        <v>1532.860762566055</v>
+        <v>1539.656095566055</v>
       </c>
       <c r="O20">
-        <v>306.5721525132109</v>
+        <v>307.9312191132109</v>
       </c>
       <c r="P20">
-        <v>1226.288610052844</v>
+        <v>1231.724876452844</v>
       </c>
       <c r="Q20">
-        <v>2679.588610052844</v>
+        <v>2685.024876452843</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.1065594167619428</v>
+        <v>0.106542977610889</v>
       </c>
       <c r="T20">
         <v>0.9396745450586301</v>
       </c>
       <c r="U20">
-        <v>0.07083097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V20">
         <v>0.2</v>
       </c>
       <c r="W20">
-        <v>0.05666478221340607</v>
+        <v>0.05546478221340606</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.777052186952927</v>
+        <v>5.902040735500186</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2976,13 +2976,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.09781166372271623</v>
+        <v>0.0973422115858726</v>
       </c>
       <c r="C21">
-        <v>20836.27416633505</v>
+        <v>20978.96141124373</v>
       </c>
       <c r="D21">
-        <v>22989.17516633506</v>
+        <v>23131.86241124373</v>
       </c>
       <c r="E21">
         <v>-3383.399</v>
@@ -3009,45 +3009,45 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M21">
-        <v>345.8795749138359</v>
+        <v>331.5338719138359</v>
       </c>
       <c r="N21">
-        <v>1507.861241412695</v>
+        <v>1522.206944412695</v>
       </c>
       <c r="O21">
-        <v>301.572248282539</v>
+        <v>304.441388882539</v>
       </c>
       <c r="P21">
-        <v>1206.288993130156</v>
+        <v>1217.765555530156</v>
       </c>
       <c r="Q21">
-        <v>2659.588993130155</v>
+        <v>2671.065555530156</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.1071819198792211</v>
+        <v>0.1071653123028709</v>
       </c>
       <c r="T21">
         <v>0.9493018648174401</v>
       </c>
       <c r="U21">
-        <v>0.07233097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V21">
         <v>0.2</v>
       </c>
       <c r="W21">
-        <v>0.05786478221340607</v>
+        <v>0.05546478221340606</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>5.359497787021182</v>
+        <v>5.591407012579123</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3058,13 +3058,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.09782894490222624</v>
+        <v>0.09746352073240307</v>
       </c>
       <c r="C22">
-        <v>20579.22700902813</v>
+        <v>20689.18367872932</v>
       </c>
       <c r="D22">
-        <v>22983.80700902813</v>
+        <v>23093.76367872932</v>
       </c>
       <c r="E22">
         <v>-3131.72</v>
@@ -3091,37 +3091,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M22">
-        <v>364.0837630671957</v>
+        <v>353.0098870671957</v>
       </c>
       <c r="N22">
-        <v>1489.657053259335</v>
+        <v>1500.730929259335</v>
       </c>
       <c r="O22">
-        <v>297.931410651867</v>
+        <v>300.146185851867</v>
       </c>
       <c r="P22">
-        <v>1191.725642607468</v>
+        <v>1200.584743407468</v>
       </c>
       <c r="Q22">
-        <v>2645.025642607468</v>
+        <v>2653.884743407468</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.1078199855744313</v>
+        <v>0.1078032053621523</v>
       </c>
       <c r="T22">
         <v>0.9591698675702199</v>
       </c>
       <c r="U22">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V22">
         <v>0.2</v>
       </c>
       <c r="W22">
-        <v>0.05786478221340607</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.091522897670123</v>
+        <v>5.251243334081659</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3140,13 +3140,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.09784622608173624</v>
+        <v>0.09746322987893354</v>
       </c>
       <c r="C23">
-        <v>20322.18235815175</v>
+        <v>20437.59587499624</v>
       </c>
       <c r="D23">
-        <v>22978.44135815175</v>
+        <v>23093.85487499624</v>
       </c>
       <c r="E23">
         <v>-2880.041000000001</v>
@@ -3173,37 +3173,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M23">
-        <v>382.2879512205554</v>
+        <v>370.6603814205554</v>
       </c>
       <c r="N23">
-        <v>1471.452865105975</v>
+        <v>1483.080434905975</v>
       </c>
       <c r="O23">
-        <v>294.290573021195</v>
+        <v>296.6160869811951</v>
       </c>
       <c r="P23">
-        <v>1177.16229208478</v>
+        <v>1186.46434792478</v>
       </c>
       <c r="Q23">
-        <v>2630.46229208478</v>
+        <v>2639.76434792478</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.1084742048315455</v>
+        <v>0.1084572476128079</v>
       </c>
       <c r="T23">
         <v>0.9692876931775009</v>
       </c>
       <c r="U23">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V23">
         <v>0.2</v>
       </c>
       <c r="W23">
-        <v>0.05786478221340607</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>4.849069426352498</v>
+        <v>5.001184127696819</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3222,13 +3222,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.09786350726124626</v>
+        <v>0.097462939025464</v>
       </c>
       <c r="C24">
-        <v>20065.14021195091</v>
+        <v>20186.00807198341</v>
       </c>
       <c r="D24">
-        <v>22973.07821195091</v>
+        <v>23093.94607198341</v>
       </c>
       <c r="E24">
         <v>-2628.362000000001</v>
@@ -3255,37 +3255,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M24">
-        <v>400.4921393739152</v>
+        <v>388.3108757739152</v>
       </c>
       <c r="N24">
-        <v>1453.248676952615</v>
+        <v>1465.429940552615</v>
       </c>
       <c r="O24">
-        <v>290.6497353905231</v>
+        <v>293.0859881105231</v>
       </c>
       <c r="P24">
-        <v>1162.598941562092</v>
+        <v>1172.343952442092</v>
       </c>
       <c r="Q24">
-        <v>2615.898941562092</v>
+        <v>2625.643952442092</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.1091451989414063</v>
+        <v>0.1091280601775829</v>
       </c>
       <c r="T24">
         <v>0.9796649502106094</v>
       </c>
       <c r="U24">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V24">
         <v>0.2</v>
       </c>
       <c r="W24">
-        <v>0.05786478221340607</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.628657179700113</v>
+        <v>4.773857576437873</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3304,13 +3304,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.09788078844075626</v>
+        <v>0.09746264817199449</v>
       </c>
       <c r="C25">
-        <v>19808.10056867227</v>
+        <v>19934.42026969085</v>
       </c>
       <c r="D25">
-        <v>22967.71756867227</v>
+        <v>23094.03726969085</v>
       </c>
       <c r="E25">
         <v>-2376.683000000001</v>
@@ -3337,37 +3337,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M25">
-        <v>418.6963275272749</v>
+        <v>405.961370127275</v>
       </c>
       <c r="N25">
-        <v>1435.044488799256</v>
+        <v>1447.779446199256</v>
       </c>
       <c r="O25">
-        <v>287.0088977598512</v>
+        <v>289.5558892398512</v>
       </c>
       <c r="P25">
-        <v>1148.035591039405</v>
+        <v>1158.223556959405</v>
       </c>
       <c r="Q25">
-        <v>2601.335591039405</v>
+        <v>2611.523556959404</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.109833621469705</v>
+        <v>0.1098162964453391</v>
       </c>
       <c r="T25">
         <v>0.990311746387435</v>
       </c>
       <c r="U25">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V25">
         <v>0.2</v>
       </c>
       <c r="W25">
-        <v>0.05786478221340607</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.427411215365325</v>
+        <v>4.566298551375356</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3386,13 +3386,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.09816686962026627</v>
+        <v>0.09746235731852496</v>
       </c>
       <c r="C26">
-        <v>19468.04094587914</v>
+        <v>19682.83246811858</v>
       </c>
       <c r="D26">
-        <v>22879.33694587914</v>
+        <v>23094.12846811858</v>
       </c>
       <c r="E26">
         <v>-2125.004000000001</v>
@@ -3419,45 +3419,45 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M26">
-        <v>445.3569300806348</v>
+        <v>423.6118644806348</v>
       </c>
       <c r="N26">
-        <v>1408.383886245896</v>
+        <v>1430.128951845896</v>
       </c>
       <c r="O26">
-        <v>281.6767772491792</v>
+        <v>286.0257903691792</v>
       </c>
       <c r="P26">
-        <v>1126.707108996717</v>
+        <v>1144.103161476717</v>
       </c>
       <c r="Q26">
-        <v>2580.007108996717</v>
+        <v>2597.403161476716</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.1105401603803274</v>
+        <v>0.1105226441938257</v>
       </c>
       <c r="T26">
         <v>1.001238721411019</v>
       </c>
       <c r="U26">
-        <v>0.07373097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V26">
         <v>0.2</v>
       </c>
       <c r="W26">
-        <v>0.05898478221340606</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y26">
-        <v>4.162371103085561</v>
+        <v>4.376036111734717</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3468,13 +3468,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.09819535079977627</v>
+        <v>0.09766206646505543</v>
       </c>
       <c r="C27">
-        <v>19207.60031421986</v>
+        <v>19368.70284544978</v>
       </c>
       <c r="D27">
-        <v>22870.57531421986</v>
+        <v>23031.67784544978</v>
       </c>
       <c r="E27">
         <v>-1873.325000000001</v>
@@ -3501,37 +3501,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M27">
-        <v>463.9134688339946</v>
+        <v>447.5543338339946</v>
       </c>
       <c r="N27">
-        <v>1389.827347492536</v>
+        <v>1406.186482492536</v>
       </c>
       <c r="O27">
-        <v>277.9654694985072</v>
+        <v>281.2372964985072</v>
       </c>
       <c r="P27">
-        <v>1111.861877994029</v>
+        <v>1124.949185994029</v>
       </c>
       <c r="Q27">
-        <v>2565.161877994029</v>
+        <v>2578.249185994029</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.1112655403285663</v>
+        <v>0.1112478278822719</v>
       </c>
       <c r="T27">
         <v>1.012457082435232</v>
       </c>
       <c r="U27">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V27">
         <v>0.2</v>
       </c>
       <c r="W27">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>3.995876258962138</v>
+        <v>4.141934679631802</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3550,13 +3550,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.09822383197928627</v>
+        <v>0.09766977561158591</v>
       </c>
       <c r="C28">
-        <v>18947.16639051749</v>
+        <v>19114.61990455487</v>
       </c>
       <c r="D28">
-        <v>22861.82039051749</v>
+        <v>23029.27390455487</v>
       </c>
       <c r="E28">
         <v>-1621.646000000001</v>
@@ -3583,37 +3583,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M28">
-        <v>482.4700075873543</v>
+        <v>465.4565071873544</v>
       </c>
       <c r="N28">
-        <v>1371.270808739176</v>
+        <v>1388.284309139176</v>
       </c>
       <c r="O28">
-        <v>274.2541617478353</v>
+        <v>277.6568618278353</v>
       </c>
       <c r="P28">
-        <v>1097.016646991341</v>
+        <v>1110.627447311341</v>
       </c>
       <c r="Q28">
-        <v>2550.316646991341</v>
+        <v>2563.927447311341</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1120105251402712</v>
+        <v>0.1119926111298653</v>
       </c>
       <c r="T28">
         <v>1.023978642406046</v>
       </c>
       <c r="U28">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V28">
         <v>0.2</v>
       </c>
       <c r="W28">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.842188710540518</v>
+        <v>3.982629499645963</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3632,13 +3632,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.09825231315879629</v>
+        <v>0.09767748475811637</v>
       </c>
       <c r="C29">
-        <v>18686.73916707146</v>
+        <v>18860.53746543224</v>
       </c>
       <c r="D29">
-        <v>22853.07216707146</v>
+        <v>23026.87046543224</v>
       </c>
       <c r="E29">
         <v>-1369.967000000001</v>
@@ -3665,37 +3665,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M29">
-        <v>501.0265463407141</v>
+        <v>483.3586805407141</v>
       </c>
       <c r="N29">
-        <v>1352.714269985817</v>
+        <v>1370.382135785816</v>
       </c>
       <c r="O29">
-        <v>270.5428539971633</v>
+        <v>274.0764271571633</v>
       </c>
       <c r="P29">
-        <v>1082.171415988653</v>
+        <v>1096.305708628653</v>
       </c>
       <c r="Q29">
-        <v>2535.471415988653</v>
+        <v>2549.605708628653</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1127759204947625</v>
+        <v>0.1127577993979407</v>
       </c>
       <c r="T29">
         <v>1.035815861554142</v>
       </c>
       <c r="U29">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V29">
         <v>0.2</v>
       </c>
       <c r="W29">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.699885424964943</v>
+        <v>3.835124703362779</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3714,13 +3714,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.0982807943383063</v>
+        <v>0.09768519390464685</v>
       </c>
       <c r="C30">
-        <v>18426.31863619306</v>
+        <v>18606.4555279248</v>
       </c>
       <c r="D30">
-        <v>22844.33063619307</v>
+        <v>23024.4675279248</v>
       </c>
       <c r="E30">
         <v>-1118.288</v>
@@ -3747,37 +3747,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M30">
-        <v>519.5830850940739</v>
+        <v>501.2608538940739</v>
       </c>
       <c r="N30">
-        <v>1334.157731232457</v>
+        <v>1352.479962432457</v>
       </c>
       <c r="O30">
-        <v>266.8315462464913</v>
+        <v>270.4959924864913</v>
       </c>
       <c r="P30">
-        <v>1067.326184985965</v>
+        <v>1081.983969945965</v>
       </c>
       <c r="Q30">
-        <v>2520.626184985965</v>
+        <v>2535.283969945966</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1135625768313231</v>
+        <v>0.1135442428956849</v>
       </c>
       <c r="T30">
         <v>1.04798189234524</v>
       </c>
       <c r="U30">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V30">
         <v>0.2</v>
       </c>
       <c r="W30">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.567746659787623</v>
+        <v>3.698155963956965</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3796,13 +3796,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.09830927551781631</v>
+        <v>0.09769290305117732</v>
       </c>
       <c r="C31">
-        <v>18165.9047902053</v>
+        <v>18352.37409187553</v>
       </c>
       <c r="D31">
-        <v>22835.5957902053</v>
+        <v>23022.06509187553</v>
       </c>
       <c r="E31">
         <v>-866.6090000000013</v>
@@ -3829,37 +3829,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M31">
-        <v>538.1396238474337</v>
+        <v>519.1630272474337</v>
       </c>
       <c r="N31">
-        <v>1315.601192479097</v>
+        <v>1334.577789079097</v>
       </c>
       <c r="O31">
-        <v>263.1202384958194</v>
+        <v>266.9155578158194</v>
       </c>
       <c r="P31">
-        <v>1052.480953983277</v>
+        <v>1067.662231263278</v>
       </c>
       <c r="Q31">
-        <v>2505.780953983277</v>
+        <v>2520.962231263277</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1143713925013078</v>
+        <v>0.1143528397313938</v>
       </c>
       <c r="T31">
         <v>1.060490628229046</v>
       </c>
       <c r="U31">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V31">
         <v>0.2</v>
       </c>
       <c r="W31">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.444720912898395</v>
+        <v>3.570633344510174</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3878,13 +3878,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.09833775669732632</v>
+        <v>0.0977006121977078</v>
       </c>
       <c r="C32">
-        <v>17905.49762144291</v>
+        <v>18098.29315712748</v>
       </c>
       <c r="D32">
-        <v>22826.86762144291</v>
+        <v>23019.66315712748</v>
       </c>
       <c r="E32">
         <v>-614.9300000000012</v>
@@ -3911,37 +3911,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M32">
-        <v>556.6961626007934</v>
+        <v>537.0652006007934</v>
       </c>
       <c r="N32">
-        <v>1297.044653725737</v>
+        <v>1316.675615725737</v>
       </c>
       <c r="O32">
-        <v>259.4089307451474</v>
+        <v>263.3351231451475</v>
       </c>
       <c r="P32">
-        <v>1037.63572298059</v>
+        <v>1053.34049258059</v>
       </c>
       <c r="Q32">
-        <v>2490.93572298059</v>
+        <v>2506.64049258059</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.115203317190435</v>
+        <v>0.1151845393338371</v>
       </c>
       <c r="T32">
         <v>1.073356756566675</v>
       </c>
       <c r="U32">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V32">
         <v>0.2</v>
       </c>
       <c r="W32">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.329896882468449</v>
+        <v>3.451612233026502</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3960,13 +3960,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.09836623787683631</v>
+        <v>0.09770832134423826</v>
       </c>
       <c r="C33">
-        <v>17645.09712225237</v>
+        <v>17844.21272352376</v>
       </c>
       <c r="D33">
-        <v>22818.14612225237</v>
+        <v>23017.26172352376</v>
       </c>
       <c r="E33">
         <v>-363.2510000000011</v>
@@ -3993,37 +3993,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M33">
-        <v>575.2527013541531</v>
+        <v>554.9673739541532</v>
       </c>
       <c r="N33">
-        <v>1278.488114972377</v>
+        <v>1298.773442372377</v>
       </c>
       <c r="O33">
-        <v>255.6976229944755</v>
+        <v>259.7546884744755</v>
       </c>
       <c r="P33">
-        <v>1022.790491977902</v>
+        <v>1039.018753897902</v>
       </c>
       <c r="Q33">
-        <v>2476.090491977902</v>
+        <v>2492.318753897902</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1160593556386673</v>
+        <v>0.1160403461711339</v>
       </c>
       <c r="T33">
         <v>1.086595816160467</v>
       </c>
       <c r="U33">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V33">
         <v>0.2</v>
       </c>
       <c r="W33">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.222480854001725</v>
+        <v>3.340269902928872</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4042,13 +4042,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.09839471905634632</v>
+        <v>0.09771603049076874</v>
       </c>
       <c r="C34">
-        <v>17384.70328499183</v>
+        <v>17590.13279090754</v>
       </c>
       <c r="D34">
-        <v>22809.43128499183</v>
+        <v>23014.86079090754</v>
       </c>
       <c r="E34">
         <v>-111.5720000000001</v>
@@ -4075,37 +4075,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M34">
-        <v>593.809240107513</v>
+        <v>572.8695473075131</v>
       </c>
       <c r="N34">
-        <v>1259.931576219018</v>
+        <v>1280.871269019018</v>
       </c>
       <c r="O34">
-        <v>251.9863152438035</v>
+        <v>256.1742538038035</v>
       </c>
       <c r="P34">
-        <v>1007.945260975214</v>
+        <v>1024.697015215214</v>
       </c>
       <c r="Q34">
-        <v>2461.245260975214</v>
+        <v>2477.997015215214</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1169405716883182</v>
+        <v>0.116921323797763</v>
       </c>
       <c r="T34">
         <v>1.100224259859958</v>
       </c>
       <c r="U34">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V34">
         <v>0.2</v>
       </c>
       <c r="W34">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.12177832731417</v>
+        <v>3.235886468462344</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4124,13 +4124,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.09842320023585634</v>
+        <v>0.09772373963729922</v>
       </c>
       <c r="C35">
-        <v>17124.31610203112</v>
+        <v>17336.05335912207</v>
       </c>
       <c r="D35">
-        <v>22800.72310203112</v>
+        <v>23012.46035912207</v>
       </c>
       <c r="E35">
         <v>140.107</v>
@@ -4157,37 +4157,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M35">
-        <v>612.3657788608729</v>
+        <v>590.7717206608729</v>
       </c>
       <c r="N35">
-        <v>1241.375037465658</v>
+        <v>1262.969095665658</v>
       </c>
       <c r="O35">
-        <v>248.2750074931316</v>
+        <v>252.5938191331315</v>
       </c>
       <c r="P35">
-        <v>993.1000299725263</v>
+        <v>1010.375276532526</v>
       </c>
       <c r="Q35">
-        <v>2446.400029972526</v>
+        <v>2463.675276532526</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1178480926946751</v>
+        <v>0.1178285992639929</v>
       </c>
       <c r="T35">
         <v>1.11425952277436</v>
       </c>
       <c r="U35">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V35">
         <v>0.2</v>
       </c>
       <c r="W35">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.027178984062226</v>
+        <v>3.137829302751364</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4206,13 +4206,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.09915888141536634</v>
+        <v>0.09773144878382968</v>
       </c>
       <c r="C36">
-        <v>16649.98256434182</v>
+        <v>17081.97442801065</v>
       </c>
       <c r="D36">
-        <v>22578.06856434181</v>
+        <v>23010.06042801066</v>
       </c>
       <c r="E36">
         <v>391.7860000000001</v>
@@ -4239,45 +4239,45 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M36">
-        <v>653.1707412142325</v>
+        <v>608.6738940142327</v>
       </c>
       <c r="N36">
-        <v>1200.570075112298</v>
+        <v>1245.066922312298</v>
       </c>
       <c r="O36">
-        <v>240.1140150224596</v>
+        <v>249.0133844624596</v>
       </c>
       <c r="P36">
-        <v>960.4560600898385</v>
+        <v>996.0535378498383</v>
       </c>
       <c r="Q36">
-        <v>2413.756060089839</v>
+        <v>2449.353537849838</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1187831143375883</v>
+        <v>0.1187633679261691</v>
       </c>
       <c r="T36">
         <v>1.128720096686168</v>
       </c>
       <c r="U36">
-        <v>0.07633097776675757</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V36">
         <v>0.2</v>
       </c>
       <c r="W36">
-        <v>0.06106478221340605</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y36">
-        <v>2.838064688691444</v>
+        <v>3.045540205611618</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4288,13 +4288,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.09920816259487635</v>
+        <v>0.09843915793036015</v>
       </c>
       <c r="C37">
-        <v>16383.5438767018</v>
+        <v>16612.09081924655</v>
       </c>
       <c r="D37">
-        <v>22563.30887670181</v>
+        <v>22791.85581924655</v>
       </c>
       <c r="E37">
         <v>643.4650000000001</v>
@@ -4321,37 +4321,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M37">
-        <v>672.3816453675923</v>
+        <v>648.5979798675924</v>
       </c>
       <c r="N37">
-        <v>1181.359170958938</v>
+        <v>1205.142836458938</v>
       </c>
       <c r="O37">
-        <v>236.2718341917877</v>
+        <v>241.0285672917877</v>
       </c>
       <c r="P37">
-        <v>945.0873367671505</v>
+        <v>964.1142691671506</v>
       </c>
       <c r="Q37">
-        <v>2398.38733676715</v>
+        <v>2417.41426916715</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1197469058772065</v>
+        <v>0.1197268987010278</v>
       </c>
       <c r="T37">
         <v>1.143625611333724</v>
       </c>
       <c r="U37">
-        <v>0.07633097776675757</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V37">
         <v>0.2</v>
       </c>
       <c r="W37">
-        <v>0.06106478221340605</v>
+        <v>0.05890478221340606</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.756977126157403</v>
+        <v>2.858073681797408</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4370,13 +4370,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.09925744377438636</v>
+        <v>0.09846686707689063</v>
       </c>
       <c r="C38">
-        <v>16117.12447379913</v>
+        <v>16351.9525476278</v>
       </c>
       <c r="D38">
-        <v>22548.56847379913</v>
+        <v>22783.3965476278</v>
       </c>
       <c r="E38">
         <v>895.1439999999984</v>
@@ -4403,37 +4403,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M38">
-        <v>691.5925495209519</v>
+        <v>667.1293507209521</v>
       </c>
       <c r="N38">
-        <v>1162.148266805579</v>
+        <v>1186.611465605579</v>
       </c>
       <c r="O38">
-        <v>232.4296533611158</v>
+        <v>237.3222931211157</v>
       </c>
       <c r="P38">
-        <v>929.718613444463</v>
+        <v>949.2891724844628</v>
       </c>
       <c r="Q38">
-        <v>2383.018613444463</v>
+        <v>2402.589172484463</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1207408159024378</v>
+        <v>0.1207205398126007</v>
       </c>
       <c r="T38">
         <v>1.158996923314016</v>
       </c>
       <c r="U38">
-        <v>0.07633097776675757</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V38">
         <v>0.2</v>
       </c>
       <c r="W38">
-        <v>0.06106478221340605</v>
+        <v>0.05890478221340606</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.680394428208587</v>
+        <v>2.778682746191925</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4452,13 +4452,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.09930672495389636</v>
+        <v>0.09849457622342112</v>
       </c>
       <c r="C39">
-        <v>15850.72431786283</v>
+        <v>16091.82055305181</v>
       </c>
       <c r="D39">
-        <v>22533.84731786283</v>
+        <v>22774.94355305181</v>
       </c>
       <c r="E39">
         <v>1146.822999999999</v>
@@ -4485,37 +4485,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M39">
-        <v>710.8034536743118</v>
+        <v>685.6607215743118</v>
       </c>
       <c r="N39">
-        <v>1142.937362652219</v>
+        <v>1168.080094752219</v>
       </c>
       <c r="O39">
-        <v>228.5874725304438</v>
+        <v>233.6160189504438</v>
       </c>
       <c r="P39">
-        <v>914.349890121775</v>
+        <v>934.4640758017752</v>
       </c>
       <c r="Q39">
-        <v>2367.649890121775</v>
+        <v>2387.764075801775</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1217662786268827</v>
+        <v>0.1217457250864458</v>
       </c>
       <c r="T39">
         <v>1.174856213452412</v>
       </c>
       <c r="U39">
-        <v>0.07633097776675757</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V39">
         <v>0.2</v>
       </c>
       <c r="W39">
-        <v>0.06106478221340605</v>
+        <v>0.05890478221340606</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.6079513355543</v>
+        <v>2.703583212511062</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4534,13 +4534,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.09935600613340639</v>
+        <v>0.09852228536995158</v>
       </c>
       <c r="C40">
-        <v>15584.34337122053</v>
+        <v>15831.69482853452</v>
       </c>
       <c r="D40">
-        <v>22519.14537122053</v>
+        <v>22766.49682853452</v>
       </c>
       <c r="E40">
         <v>1398.502</v>
@@ -4567,37 +4567,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M40">
-        <v>730.0143578276717</v>
+        <v>704.1920924276717</v>
       </c>
       <c r="N40">
-        <v>1123.726458498859</v>
+        <v>1149.548723898859</v>
       </c>
       <c r="O40">
-        <v>224.7452916997718</v>
+        <v>229.9097447797718</v>
       </c>
       <c r="P40">
-        <v>898.9811667990871</v>
+        <v>919.6389791190871</v>
       </c>
       <c r="Q40">
-        <v>2352.281166799087</v>
+        <v>2372.938979119087</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1228248207940517</v>
+        <v>0.1228039808529956</v>
       </c>
       <c r="T40">
         <v>1.191227093595273</v>
       </c>
       <c r="U40">
-        <v>0.07633097776675757</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V40">
         <v>0.2</v>
       </c>
       <c r="W40">
-        <v>0.06106478221340605</v>
+        <v>0.05890478221340606</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.539321037250239</v>
+        <v>2.632436285866033</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4616,13 +4616,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.1002476873129164</v>
+        <v>0.09854999451648205</v>
       </c>
       <c r="C41">
-        <v>15069.92626751647</v>
+        <v>15571.57536710225</v>
       </c>
       <c r="D41">
-        <v>22256.40726751647</v>
+        <v>22758.05636710225</v>
       </c>
       <c r="E41">
         <v>1650.181</v>
@@ -4649,45 +4649,45 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M41">
-        <v>775.7270606810315</v>
+        <v>722.7234632810315</v>
       </c>
       <c r="N41">
-        <v>1078.013755645499</v>
+        <v>1131.017353045499</v>
       </c>
       <c r="O41">
-        <v>215.6027511290999</v>
+        <v>226.2034706090998</v>
       </c>
       <c r="P41">
-        <v>862.4110045163994</v>
+        <v>904.8138824363992</v>
       </c>
       <c r="Q41">
-        <v>2315.711004516399</v>
+        <v>2358.113882436399</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1239180692617836</v>
+        <v>0.1238969335299241</v>
       </c>
       <c r="T41">
         <v>1.208134723906753</v>
       </c>
       <c r="U41">
-        <v>0.07903097776675758</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V41">
         <v>0.2</v>
       </c>
       <c r="W41">
-        <v>0.06322478221340606</v>
+        <v>0.05890478221340606</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y41">
-        <v>2.389681771187771</v>
+        <v>2.564937919561776</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4698,13 +4698,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.1003185684924264</v>
+        <v>0.09857770366301254</v>
       </c>
       <c r="C42">
-        <v>14797.62459475295</v>
+        <v>15311.46216179163</v>
       </c>
       <c r="D42">
-        <v>22235.78459475295</v>
+        <v>22749.62216179163</v>
       </c>
       <c r="E42">
         <v>1901.860000000001</v>
@@ -4731,45 +4731,45 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M42">
-        <v>795.6174981343913</v>
+        <v>741.2548341343913</v>
       </c>
       <c r="N42">
-        <v>1058.123318192139</v>
+        <v>1112.485982192139</v>
       </c>
       <c r="O42">
-        <v>211.6246636384279</v>
+        <v>222.4971964384279</v>
       </c>
       <c r="P42">
-        <v>846.4986545537115</v>
+        <v>889.9887857537115</v>
       </c>
       <c r="Q42">
-        <v>2299.798654553711</v>
+        <v>2343.288785753712</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1250477593451066</v>
+        <v>0.1250263179627502</v>
       </c>
       <c r="T42">
         <v>1.225605941895281</v>
       </c>
       <c r="U42">
-        <v>0.07903097776675758</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V42">
         <v>0.2</v>
       </c>
       <c r="W42">
-        <v>0.06322478221340606</v>
+        <v>0.05890478221340606</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y42">
-        <v>2.329939726908076</v>
+        <v>2.500814471572732</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4780,13 +4780,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.1003894496719364</v>
+        <v>0.099753412809543</v>
       </c>
       <c r="C43">
-        <v>14525.36110433538</v>
+        <v>14707.58760749582</v>
       </c>
       <c r="D43">
-        <v>22215.20010433538</v>
+        <v>22397.42660749582</v>
       </c>
       <c r="E43">
         <v>2153.539000000001</v>
@@ -4813,37 +4813,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M43">
-        <v>815.5079355877511</v>
+        <v>795.9021414877511</v>
       </c>
       <c r="N43">
-        <v>1038.232880738779</v>
+        <v>1057.83867483878</v>
       </c>
       <c r="O43">
-        <v>207.6465761477559</v>
+        <v>211.5677349677559</v>
       </c>
       <c r="P43">
-        <v>830.5863045910235</v>
+        <v>846.2709398710236</v>
       </c>
       <c r="Q43">
-        <v>2283.886304591023</v>
+        <v>2299.570939871024</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1262157440075253</v>
+        <v>0.1261939866136382</v>
       </c>
       <c r="T43">
         <v>1.243669404561387</v>
       </c>
       <c r="U43">
-        <v>0.07903097776675758</v>
+        <v>0.07713097776675758</v>
       </c>
       <c r="V43">
         <v>0.2</v>
       </c>
       <c r="W43">
-        <v>0.06322478221340606</v>
+        <v>0.06170478221340606</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.273111928690806</v>
+        <v>2.329106456305545</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4862,13 +4862,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.1020395308514464</v>
+        <v>0.09980912195607347</v>
       </c>
       <c r="C44">
-        <v>13805.02810563608</v>
+        <v>14439.49077020624</v>
       </c>
       <c r="D44">
-        <v>21746.54610563608</v>
+        <v>22381.00877020624</v>
       </c>
       <c r="E44">
         <v>2405.217999999999</v>
@@ -4895,45 +4895,45 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M44">
-        <v>885.0798076411108</v>
+        <v>815.3143888411108</v>
       </c>
       <c r="N44">
-        <v>968.6610086854198</v>
+        <v>1038.42642748542</v>
       </c>
       <c r="O44">
-        <v>193.732201737084</v>
+        <v>207.685285497084</v>
       </c>
       <c r="P44">
-        <v>774.9288069483358</v>
+        <v>830.7411419883359</v>
       </c>
       <c r="Q44">
-        <v>2228.228806948336</v>
+        <v>2284.041141988336</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1274240040031308</v>
+        <v>0.1274019197007637</v>
       </c>
       <c r="T44">
         <v>1.262355745250462</v>
       </c>
       <c r="U44">
-        <v>0.08373097776675759</v>
+        <v>0.07713097776675758</v>
       </c>
       <c r="V44">
         <v>0.2</v>
       </c>
       <c r="W44">
-        <v>0.06698478221340608</v>
+        <v>0.06170478221340606</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y44">
-        <v>2.094433519240561</v>
+        <v>2.273651540679223</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4944,13 +4944,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.1021480120309564</v>
+        <v>0.100828031102604</v>
       </c>
       <c r="C45">
-        <v>13523.23017411714</v>
+        <v>13891.72254583645</v>
       </c>
       <c r="D45">
-        <v>21716.42717411714</v>
+        <v>22084.91954583645</v>
       </c>
       <c r="E45">
         <v>2656.896999999999</v>
@@ -4977,37 +4977,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M45">
-        <v>906.1531363944706</v>
+        <v>865.0287877944706</v>
       </c>
       <c r="N45">
-        <v>947.58767993206</v>
+        <v>988.71202853206</v>
       </c>
       <c r="O45">
-        <v>189.517535986412</v>
+        <v>197.742405706412</v>
       </c>
       <c r="P45">
-        <v>758.0701439456481</v>
+        <v>790.969622825648</v>
       </c>
       <c r="Q45">
-        <v>2211.370143945648</v>
+        <v>2244.269622825648</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1286746590863014</v>
+        <v>0.1286522364049813</v>
       </c>
       <c r="T45">
         <v>1.281697747016347</v>
       </c>
       <c r="U45">
-        <v>0.08373097776675759</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V45">
         <v>0.2</v>
       </c>
       <c r="W45">
-        <v>0.06698478221340608</v>
+        <v>0.06394478221340608</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.045725762979153</v>
+        <v>2.142981646949507</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5026,13 +5026,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1055300932104664</v>
+        <v>0.1009061402491344</v>
       </c>
       <c r="C46">
-        <v>12372.65780114947</v>
+        <v>13617.66844639208</v>
       </c>
       <c r="D46">
-        <v>20817.53380114948</v>
+        <v>22062.54444639208</v>
       </c>
       <c r="E46">
         <v>2908.575999999999</v>
@@ -5059,45 +5059,45 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M46">
-        <v>1030.21351194783</v>
+        <v>885.1457363478305</v>
       </c>
       <c r="N46">
-        <v>823.5273043787004</v>
+        <v>968.5950799787001</v>
       </c>
       <c r="O46">
-        <v>164.7054608757401</v>
+        <v>193.7190159957401</v>
       </c>
       <c r="P46">
-        <v>658.8218435029603</v>
+        <v>774.8760639829601</v>
       </c>
       <c r="Q46">
-        <v>2112.12184350296</v>
+        <v>2228.17606398296</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1299699804224424</v>
+        <v>0.1299472072772067</v>
       </c>
       <c r="T46">
         <v>1.301730534559584</v>
       </c>
       <c r="U46">
-        <v>0.09303097776675757</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V46">
         <v>0.2</v>
       </c>
       <c r="W46">
-        <v>0.07442478221340607</v>
+        <v>0.06394478221340608</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y46">
-        <v>1.799375367171852</v>
+        <v>2.094277518609746</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5108,13 +5108,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1057129743899765</v>
+        <v>0.1009842493956649</v>
       </c>
       <c r="C47">
-        <v>12074.48842042742</v>
+        <v>13343.65963924449</v>
       </c>
       <c r="D47">
-        <v>20771.04342042742</v>
+        <v>22040.21463924449</v>
       </c>
       <c r="E47">
         <v>3160.254999999999</v>
@@ -5141,45 +5141,45 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M47">
-        <v>1053.62745540119</v>
+        <v>905.2626849011903</v>
       </c>
       <c r="N47">
-        <v>800.1133609253404</v>
+        <v>948.4781314253404</v>
       </c>
       <c r="O47">
-        <v>160.0226721850681</v>
+        <v>189.6956262850681</v>
       </c>
       <c r="P47">
-        <v>640.0906887402723</v>
+        <v>758.7825051402723</v>
       </c>
       <c r="Q47">
-        <v>2093.390688740272</v>
+        <v>2212.082505140272</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1313124043526249</v>
+        <v>0.1312892679993312</v>
       </c>
       <c r="T47">
         <v>1.322491787104394</v>
       </c>
       <c r="U47">
-        <v>0.09303097776675757</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V47">
         <v>0.2</v>
       </c>
       <c r="W47">
-        <v>0.07442478221340607</v>
+        <v>0.06394478221340608</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y47">
-        <v>1.759389247901367</v>
+        <v>2.047738018196196</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5190,13 +5190,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.1076254555694865</v>
+        <v>0.1010623585421954</v>
       </c>
       <c r="C48">
-        <v>11348.79190862471</v>
+        <v>13069.69598700986</v>
       </c>
       <c r="D48">
-        <v>20297.02590862471</v>
+        <v>22017.92998700986</v>
       </c>
       <c r="E48">
         <v>3411.933999999999</v>
@@ -5223,45 +5223,45 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M48">
-        <v>1131.45439865455</v>
+        <v>925.37963345455</v>
       </c>
       <c r="N48">
-        <v>722.2864176719809</v>
+        <v>928.3611828719806</v>
       </c>
       <c r="O48">
-        <v>144.4572835343962</v>
+        <v>185.6722365743962</v>
       </c>
       <c r="P48">
-        <v>577.8291341375847</v>
+        <v>742.6889462975845</v>
       </c>
       <c r="Q48">
-        <v>2031.129134137585</v>
+        <v>2195.988946297584</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.132704547687629</v>
+        <v>0.132681034674127</v>
       </c>
       <c r="T48">
         <v>1.344021974928642</v>
       </c>
       <c r="U48">
-        <v>0.09773097776675757</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V48">
         <v>0.2</v>
       </c>
       <c r="W48">
-        <v>0.07818478221340606</v>
+        <v>0.06394478221340608</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y48">
-        <v>1.638369887934393</v>
+        <v>2.003221974322366</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5272,13 +5272,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.1078459367489965</v>
+        <v>0.1040732676887259</v>
       </c>
       <c r="C49">
-        <v>11043.85283880888</v>
+        <v>11992.06043822411</v>
       </c>
       <c r="D49">
-        <v>20243.76583880889</v>
+        <v>21191.97343822411</v>
       </c>
       <c r="E49">
         <v>3663.613000000001</v>
@@ -5305,45 +5305,45 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M49">
-        <v>1156.05123340791</v>
+        <v>1037.76210340791</v>
       </c>
       <c r="N49">
-        <v>697.6895829186208</v>
+        <v>815.9787129186207</v>
       </c>
       <c r="O49">
-        <v>139.5379165837242</v>
+        <v>163.1957425837242</v>
       </c>
       <c r="P49">
-        <v>558.1516663348966</v>
+        <v>652.7829703348965</v>
       </c>
       <c r="Q49">
-        <v>2011.451666334897</v>
+        <v>2106.082970334896</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1341492247333879</v>
+        <v>0.1341253208460849</v>
       </c>
       <c r="T49">
         <v>1.366364622670785</v>
       </c>
       <c r="U49">
-        <v>0.09773097776675757</v>
+        <v>0.08773097776675759</v>
       </c>
       <c r="V49">
         <v>0.2</v>
       </c>
       <c r="W49">
-        <v>0.07818478221340606</v>
+        <v>0.07018478221340607</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y49">
-        <v>1.603510954148554</v>
+        <v>1.786286866940916</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5354,13 +5354,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1080664179285065</v>
+        <v>0.1057113768352563</v>
       </c>
       <c r="C50">
-        <v>10739.19254984556</v>
+        <v>11316.52094823443</v>
       </c>
       <c r="D50">
-        <v>20190.78454984556</v>
+        <v>20768.11294823443</v>
       </c>
       <c r="E50">
         <v>3915.291999999999</v>
@@ -5387,37 +5387,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M50">
-        <v>1180.64806816127</v>
+        <v>1106.956456961269</v>
       </c>
       <c r="N50">
-        <v>673.0927481652611</v>
+        <v>746.7843593652613</v>
       </c>
       <c r="O50">
-        <v>134.6185496330522</v>
+        <v>149.3568718730523</v>
       </c>
       <c r="P50">
-        <v>538.4741985322089</v>
+        <v>597.427487492209</v>
       </c>
       <c r="Q50">
-        <v>1991.774198532209</v>
+        <v>2050.727487492209</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1356494662809068</v>
+        <v>0.135625156486195</v>
       </c>
       <c r="T50">
         <v>1.389566603018396</v>
       </c>
       <c r="U50">
-        <v>0.09773097776675757</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V50">
         <v>0.2</v>
       </c>
       <c r="W50">
-        <v>0.07818478221340606</v>
+        <v>0.07330478221340607</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.570104475937126</v>
+        <v>1.674628486666292</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5436,13 +5436,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1082868991080165</v>
+        <v>0.1058830859817868</v>
       </c>
       <c r="C51">
-        <v>10434.80885860132</v>
+        <v>11021.39196573967</v>
       </c>
       <c r="D51">
-        <v>20138.07985860132</v>
+        <v>20724.66296573967</v>
       </c>
       <c r="E51">
         <v>4166.971</v>
@@ -5469,37 +5469,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M51">
-        <v>1205.244902914629</v>
+        <v>1130.018049814629</v>
       </c>
       <c r="N51">
-        <v>648.4959134119015</v>
+        <v>723.7227665119015</v>
       </c>
       <c r="O51">
-        <v>129.6991826823803</v>
+        <v>144.7445533023803</v>
       </c>
       <c r="P51">
-        <v>518.7967307295212</v>
+        <v>578.9782132095212</v>
       </c>
       <c r="Q51">
-        <v>1972.096730729521</v>
+        <v>2032.278213209521</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1372085408302892</v>
+        <v>0.137183809210231</v>
       </c>
       <c r="T51">
         <v>1.413678464948265</v>
       </c>
       <c r="U51">
-        <v>0.09773097776675757</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V51">
         <v>0.2</v>
       </c>
       <c r="W51">
-        <v>0.07818478221340606</v>
+        <v>0.07330478221340607</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.538061527448614</v>
+        <v>1.640452395101673</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5518,13 +5518,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1085073802875265</v>
+        <v>0.1060547951283173</v>
       </c>
       <c r="C52">
-        <v>10130.69960467823</v>
+        <v>10726.44441132748</v>
       </c>
       <c r="D52">
-        <v>20085.64960467823</v>
+        <v>20681.39441132748</v>
       </c>
       <c r="E52">
         <v>4418.65</v>
@@ -5551,37 +5551,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M52">
-        <v>1229.841737667989</v>
+        <v>1153.079642667989</v>
       </c>
       <c r="N52">
-        <v>623.8990786585416</v>
+        <v>700.6611736585417</v>
       </c>
       <c r="O52">
-        <v>124.7798157317083</v>
+        <v>140.1322347317083</v>
       </c>
       <c r="P52">
-        <v>499.1192629268333</v>
+        <v>560.5289389268333</v>
       </c>
       <c r="Q52">
-        <v>1952.419262926833</v>
+        <v>2013.828938926833</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1388299783616469</v>
+        <v>0.1388048080432285</v>
       </c>
       <c r="T52">
         <v>1.43875480135533</v>
       </c>
       <c r="U52">
-        <v>0.09773097776675757</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V52">
         <v>0.2</v>
       </c>
       <c r="W52">
-        <v>0.07818478221340606</v>
+        <v>0.07330478221340607</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.507300296899641</v>
+        <v>1.60764334719964</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5600,13 +5600,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1153782614670365</v>
+        <v>0.1062265042748478</v>
       </c>
       <c r="C53">
-        <v>8371.681282453668</v>
+        <v>10431.6771510191</v>
       </c>
       <c r="D53">
-        <v>18578.31028245367</v>
+        <v>20638.3061510191</v>
       </c>
       <c r="E53">
         <v>4670.329</v>
@@ -5633,45 +5633,45 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M53">
-        <v>1463.659325121349</v>
+        <v>1176.141235521349</v>
       </c>
       <c r="N53">
-        <v>390.0814912051817</v>
+        <v>677.5995808051819</v>
       </c>
       <c r="O53">
-        <v>78.01629824103634</v>
+        <v>135.5199161610364</v>
       </c>
       <c r="P53">
-        <v>312.0651929641454</v>
+        <v>542.0796646441455</v>
       </c>
       <c r="Q53">
-        <v>1765.365192964145</v>
+        <v>1995.379664644146</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1405175970167335</v>
+        <v>0.1404919700938993</v>
       </c>
       <c r="T53">
         <v>1.464854661697377</v>
       </c>
       <c r="U53">
-        <v>0.1140309777667576</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V53">
         <v>0.2</v>
       </c>
       <c r="W53">
-        <v>0.09122478221340607</v>
+        <v>0.07330478221340607</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y53">
-        <v>1.266511123531318</v>
+        <v>1.576120928627098</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5682,13 +5682,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1300477118349225</v>
+        <v>0.1063982134213782</v>
       </c>
       <c r="C54">
-        <v>5554.389809346922</v>
+        <v>10137.08906026645</v>
       </c>
       <c r="D54">
-        <v>16012.69780934692</v>
+        <v>20595.39706026645</v>
       </c>
       <c r="E54">
         <v>4922.008</v>
@@ -5715,45 +5715,45 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M54">
-        <v>1920.313499174709</v>
+        <v>1199.202828374709</v>
       </c>
       <c r="N54">
-        <v>-66.57268284817815</v>
+        <v>654.5379879518221</v>
       </c>
       <c r="O54">
-        <v>-13.31453656963563</v>
+        <v>130.9075975903644</v>
       </c>
       <c r="P54">
-        <v>-53.25814627854252</v>
+        <v>523.6303903614577</v>
       </c>
       <c r="Q54">
-        <v>1400.041853721458</v>
+        <v>1976.930390361458</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1426637428679607</v>
+        <v>0.142249430563348</v>
       </c>
       <c r="T54">
-        <v>1.498045872769774</v>
+        <v>1.492042016220342</v>
       </c>
       <c r="U54">
-        <v>0.1467309777667576</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V54">
-        <v>0.1930664776478644</v>
+        <v>0.2</v>
       </c>
       <c r="W54">
-        <v>0.1184021447275026</v>
+        <v>0.07330478221340607</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y54">
-        <v>0.9653323882393219</v>
+        <v>1.545810910768885</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5764,13 +5764,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.13105702161259</v>
+        <v>0.1065699225679087</v>
       </c>
       <c r="C55">
-        <v>5151.997018783368</v>
+        <v>9842.679023854202</v>
       </c>
       <c r="D55">
-        <v>15861.98401878337</v>
+        <v>20552.6660238542</v>
       </c>
       <c r="E55">
         <v>5173.687</v>
@@ -5797,45 +5797,45 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M55">
-        <v>1957.242604928069</v>
+        <v>1222.264421228068</v>
       </c>
       <c r="N55">
-        <v>-103.501788601538</v>
+        <v>631.4763950984623</v>
       </c>
       <c r="O55">
-        <v>-20.7003577203076</v>
+        <v>126.2952790196925</v>
       </c>
       <c r="P55">
-        <v>-82.8014308812304</v>
+        <v>505.1811160787698</v>
       </c>
       <c r="Q55">
-        <v>1370.49856911877</v>
+        <v>1958.48111607877</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.144724673567279</v>
+        <v>0.1440816765846882</v>
       </c>
       <c r="T55">
-        <v>1.529919189211684</v>
+        <v>1.520386279446413</v>
       </c>
       <c r="U55">
-        <v>0.1467309777667576</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V55">
-        <v>0.1894237139186594</v>
+        <v>0.2</v>
       </c>
       <c r="W55">
-        <v>0.1189366510112621</v>
+        <v>0.07330478221340607</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y55">
-        <v>0.9471185695932969</v>
+        <v>1.516644667169472</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5846,13 +5846,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1320663313902576</v>
+        <v>0.1128760317144392</v>
       </c>
       <c r="C56">
-        <v>4752.414853504659</v>
+        <v>8135.817549631025</v>
       </c>
       <c r="D56">
-        <v>15714.08085350466</v>
+        <v>19097.48354963103</v>
       </c>
       <c r="E56">
         <v>5425.366</v>
@@ -5879,45 +5879,45 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M56">
-        <v>1994.171710681429</v>
+        <v>1438.313471281428</v>
       </c>
       <c r="N56">
-        <v>-140.4308943548979</v>
+        <v>415.4273450451024</v>
       </c>
       <c r="O56">
-        <v>-28.08617887097958</v>
+        <v>83.08546900902047</v>
       </c>
       <c r="P56">
-        <v>-112.3447154839183</v>
+        <v>332.3418760360819</v>
       </c>
       <c r="Q56">
-        <v>1340.955284516082</v>
+        <v>1785.641876036082</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1468752099491763</v>
+        <v>0.1459935854765215</v>
       </c>
       <c r="T56">
-        <v>1.563178302020633</v>
+        <v>1.549962901943182</v>
       </c>
       <c r="U56">
-        <v>0.1467309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V56">
-        <v>0.1859158673646101</v>
+        <v>0.2</v>
       </c>
       <c r="W56">
-        <v>0.1194513607659935</v>
+        <v>0.08466478221340606</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y56">
-        <v>0.9295793368230506</v>
+        <v>1.288829489078614</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5928,13 +5928,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1330756411679252</v>
+        <v>0.1131613408609696</v>
       </c>
       <c r="C57">
-        <v>4355.565417825841</v>
+        <v>7823.158092517737</v>
       </c>
       <c r="D57">
-        <v>15568.91041782584</v>
+        <v>19036.50309251774</v>
       </c>
       <c r="E57">
         <v>5677.045</v>
@@ -5961,45 +5961,45 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M57">
-        <v>2031.100816434788</v>
+        <v>1464.948905934788</v>
       </c>
       <c r="N57">
-        <v>-177.3600001082575</v>
+        <v>388.7919103917425</v>
       </c>
       <c r="O57">
-        <v>-35.4720000216515</v>
+        <v>77.7583820783485</v>
       </c>
       <c r="P57">
-        <v>-141.888000086606</v>
+        <v>311.033528313394</v>
       </c>
       <c r="Q57">
-        <v>1311.411999913394</v>
+        <v>1764.333528313394</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1491213257258247</v>
+        <v>0.1479904680968807</v>
       </c>
       <c r="T57">
-        <v>1.597915597621092</v>
+        <v>1.580854040995363</v>
       </c>
       <c r="U57">
-        <v>0.1467309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V57">
-        <v>0.1825355788670718</v>
+        <v>0.2</v>
       </c>
       <c r="W57">
-        <v>0.1199473538023711</v>
+        <v>0.08466478221340606</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y57">
-        <v>0.9126778943353588</v>
+        <v>1.265396225640821</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6010,13 +6010,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1340849509455928</v>
+        <v>0.1267097482093424</v>
       </c>
       <c r="C58">
-        <v>3961.373668189193</v>
+        <v>5065.017641306033</v>
       </c>
       <c r="D58">
-        <v>15426.39766818919</v>
+        <v>16530.04164130603</v>
       </c>
       <c r="E58">
         <v>5928.724</v>
@@ -6043,37 +6043,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M58">
-        <v>2068.029922188148</v>
+        <v>1894.673426988148</v>
       </c>
       <c r="N58">
-        <v>-214.2891058616171</v>
+        <v>-40.93261066161722</v>
       </c>
       <c r="O58">
-        <v>-42.85782117232343</v>
+        <v>-8.186522132323445</v>
       </c>
       <c r="P58">
-        <v>-171.4312846892937</v>
+        <v>-32.74608852929377</v>
       </c>
       <c r="Q58">
-        <v>1281.868715310706</v>
+        <v>1420.553911470706</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1514695376741389</v>
+        <v>0.1503622587281154</v>
       </c>
       <c r="T58">
-        <v>1.634231861203389</v>
+        <v>1.617544887740754</v>
       </c>
       <c r="U58">
-        <v>0.1467309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V58">
-        <v>0.1792760149587312</v>
+        <v>0.1956791909277278</v>
       </c>
       <c r="W58">
-        <v>0.1204256328017351</v>
+        <v>0.1081256328017351</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8963800747936561</v>
+        <v>0.978395954638639</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6092,13 +6092,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1350942607232603</v>
+        <v>0.12759605798701</v>
       </c>
       <c r="C59">
-        <v>3569.767283810985</v>
+        <v>4672.175799047674</v>
       </c>
       <c r="D59">
-        <v>15286.47028381099</v>
+        <v>16388.87879904768</v>
       </c>
       <c r="E59">
         <v>6180.403000000002</v>
@@ -6125,37 +6125,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M59">
-        <v>2104.959027941508</v>
+        <v>1928.506881041508</v>
       </c>
       <c r="N59">
-        <v>-251.2182116149772</v>
+        <v>-74.76606471497735</v>
       </c>
       <c r="O59">
-        <v>-50.24364232299545</v>
+        <v>-14.95321294299547</v>
       </c>
       <c r="P59">
-        <v>-200.9745692919818</v>
+        <v>-59.81285177198188</v>
       </c>
       <c r="Q59">
-        <v>1252.325430708018</v>
+        <v>1393.487148228018</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1539269687828398</v>
+        <v>0.152793939163653</v>
       </c>
       <c r="T59">
-        <v>1.672237253324399</v>
+        <v>1.655162210711469</v>
       </c>
       <c r="U59">
-        <v>0.1467309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V59">
-        <v>0.1761308217138412</v>
+        <v>0.1922462226658378</v>
       </c>
       <c r="W59">
-        <v>0.1208871300818232</v>
+        <v>0.1085871300818232</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8806541085692058</v>
+        <v>0.9612311133291891</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6174,13 +6174,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1361035705009279</v>
+        <v>0.1284823677646776</v>
       </c>
       <c r="C60">
-        <v>3180.676544305008</v>
+        <v>4281.724539671815</v>
       </c>
       <c r="D60">
-        <v>15149.05854430501</v>
+        <v>16250.10653967181</v>
       </c>
       <c r="E60">
         <v>6432.081999999999</v>
@@ -6207,37 +6207,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M60">
-        <v>2141.888133694868</v>
+        <v>1962.340335094867</v>
       </c>
       <c r="N60">
-        <v>-288.1473173683369</v>
+        <v>-108.5995187683366</v>
       </c>
       <c r="O60">
-        <v>-57.62946347366738</v>
+        <v>-21.71990375366731</v>
       </c>
       <c r="P60">
-        <v>-230.5178538946695</v>
+        <v>-86.87961501466926</v>
       </c>
       <c r="Q60">
-        <v>1222.78214610533</v>
+        <v>1366.420384985331</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1565014204205264</v>
+        <v>0.1553414139056447</v>
       </c>
       <c r="T60">
-        <v>1.712052426022598</v>
+        <v>1.694570834776027</v>
       </c>
       <c r="U60">
-        <v>0.1467309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V60">
-        <v>0.1730940834084301</v>
+        <v>0.1889316326198751</v>
       </c>
       <c r="W60">
-        <v>0.1213327136625979</v>
+        <v>0.1090327136625979</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8654704170421506</v>
+        <v>0.9446581630993757</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6256,13 +6256,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1371128802785955</v>
+        <v>0.1293686775423452</v>
       </c>
       <c r="C61">
-        <v>2794.034213847483</v>
+        <v>3893.603646529389</v>
       </c>
       <c r="D61">
-        <v>15014.09521384748</v>
+        <v>16113.66464652939</v>
       </c>
       <c r="E61">
         <v>6683.760999999999</v>
@@ -6289,37 +6289,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M61">
-        <v>2178.817239448227</v>
+        <v>1996.173789148227</v>
       </c>
       <c r="N61">
-        <v>-325.0764231216965</v>
+        <v>-142.4329728216965</v>
       </c>
       <c r="O61">
-        <v>-65.0152846243393</v>
+        <v>-28.4865945643393</v>
       </c>
       <c r="P61">
-        <v>-260.0611384973572</v>
+        <v>-113.9463782573572</v>
       </c>
       <c r="Q61">
-        <v>1193.238861502643</v>
+        <v>1339.353621742643</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1592014550649295</v>
+        <v>0.1580131557082214</v>
       </c>
       <c r="T61">
-        <v>1.753809802267052</v>
+        <v>1.735901830746174</v>
       </c>
       <c r="U61">
-        <v>0.1467309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V61">
-        <v>0.1701602853845584</v>
+        <v>0.1857294015585213</v>
       </c>
       <c r="W61">
-        <v>0.1217631927152108</v>
+        <v>0.1094631927152108</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8508014269227921</v>
+        <v>0.9286470077926066</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6338,13 +6338,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1381221900562631</v>
+        <v>0.1302549873200127</v>
       </c>
       <c r="C62">
-        <v>2409.775431479253</v>
+        <v>3507.75490853673</v>
       </c>
       <c r="D62">
-        <v>14881.51543147925</v>
+        <v>15979.49490853673</v>
       </c>
       <c r="E62">
         <v>6935.439999999999</v>
@@ -6371,37 +6371,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M62">
-        <v>2215.746345201587</v>
+        <v>2030.007243201587</v>
       </c>
       <c r="N62">
-        <v>-362.0055288750561</v>
+        <v>-176.2664268750561</v>
       </c>
       <c r="O62">
-        <v>-72.40110577501123</v>
+        <v>-35.25328537501123</v>
       </c>
       <c r="P62">
-        <v>-289.6044231000449</v>
+        <v>-141.0131415000449</v>
       </c>
       <c r="Q62">
-        <v>1163.695576899955</v>
+        <v>1312.286858499955</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1620364914415528</v>
+        <v>0.160818484600927</v>
       </c>
       <c r="T62">
-        <v>1.797655047323728</v>
+        <v>1.779299376514829</v>
       </c>
       <c r="U62">
-        <v>0.1467309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V62">
-        <v>0.1673242806281492</v>
+        <v>0.182633911532546</v>
       </c>
       <c r="W62">
-        <v>0.1221793224660699</v>
+        <v>0.1098793224660699</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8366214031407457</v>
+        <v>0.9131695576627299</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6420,13 +6420,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1391314998339306</v>
+        <v>0.1311412970976803</v>
       </c>
       <c r="C63">
-        <v>2027.837607169104</v>
+        <v>3124.122037368785</v>
       </c>
       <c r="D63">
-        <v>14751.25660716911</v>
+        <v>15847.54103736878</v>
       </c>
       <c r="E63">
         <v>7187.118999999999</v>
@@ -6453,37 +6453,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M63">
-        <v>2252.675450954947</v>
+        <v>2063.840697254946</v>
       </c>
       <c r="N63">
-        <v>-398.9346346284162</v>
+        <v>-210.0998809284158</v>
       </c>
       <c r="O63">
-        <v>-79.78692692568325</v>
+        <v>-42.01997618568316</v>
       </c>
       <c r="P63">
-        <v>-319.147707702733</v>
+        <v>-168.0799047427327</v>
       </c>
       <c r="Q63">
-        <v>1134.152292297267</v>
+        <v>1285.220095257267</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1650169142990285</v>
+        <v>0.1637676765137712</v>
       </c>
       <c r="T63">
-        <v>1.843748766485875</v>
+        <v>1.824922437451107</v>
       </c>
       <c r="U63">
-        <v>0.1467309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V63">
-        <v>0.1645812596342451</v>
+        <v>0.1796399129828321</v>
       </c>
       <c r="W63">
-        <v>0.1225818086185402</v>
+        <v>0.1102818086185402</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8229062981712252</v>
+        <v>0.8981995649141605</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6502,13 +6502,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1401408096115982</v>
+        <v>0.1320276068753479</v>
       </c>
       <c r="C64">
-        <v>1648.160323288294</v>
+        <v>2742.650588721453</v>
       </c>
       <c r="D64">
-        <v>14623.25832328829</v>
+        <v>15717.74858872145</v>
       </c>
       <c r="E64">
         <v>7438.797999999999</v>
@@ -6535,37 +6535,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M64">
-        <v>2289.604556708307</v>
+        <v>2097.674151308307</v>
       </c>
       <c r="N64">
-        <v>-435.8637403817759</v>
+        <v>-243.9333349817759</v>
       </c>
       <c r="O64">
-        <v>-87.17274807635518</v>
+        <v>-48.78666699635519</v>
       </c>
       <c r="P64">
-        <v>-348.6909923054207</v>
+        <v>-195.1466679854207</v>
       </c>
       <c r="Q64">
-        <v>1104.609007694579</v>
+        <v>1258.153332014579</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.168154201517424</v>
+        <v>0.1668720890536073</v>
       </c>
       <c r="T64">
-        <v>1.892268470867082</v>
+        <v>1.872946712120873</v>
       </c>
       <c r="U64">
-        <v>0.1467309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V64">
-        <v>0.1619267231885314</v>
+        <v>0.1767424950314961</v>
       </c>
       <c r="W64">
-        <v>0.1229713113467373</v>
+        <v>0.1106713113467373</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.809633615942657</v>
+        <v>0.8837124751574804</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6584,13 +6584,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1626967270037341</v>
+        <v>0.1329139166530155</v>
       </c>
       <c r="C65">
-        <v>-978.6188407840455</v>
+        <v>2363.287887411807</v>
       </c>
       <c r="D65">
-        <v>12248.15815921596</v>
+        <v>15590.06488741181</v>
       </c>
       <c r="E65">
         <v>7690.477000000001</v>
@@ -6617,45 +6617,45 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M65">
-        <v>2845.017570361667</v>
+        <v>2131.507605361666</v>
       </c>
       <c r="N65">
-        <v>-991.2767540351363</v>
+        <v>-277.7667890351356</v>
       </c>
       <c r="O65">
-        <v>-198.2553508070273</v>
+        <v>-55.55335780702713</v>
       </c>
       <c r="P65">
-        <v>-793.021403228109</v>
+        <v>-222.2134312281085</v>
       </c>
       <c r="Q65">
-        <v>660.278596771891</v>
+        <v>1231.086568771892</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1740167680840255</v>
+        <v>0.1701443076766778</v>
       </c>
       <c r="T65">
-        <v>1.982935973370131</v>
+        <v>1.923566893529545</v>
       </c>
       <c r="U65">
-        <v>0.1794309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V65">
-        <v>0.1303148940546527</v>
+        <v>0.1739370586024247</v>
       </c>
       <c r="W65">
-        <v>0.1560484489089598</v>
+        <v>0.1110484489089598</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y65">
-        <v>0.6515744702732637</v>
+        <v>0.8696852930121236</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1983972591133556</v>
+        <v>0.1338002264306831</v>
       </c>
       <c r="C66">
-        <v>-3735.040876915356</v>
+        <v>1985.982956099433</v>
       </c>
       <c r="D66">
-        <v>9743.415123084646</v>
+        <v>15464.43895609944</v>
       </c>
       <c r="E66">
         <v>7942.156000000001</v>
@@ -6699,45 +6699,45 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M66">
-        <v>3730.985782615026</v>
+        <v>2165.341059415026</v>
       </c>
       <c r="N66">
-        <v>-1877.244966288496</v>
+        <v>-311.6002430884957</v>
       </c>
       <c r="O66">
-        <v>-375.4489932576992</v>
+        <v>-62.32004861769915</v>
       </c>
       <c r="P66">
-        <v>-1501.795973030797</v>
+        <v>-249.2801944707966</v>
       </c>
       <c r="Q66">
-        <v>-48.49597303079668</v>
+        <v>1204.019805529203</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1802345181195648</v>
+        <v>0.1735983162232522</v>
       </c>
       <c r="T66">
-        <v>2.079096564555945</v>
+        <v>1.976999307238699</v>
       </c>
       <c r="U66">
-        <v>0.2316309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V66">
-        <v>0.0993700284232793</v>
+        <v>0.1712192920617618</v>
       </c>
       <c r="W66">
-        <v>0.2086138009223629</v>
+        <v>0.1114138009223629</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y66">
-        <v>0.4968501421163964</v>
+        <v>0.856096460308809</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6748,13 +6748,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.2002555688910232</v>
+        <v>0.1346865362083506</v>
       </c>
       <c r="C67">
-        <v>-4089.343771735603</v>
+        <v>1610.686447426593</v>
       </c>
       <c r="D67">
-        <v>9640.791228264399</v>
+        <v>15340.8214474266</v>
       </c>
       <c r="E67">
         <v>8193.835000000001</v>
@@ -6781,45 +6781,45 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M67">
-        <v>3789.282435468386</v>
+        <v>2199.174513468386</v>
       </c>
       <c r="N67">
-        <v>-1935.541619141856</v>
+        <v>-345.4336971418554</v>
       </c>
       <c r="O67">
-        <v>-387.1083238283711</v>
+        <v>-69.08673942837109</v>
       </c>
       <c r="P67">
-        <v>-1548.433295313484</v>
+        <v>-276.3469577134844</v>
       </c>
       <c r="Q67">
-        <v>-95.1332953134845</v>
+        <v>1176.953042286515</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1840755043515524</v>
+        <v>0.1772496966867737</v>
       </c>
       <c r="T67">
-        <v>2.138499323543258</v>
+        <v>2.033485001731234</v>
       </c>
       <c r="U67">
-        <v>0.2316309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V67">
-        <v>0.09784125875522885</v>
+        <v>0.1685851491069655</v>
       </c>
       <c r="W67">
-        <v>0.2089679113353536</v>
+        <v>0.1117679113353536</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y67">
-        <v>0.4892062937761442</v>
+        <v>0.8429257455348274</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6830,13 +6830,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.2021138786686907</v>
+        <v>0.1355728459860182</v>
       </c>
       <c r="C68">
-        <v>-4441.507397400215</v>
+        <v>1237.350579387174</v>
       </c>
       <c r="D68">
-        <v>9540.306602599787</v>
+        <v>15219.16457938718</v>
       </c>
       <c r="E68">
         <v>8445.514000000001</v>
@@ -6863,45 +6863,45 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M68">
-        <v>3847.579088321746</v>
+        <v>2233.007967521746</v>
       </c>
       <c r="N68">
-        <v>-1993.838271995215</v>
+        <v>-379.2671511952151</v>
       </c>
       <c r="O68">
-        <v>-398.7676543990431</v>
+        <v>-75.85343023904302</v>
       </c>
       <c r="P68">
-        <v>-1595.070617596172</v>
+        <v>-303.4137209561721</v>
       </c>
       <c r="Q68">
-        <v>-141.7706175961723</v>
+        <v>1149.886279043828</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1881424309501275</v>
+        <v>0.1811158642363847</v>
       </c>
       <c r="T68">
-        <v>2.201396362471001</v>
+        <v>2.093293384135094</v>
       </c>
       <c r="U68">
-        <v>0.2316309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V68">
-        <v>0.0963588154407557</v>
+        <v>0.1660308286659509</v>
       </c>
       <c r="W68">
-        <v>0.2093112911297688</v>
+        <v>0.1121112911297688</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y68">
-        <v>0.4817940772037784</v>
+        <v>0.8301541433297543</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6912,13 +6912,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.2039721884463583</v>
+        <v>0.1364591557636858</v>
       </c>
       <c r="C69">
-        <v>-4791.597955810321</v>
+        <v>865.9290737467491</v>
       </c>
       <c r="D69">
-        <v>9441.895044189681</v>
+        <v>15099.42207374675</v>
       </c>
       <c r="E69">
         <v>8697.193000000001</v>
@@ -6945,45 +6945,45 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M69">
-        <v>3905.875741175106</v>
+        <v>2266.841421575106</v>
       </c>
       <c r="N69">
-        <v>-2052.134924848576</v>
+        <v>-413.1006052485752</v>
       </c>
       <c r="O69">
-        <v>-410.4269849697152</v>
+        <v>-82.62012104971505</v>
       </c>
       <c r="P69">
-        <v>-1641.707939878861</v>
+        <v>-330.4804841988602</v>
       </c>
       <c r="Q69">
-        <v>-188.4079398788606</v>
+        <v>1122.81951580114</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1924558379486162</v>
+        <v>0.1852163449708206</v>
       </c>
       <c r="T69">
-        <v>2.268105343151941</v>
+        <v>2.156726516987672</v>
       </c>
       <c r="U69">
-        <v>0.2316309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V69">
-        <v>0.09492062416552052</v>
+        <v>0.1635527565963098</v>
       </c>
       <c r="W69">
-        <v>0.2096444207810672</v>
+        <v>0.1124444207810671</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y69">
-        <v>0.4746031208276025</v>
+        <v>0.8177637829815489</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6994,13 +6994,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.2058304982240259</v>
+        <v>0.1373454655413534</v>
       </c>
       <c r="C70">
-        <v>-5139.678945174639</v>
+        <v>496.3770973469109</v>
       </c>
       <c r="D70">
-        <v>9345.493054825363</v>
+        <v>14981.54909734691</v>
       </c>
       <c r="E70">
         <v>8948.872000000001</v>
@@ -7027,45 +7027,45 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M70">
-        <v>3964.172394028466</v>
+        <v>2300.674875628466</v>
       </c>
       <c r="N70">
-        <v>-2110.431577701936</v>
+        <v>-446.9340593019349</v>
       </c>
       <c r="O70">
-        <v>-422.0863155403871</v>
+        <v>-89.38681186038698</v>
       </c>
       <c r="P70">
-        <v>-1688.345262161548</v>
+        <v>-357.5472474415479</v>
       </c>
       <c r="Q70">
-        <v>-235.0452621615484</v>
+        <v>1095.752752558452</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1970388328845104</v>
+        <v>0.1895731057511587</v>
       </c>
       <c r="T70">
-        <v>2.338983635125438</v>
+        <v>2.224124220643537</v>
       </c>
       <c r="U70">
-        <v>0.2316309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V70">
-        <v>0.09352473263367463</v>
+        <v>0.1611475689993052</v>
       </c>
       <c r="W70">
-        <v>0.2099677525014449</v>
+        <v>0.1127677525014449</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y70">
-        <v>0.467623663168373</v>
+        <v>0.8057378449965261</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7076,13 +7076,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2076888080016935</v>
+        <v>0.1586715490370706</v>
       </c>
       <c r="C71">
-        <v>-5485.811296638358</v>
+        <v>-2124.381344470705</v>
       </c>
       <c r="D71">
-        <v>9251.039703361645</v>
+        <v>12612.4696555293</v>
       </c>
       <c r="E71">
         <v>9200.551000000001</v>
@@ -7109,45 +7109,45 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M71">
-        <v>4022.469046881826</v>
+        <v>2824.225327881825</v>
       </c>
       <c r="N71">
-        <v>-2168.728230555295</v>
+        <v>-970.4845115552946</v>
       </c>
       <c r="O71">
-        <v>-433.7456461110591</v>
+        <v>-194.0969023110589</v>
       </c>
       <c r="P71">
-        <v>-1734.982584444236</v>
+        <v>-776.3876092442357</v>
       </c>
       <c r="Q71">
-        <v>-281.6825844442362</v>
+        <v>676.9123907557642</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.2019175049130431</v>
+        <v>0.1973779598658725</v>
       </c>
       <c r="T71">
-        <v>2.414434720129485</v>
+        <v>2.344862831557103</v>
       </c>
       <c r="U71">
-        <v>0.2316309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V71">
-        <v>0.09216930172594022</v>
+        <v>0.1312742859449419</v>
       </c>
       <c r="W71">
-        <v>0.2102817122878988</v>
+        <v>0.1412817122878988</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y71">
-        <v>0.460846508629701</v>
+        <v>0.6563714297247096</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7158,13 +7158,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2095471177793611</v>
+        <v>0.1988064934103418</v>
       </c>
       <c r="C72">
-        <v>-5830.053502709554</v>
+        <v>-5268.693818991298</v>
       </c>
       <c r="D72">
-        <v>9158.476497290449</v>
+        <v>9719.836181008704</v>
       </c>
       <c r="E72">
         <v>9452.230000000001</v>
@@ -7191,37 +7191,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M72">
-        <v>4080.765699735186</v>
+        <v>3816.502749735185</v>
       </c>
       <c r="N72">
-        <v>-2227.024883408655</v>
+        <v>-1962.761933408655</v>
       </c>
       <c r="O72">
-        <v>-445.4049766817311</v>
+        <v>-392.5523866817309</v>
       </c>
       <c r="P72">
-        <v>-1781.619906726924</v>
+        <v>-1570.209546726924</v>
       </c>
       <c r="Q72">
-        <v>-328.319906726924</v>
+        <v>-116.9095467269237</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.2071214217434778</v>
+        <v>0.2063193405134138</v>
       </c>
       <c r="T72">
-        <v>2.494915877467134</v>
+        <v>2.483183146474761</v>
       </c>
       <c r="U72">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V72">
-        <v>0.09085259741556964</v>
+        <v>0.09714342883442995</v>
       </c>
       <c r="W72">
-        <v>0.2105867017947396</v>
+        <v>0.1955867017947396</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4542629870778481</v>
+        <v>0.4857171441721497</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7240,13 +7240,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.2114054275570286</v>
+        <v>0.2005148031880094</v>
       </c>
       <c r="C73">
-        <v>-6172.461738052067</v>
+        <v>-5614.340210682059</v>
       </c>
       <c r="D73">
-        <v>9067.747261947932</v>
+        <v>9625.868789317939</v>
       </c>
       <c r="E73">
         <v>9703.908999999998</v>
@@ -7273,37 +7273,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M73">
-        <v>4139.062352588544</v>
+        <v>3871.024217588544</v>
       </c>
       <c r="N73">
-        <v>-2285.321536262013</v>
+        <v>-2017.283401262014</v>
       </c>
       <c r="O73">
-        <v>-457.0643072524026</v>
+        <v>-403.4566802524027</v>
       </c>
       <c r="P73">
-        <v>-1828.25722900961</v>
+        <v>-1613.826721009611</v>
       </c>
       <c r="Q73">
-        <v>-374.9572290096105</v>
+        <v>-160.5267210096108</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.2126842293898046</v>
+        <v>0.2118544901862901</v>
       </c>
       <c r="T73">
-        <v>2.580947459448759</v>
+        <v>2.568810151525614</v>
       </c>
       <c r="U73">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V73">
-        <v>0.08957298336746305</v>
+        <v>0.09577521152690277</v>
       </c>
       <c r="W73">
-        <v>0.2108831000478666</v>
+        <v>0.1958831000478666</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.4478649168373153</v>
+        <v>0.4788760576345139</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7322,13 +7322,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.2132637373346962</v>
+        <v>0.202223112965677</v>
       </c>
       <c r="C74">
-        <v>-6513.089973168875</v>
+        <v>-5958.187122561405</v>
       </c>
       <c r="D74">
-        <v>8978.798026831124</v>
+        <v>9533.700877438594</v>
       </c>
       <c r="E74">
         <v>9955.587999999998</v>
@@ -7355,37 +7355,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M74">
-        <v>4197.359005441905</v>
+        <v>3925.545685441904</v>
       </c>
       <c r="N74">
-        <v>-2343.618189115374</v>
+        <v>-2071.804869115374</v>
       </c>
       <c r="O74">
-        <v>-468.7236378230748</v>
+        <v>-414.3609738230747</v>
       </c>
       <c r="P74">
-        <v>-1874.894551292299</v>
+        <v>-1657.443895292299</v>
       </c>
       <c r="Q74">
-        <v>-421.594551292299</v>
+        <v>-204.1438952922988</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.2186443804394405</v>
+        <v>0.2177850076929433</v>
       </c>
       <c r="T74">
-        <v>2.673124154429072</v>
+        <v>2.660553371222958</v>
       </c>
       <c r="U74">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V74">
-        <v>0.08832891415402605</v>
+        <v>0.0944450002556958</v>
       </c>
       <c r="W74">
-        <v>0.2111712650161846</v>
+        <v>0.1961712650161845</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.4416445707701303</v>
+        <v>0.4722250012784789</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7404,13 +7404,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.2151220471123638</v>
+        <v>0.2039314227433446</v>
       </c>
       <c r="C75">
-        <v>-6851.990081459509</v>
+        <v>-6300.285754568715</v>
       </c>
       <c r="D75">
-        <v>8891.57691854049</v>
+        <v>9443.281245431284</v>
       </c>
       <c r="E75">
         <v>10207.267</v>
@@ -7437,37 +7437,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M75">
-        <v>4255.655658295264</v>
+        <v>3980.067153295264</v>
       </c>
       <c r="N75">
-        <v>-2401.914841968734</v>
+        <v>-2126.326336968733</v>
       </c>
       <c r="O75">
-        <v>-480.3829683937468</v>
+        <v>-425.2652673937466</v>
       </c>
       <c r="P75">
-        <v>-1921.531873574987</v>
+        <v>-1701.061069574986</v>
       </c>
       <c r="Q75">
-        <v>-468.2318735749868</v>
+        <v>-247.7610695749863</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.2250460241594197</v>
+        <v>0.224154822792682</v>
       </c>
       <c r="T75">
-        <v>2.77212875274126</v>
+        <v>2.759092384971956</v>
       </c>
       <c r="U75">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V75">
-        <v>0.08711892902862843</v>
+        <v>0.09315123312890544</v>
       </c>
       <c r="W75">
-        <v>0.2114515350538636</v>
+        <v>0.1964515350538636</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.4355946451431422</v>
+        <v>0.4657561656445273</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7486,13 +7486,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.2169803568900314</v>
+        <v>0.2056397325210121</v>
       </c>
       <c r="C76">
-        <v>-7189.211940097663</v>
+        <v>-6640.685382527954</v>
       </c>
       <c r="D76">
-        <v>8806.034059902337</v>
+        <v>9354.560617472045</v>
       </c>
       <c r="E76">
         <v>10458.946</v>
@@ -7519,37 +7519,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M76">
-        <v>4313.952311148624</v>
+        <v>4034.588621148624</v>
       </c>
       <c r="N76">
-        <v>-2460.211494822093</v>
+        <v>-2180.847804822093</v>
       </c>
       <c r="O76">
-        <v>-492.0422989644187</v>
+        <v>-436.1695609644187</v>
       </c>
       <c r="P76">
-        <v>-1968.169195857675</v>
+        <v>-1744.678243857674</v>
       </c>
       <c r="Q76">
-        <v>-514.8691958576746</v>
+        <v>-291.3782438576745</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.2319401020117051</v>
+        <v>0.2310146236693236</v>
       </c>
       <c r="T76">
-        <v>2.878749089385154</v>
+        <v>2.865211322855493</v>
       </c>
       <c r="U76">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V76">
-        <v>0.08594164620391724</v>
+        <v>0.09189243268121754</v>
       </c>
       <c r="W76">
-        <v>0.2117242302256595</v>
+        <v>0.1967242302256595</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.4297082310195862</v>
+        <v>0.4594621634060876</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7568,13 +7568,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.2188386666676989</v>
+        <v>0.2073480422986797</v>
       </c>
       <c r="C77">
-        <v>-7524.803525141255</v>
+        <v>-6979.43344769272</v>
       </c>
       <c r="D77">
-        <v>8722.121474858748</v>
+        <v>9267.491552307283</v>
       </c>
       <c r="E77">
         <v>10710.625</v>
@@ -7601,37 +7601,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M77">
-        <v>4372.248964001985</v>
+        <v>4089.110089001984</v>
       </c>
       <c r="N77">
-        <v>-2518.508147675454</v>
+        <v>-2235.369272675453</v>
       </c>
       <c r="O77">
-        <v>-503.7016295350908</v>
+        <v>-447.0738545350907</v>
       </c>
       <c r="P77">
-        <v>-2014.806518140363</v>
+        <v>-1788.295418140363</v>
       </c>
       <c r="Q77">
-        <v>-561.5065181403631</v>
+        <v>-334.9954181403627</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.2393857060921734</v>
+        <v>0.2384232086160966</v>
       </c>
       <c r="T77">
-        <v>2.993899052960561</v>
+        <v>2.979819775769713</v>
       </c>
       <c r="U77">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V77">
-        <v>0.08479575758786499</v>
+        <v>0.09066720024546794</v>
       </c>
       <c r="W77">
-        <v>0.2119896535262075</v>
+        <v>0.1969896535262075</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.423978787939325</v>
+        <v>0.4533360012273397</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7650,13 +7650,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.2206969764453665</v>
+        <v>0.2090563520763473</v>
       </c>
       <c r="C78">
-        <v>-7858.811001255977</v>
+        <v>-7316.57564133668</v>
       </c>
       <c r="D78">
-        <v>8639.792998744026</v>
+        <v>9182.028358663323</v>
       </c>
       <c r="E78">
         <v>10962.304</v>
@@ -7683,37 +7683,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M78">
-        <v>4430.545616855345</v>
+        <v>4143.631556855344</v>
       </c>
       <c r="N78">
-        <v>-2576.804800528814</v>
+        <v>-2289.890740528813</v>
       </c>
       <c r="O78">
-        <v>-515.3609601057627</v>
+        <v>-457.9781481057626</v>
       </c>
       <c r="P78">
-        <v>-2061.443840423051</v>
+        <v>-1831.91259242305</v>
       </c>
       <c r="Q78">
-        <v>-608.143840423051</v>
+        <v>-378.6125924230503</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.2474517771793472</v>
+        <v>0.2464491756417672</v>
       </c>
       <c r="T78">
-        <v>3.118644846833918</v>
+        <v>3.103978933093452</v>
       </c>
       <c r="U78">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V78">
-        <v>0.08368002393539309</v>
+        <v>0.0894742107685539</v>
       </c>
       <c r="W78">
-        <v>0.2122480920030568</v>
+        <v>0.1972480920030568</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4184001196769654</v>
+        <v>0.4473710538427695</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7732,13 +7732,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.2225552862230341</v>
+        <v>0.2107646618540149</v>
       </c>
       <c r="C79">
-        <v>-8191.278806404973</v>
+        <v>-7652.15598470632</v>
       </c>
       <c r="D79">
-        <v>8559.00419359503</v>
+        <v>9098.127015293683</v>
       </c>
       <c r="E79">
         <v>11213.983</v>
@@ -7765,37 +7765,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M79">
-        <v>4488.842269708704</v>
+        <v>4198.153024708704</v>
       </c>
       <c r="N79">
-        <v>-2635.101453382174</v>
+        <v>-2344.412208382173</v>
       </c>
       <c r="O79">
-        <v>-527.0202906764347</v>
+        <v>-468.8824416764346</v>
       </c>
       <c r="P79">
-        <v>-2108.081162705739</v>
+        <v>-1875.529766705738</v>
       </c>
       <c r="Q79">
-        <v>-654.7811627057388</v>
+        <v>-422.2297667057385</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.2562192457523623</v>
+        <v>0.2551730528435832</v>
       </c>
       <c r="T79">
-        <v>3.254238101044089</v>
+        <v>3.238934538880123</v>
       </c>
       <c r="U79">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V79">
-        <v>0.08259327037779057</v>
+        <v>0.08831220803129994</v>
       </c>
       <c r="W79">
-        <v>0.2124998177921958</v>
+        <v>0.1974998177921958</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4129663518889529</v>
+        <v>0.4415610401564998</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7814,13 +7814,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.2244135960007017</v>
+        <v>0.2124729716316824</v>
       </c>
       <c r="C80">
-        <v>-8522.249731830991</v>
+        <v>-7986.216904629937</v>
       </c>
       <c r="D80">
-        <v>8479.712268169013</v>
+        <v>9015.745095370066</v>
       </c>
       <c r="E80">
         <v>11465.662</v>
@@ -7847,37 +7847,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M80">
-        <v>4547.138922562064</v>
+        <v>4252.674492562063</v>
       </c>
       <c r="N80">
-        <v>-2693.398106235533</v>
+        <v>-2398.933676235532</v>
       </c>
       <c r="O80">
-        <v>-538.6796212471066</v>
+        <v>-479.7867352471065</v>
       </c>
       <c r="P80">
-        <v>-2154.718484988427</v>
+        <v>-1919.146940988426</v>
       </c>
       <c r="Q80">
-        <v>-701.4184849884266</v>
+        <v>-465.846940988426</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.2657837569229243</v>
+        <v>0.2646900097910188</v>
       </c>
       <c r="T80">
-        <v>3.402158014727911</v>
+        <v>3.386158836101947</v>
       </c>
       <c r="U80">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V80">
-        <v>0.08153438229602403</v>
+        <v>0.08718000023602687</v>
       </c>
       <c r="W80">
-        <v>0.2127450890739209</v>
+        <v>0.1977450890739209</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4076719114801202</v>
+        <v>0.4359000011801344</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7896,13 +7896,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2262719057783693</v>
+        <v>0.21418128140935</v>
       </c>
       <c r="C81">
-        <v>-8851.764997633596</v>
+        <v>-8318.79930505574</v>
       </c>
       <c r="D81">
-        <v>8401.876002366407</v>
+        <v>8934.841694944264</v>
       </c>
       <c r="E81">
         <v>11717.341</v>
@@ -7929,37 +7929,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M81">
-        <v>4605.435575415424</v>
+        <v>4307.195960415424</v>
       </c>
       <c r="N81">
-        <v>-2751.694759088893</v>
+        <v>-2453.455144088893</v>
       </c>
       <c r="O81">
-        <v>-550.3389518177786</v>
+        <v>-490.6910288177785</v>
       </c>
       <c r="P81">
-        <v>-2201.355807271114</v>
+        <v>-1962.764115271114</v>
       </c>
       <c r="Q81">
-        <v>-748.0558072711144</v>
+        <v>-509.4641152711142</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.276259173919254</v>
+        <v>0.2751133435905911</v>
       </c>
       <c r="T81">
-        <v>3.564165539238763</v>
+        <v>3.547404494963945</v>
       </c>
       <c r="U81">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V81">
-        <v>0.08050230150746676</v>
+        <v>0.08607645592924172</v>
       </c>
       <c r="W81">
-        <v>0.2129841509561088</v>
+        <v>0.1979841509561087</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4025115075373339</v>
+        <v>0.4303822796462086</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7978,13 +7978,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2281302155560368</v>
+        <v>0.2158895911870176</v>
       </c>
       <c r="C82">
-        <v>-9179.864324221822</v>
+        <v>-8649.94263477248</v>
       </c>
       <c r="D82">
-        <v>8325.455675778181</v>
+        <v>8855.377365227523</v>
       </c>
       <c r="E82">
         <v>11969.02</v>
@@ -8011,37 +8011,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M82">
-        <v>4663.732228268784</v>
+        <v>4361.717428268783</v>
       </c>
       <c r="N82">
-        <v>-2809.991411942253</v>
+        <v>-2507.976611942252</v>
       </c>
       <c r="O82">
-        <v>-561.9982823884505</v>
+        <v>-501.5953223884504</v>
       </c>
       <c r="P82">
-        <v>-2247.993129553802</v>
+        <v>-2006.381289553802</v>
       </c>
       <c r="Q82">
-        <v>-794.6931295538022</v>
+        <v>-553.0812895538018</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2877821326152167</v>
+        <v>0.2865790107701207</v>
       </c>
       <c r="T82">
-        <v>3.742373816200702</v>
+        <v>3.724774719712142</v>
       </c>
       <c r="U82">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V82">
-        <v>0.07949602273862344</v>
+        <v>0.0850005002301262</v>
       </c>
       <c r="W82">
-        <v>0.2132172362912418</v>
+        <v>0.1982172362912418</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3974801136931172</v>
+        <v>0.4250025011506311</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8060,13 +8060,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2299885253337044</v>
+        <v>0.2175979009646851</v>
       </c>
       <c r="C83">
-        <v>-9506.585999902542</v>
+        <v>-8979.684951548223</v>
       </c>
       <c r="D83">
-        <v>8250.413000097462</v>
+        <v>8777.314048451781</v>
       </c>
       <c r="E83">
         <v>12220.699</v>
@@ -8093,37 +8093,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M83">
-        <v>4722.028881122144</v>
+        <v>4416.238896122143</v>
       </c>
       <c r="N83">
-        <v>-2868.288064795613</v>
+        <v>-2562.498079795612</v>
       </c>
       <c r="O83">
-        <v>-573.6576129591225</v>
+        <v>-512.4996159591225</v>
       </c>
       <c r="P83">
-        <v>-2294.63045183649</v>
+        <v>-2049.99846383649</v>
       </c>
       <c r="Q83">
-        <v>-841.3304518364901</v>
+        <v>-596.69846383649</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.3005180343318071</v>
+        <v>0.2992515902843376</v>
       </c>
       <c r="T83">
-        <v>3.939340859158634</v>
+        <v>3.920815494433834</v>
       </c>
       <c r="U83">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V83">
-        <v>0.07851459035913426</v>
+        <v>0.08395111133839624</v>
       </c>
       <c r="W83">
-        <v>0.2134445664329149</v>
+        <v>0.1984445664329149</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3925729517956713</v>
+        <v>0.4197555566919813</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8142,13 +8142,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.231846835111372</v>
+        <v>0.2193062107423528</v>
       </c>
       <c r="C84">
-        <v>-9831.966944846179</v>
+        <v>-9308.062982906298</v>
       </c>
       <c r="D84">
-        <v>8176.711055153825</v>
+        <v>8700.615017093705</v>
       </c>
       <c r="E84">
         <v>12472.378</v>
@@ -8175,37 +8175,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M84">
-        <v>4780.325533975503</v>
+        <v>4470.760363975503</v>
       </c>
       <c r="N84">
-        <v>-2926.584717648972</v>
+        <v>-2617.019547648972</v>
       </c>
       <c r="O84">
-        <v>-585.3169435297945</v>
+        <v>-523.4039095297943</v>
       </c>
       <c r="P84">
-        <v>-2341.267774119178</v>
+        <v>-2093.615638119177</v>
       </c>
       <c r="Q84">
-        <v>-887.9677741191779</v>
+        <v>-640.3156381191773</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.3146690362391297</v>
+        <v>0.3133322341890231</v>
       </c>
       <c r="T84">
-        <v>4.158193129111892</v>
+        <v>4.138638577457936</v>
       </c>
       <c r="U84">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V84">
-        <v>0.07755709535475457</v>
+        <v>0.0829273172976841</v>
       </c>
       <c r="W84">
-        <v>0.2136663519369862</v>
+        <v>0.1986663519369861</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3877854767737728</v>
+        <v>0.4146365864884205</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8224,13 +8224,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2337051448890395</v>
+        <v>0.2210145205200204</v>
       </c>
       <c r="C85">
-        <v>-10156.04277165429</v>
+        <v>-9635.112183742387</v>
       </c>
       <c r="D85">
-        <v>8104.314228345715</v>
+        <v>8625.244816257617</v>
       </c>
       <c r="E85">
         <v>12724.057</v>
@@ -8257,37 +8257,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M85">
-        <v>4838.622186828863</v>
+        <v>4525.281831828863</v>
       </c>
       <c r="N85">
-        <v>-2984.881370502332</v>
+        <v>-2671.541015502332</v>
       </c>
       <c r="O85">
-        <v>-596.9762741004664</v>
+        <v>-534.3082031004664</v>
       </c>
       <c r="P85">
-        <v>-2387.905096401866</v>
+        <v>-2137.232812401865</v>
       </c>
       <c r="Q85">
-        <v>-934.6050964018657</v>
+        <v>-683.9328124018655</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.330484861900255</v>
+        <v>0.3290694244354362</v>
       </c>
       <c r="T85">
-        <v>4.402792724942003</v>
+        <v>4.382087905543697</v>
       </c>
       <c r="U85">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V85">
-        <v>0.07662267251915511</v>
+        <v>0.08192819299289272</v>
       </c>
       <c r="W85">
-        <v>0.2138827932120436</v>
+        <v>0.1988827932120436</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3831133625957756</v>
+        <v>0.4096409649644636</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8306,13 +8306,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2355634546667071</v>
+        <v>0.2227228302976879</v>
       </c>
       <c r="C86">
-        <v>-10478.84784273781</v>
+        <v>-9960.866790972621</v>
       </c>
       <c r="D86">
-        <v>8033.188157262193</v>
+        <v>8551.169209027379</v>
       </c>
       <c r="E86">
         <v>12975.736</v>
@@ -8339,37 +8339,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M86">
-        <v>4896.918839682222</v>
+        <v>4579.803299682221</v>
       </c>
       <c r="N86">
-        <v>-3043.178023355691</v>
+        <v>-2726.06248335569</v>
       </c>
       <c r="O86">
-        <v>-608.6356046711383</v>
+        <v>-545.2124966711381</v>
       </c>
       <c r="P86">
-        <v>-2434.542418684553</v>
+        <v>-2180.849986684552</v>
       </c>
       <c r="Q86">
-        <v>-981.2424186845531</v>
+        <v>-727.5499866845523</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.3482776657690208</v>
+        <v>0.3467737634626508</v>
       </c>
       <c r="T86">
-        <v>4.677967270250876</v>
+        <v>4.655968399640176</v>
       </c>
       <c r="U86">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V86">
-        <v>0.07571049784630805</v>
+        <v>0.08095285736202497</v>
       </c>
       <c r="W86">
-        <v>0.2140940811234093</v>
+        <v>0.1990940811234093</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3785524892315403</v>
+        <v>0.4047642868101249</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8388,13 +8388,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2374217644443747</v>
+        <v>0.2244311400753555</v>
       </c>
       <c r="C87">
-        <v>-10800.41532470013</v>
+        <v>-10285.35987538972</v>
       </c>
       <c r="D87">
-        <v>7963.299675299869</v>
+        <v>8478.35512461028</v>
       </c>
       <c r="E87">
         <v>13227.415</v>
@@ -8421,37 +8421,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M87">
-        <v>4955.215492535582</v>
+        <v>4634.324767535581</v>
       </c>
       <c r="N87">
-        <v>-3101.474676209051</v>
+        <v>-2780.583951209051</v>
       </c>
       <c r="O87">
-        <v>-620.2949352418102</v>
+        <v>-556.1167902418101</v>
       </c>
       <c r="P87">
-        <v>-2481.179740967241</v>
+        <v>-2224.46716096724</v>
       </c>
       <c r="Q87">
-        <v>-1027.879740967241</v>
+        <v>-771.1671609672405</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.3684428434869555</v>
+        <v>0.3668386810268275</v>
       </c>
       <c r="T87">
-        <v>4.989831754934268</v>
+        <v>4.966366292949521</v>
       </c>
       <c r="U87">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V87">
-        <v>0.07481978610693972</v>
+        <v>0.08000047080482467</v>
       </c>
       <c r="W87">
-        <v>0.2143003975545075</v>
+        <v>0.1993003975545075</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3740989305346986</v>
+        <v>0.4000023540241233</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8470,13 +8470,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2392800742220423</v>
+        <v>0.2261394498530231</v>
       </c>
       <c r="C88">
-        <v>-11120.77723990591</v>
+        <v>-10608.62339089206</v>
       </c>
       <c r="D88">
-        <v>7894.61676009409</v>
+        <v>8406.770609107938</v>
       </c>
       <c r="E88">
         <v>13479.094</v>
@@ -8503,37 +8503,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M88">
-        <v>5013.512145388941</v>
+        <v>4688.846235388941</v>
       </c>
       <c r="N88">
-        <v>-3159.771329062411</v>
+        <v>-2835.10541906241</v>
       </c>
       <c r="O88">
-        <v>-631.9542658124822</v>
+        <v>-567.0210838124821</v>
       </c>
       <c r="P88">
-        <v>-2527.817063249929</v>
+        <v>-2268.084335249928</v>
       </c>
       <c r="Q88">
-        <v>-1074.517063249929</v>
+        <v>-814.7843352499278</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.391488760878881</v>
+        <v>0.3897700153858867</v>
       </c>
       <c r="T88">
-        <v>5.346248308858145</v>
+        <v>5.321106742445917</v>
       </c>
       <c r="U88">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V88">
-        <v>0.07394978859406832</v>
+        <v>0.07907023277221042</v>
       </c>
       <c r="W88">
-        <v>0.2145019159290685</v>
+        <v>0.1995019159290685</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3697489429703417</v>
+        <v>0.3953511638610522</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8552,13 +8552,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2411383839997099</v>
+        <v>0.2278477596306906</v>
       </c>
       <c r="C89">
-        <v>-11439.96451540399</v>
+        <v>-10930.6882212398</v>
       </c>
       <c r="D89">
-        <v>7827.108484596009</v>
+        <v>8336.384778760204</v>
       </c>
       <c r="E89">
         <v>13730.773</v>
@@ -8585,37 +8585,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M89">
-        <v>5071.808798242301</v>
+        <v>4743.367703242301</v>
       </c>
       <c r="N89">
-        <v>-3218.06798191577</v>
+        <v>-2889.62688691577</v>
       </c>
       <c r="O89">
-        <v>-643.6135963831541</v>
+        <v>-577.9253773831541</v>
       </c>
       <c r="P89">
-        <v>-2574.454385532616</v>
+        <v>-2311.701509532616</v>
       </c>
       <c r="Q89">
-        <v>-1121.154385532617</v>
+        <v>-858.401509532616</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.4180802040234102</v>
+        <v>0.4162292473386472</v>
       </c>
       <c r="T89">
-        <v>5.757498178770309</v>
+        <v>5.730422645710987</v>
       </c>
       <c r="U89">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V89">
-        <v>0.07309979102402156</v>
+        <v>0.07816137952195513</v>
       </c>
       <c r="W89">
-        <v>0.2146988016973178</v>
+        <v>0.1996988016973178</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3654989551201079</v>
+        <v>0.3908068976097757</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8634,13 +8634,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2429966937773774</v>
+        <v>0.2295560694083582</v>
       </c>
       <c r="C90">
-        <v>-11758.00702936157</v>
+        <v>-11251.58422448162</v>
       </c>
       <c r="D90">
-        <v>7760.74497063843</v>
+        <v>8267.167775518385</v>
       </c>
       <c r="E90">
         <v>13982.452</v>
@@ -8667,37 +8667,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M90">
-        <v>5130.105451095661</v>
+        <v>4797.88917109566</v>
       </c>
       <c r="N90">
-        <v>-3276.36463476913</v>
+        <v>-2944.14835476913</v>
       </c>
       <c r="O90">
-        <v>-655.2729269538261</v>
+        <v>-588.8296709538259</v>
       </c>
       <c r="P90">
-        <v>-2621.091707815304</v>
+        <v>-2355.318683815304</v>
       </c>
       <c r="Q90">
-        <v>-1167.791707815304</v>
+        <v>-902.0186838153038</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.4491035543586945</v>
+        <v>0.4470983512835344</v>
       </c>
       <c r="T90">
-        <v>6.237289693667836</v>
+        <v>6.207957866186902</v>
       </c>
       <c r="U90">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V90">
-        <v>0.07226911158056677</v>
+        <v>0.07727318202738748</v>
       </c>
       <c r="W90">
-        <v>0.214891212789016</v>
+        <v>0.199891212789016</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3613455579028338</v>
+        <v>0.3863659101369373</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8716,13 +8716,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.244855003555045</v>
+        <v>0.2312643791860258</v>
       </c>
       <c r="C91">
-        <v>-12074.93365515596</v>
+        <v>-11571.34027518654</v>
       </c>
       <c r="D91">
-        <v>7695.49734484404</v>
+        <v>8199.090724813463</v>
       </c>
       <c r="E91">
         <v>14234.131</v>
@@ -8749,37 +8749,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M91">
-        <v>5188.402103949021</v>
+        <v>4852.410638949021</v>
       </c>
       <c r="N91">
-        <v>-3334.66128762249</v>
+        <v>-2998.66982262249</v>
       </c>
       <c r="O91">
-        <v>-666.932257524498</v>
+        <v>-599.733964524498</v>
       </c>
       <c r="P91">
-        <v>-2667.729030097992</v>
+        <v>-2398.935858097992</v>
       </c>
       <c r="Q91">
-        <v>-1214.429030097992</v>
+        <v>-945.635858097992</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.4857675138458486</v>
+        <v>0.4835800195820376</v>
       </c>
       <c r="T91">
-        <v>6.804316029455822</v>
+        <v>6.772317672203894</v>
       </c>
       <c r="U91">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V91">
-        <v>0.07145709909089748</v>
+        <v>0.07640494402707974</v>
       </c>
       <c r="W91">
-        <v>0.2150793000359569</v>
+        <v>0.2000793000359569</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3572854954544874</v>
+        <v>0.3820247201353987</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8798,13 +8798,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2467133133327125</v>
+        <v>0.2329726889636934</v>
       </c>
       <c r="C92">
-        <v>-12390.77230326079</v>
+        <v>-11889.98430460611</v>
       </c>
       <c r="D92">
-        <v>7631.33769673921</v>
+        <v>8132.125695393889</v>
       </c>
       <c r="E92">
         <v>14485.81</v>
@@ -8831,37 +8831,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M92">
-        <v>5246.698756802381</v>
+        <v>4906.93210680238</v>
       </c>
       <c r="N92">
-        <v>-3392.95794047585</v>
+        <v>-3053.191290475849</v>
       </c>
       <c r="O92">
-        <v>-678.59158809517</v>
+        <v>-610.6382580951698</v>
       </c>
       <c r="P92">
-        <v>-2714.36635238068</v>
+        <v>-2442.553032380679</v>
       </c>
       <c r="Q92">
-        <v>-1261.06635238068</v>
+        <v>-989.2530323806793</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.5297642652304334</v>
+        <v>0.5273580215402414</v>
       </c>
       <c r="T92">
-        <v>7.484747632401404</v>
+        <v>7.449549439424284</v>
       </c>
       <c r="U92">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V92">
-        <v>0.07066313132322084</v>
+        <v>0.07555600020455663</v>
       </c>
       <c r="W92">
-        <v>0.2152632075662991</v>
+        <v>0.2002632075662991</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3533156566161042</v>
+        <v>0.3777800010227832</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8880,13 +8880,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2485716231103801</v>
+        <v>0.2346809987413609</v>
       </c>
       <c r="C93">
-        <v>-12705.54996105415</v>
+        <v>-12207.54333888447</v>
       </c>
       <c r="D93">
-        <v>7568.239038945851</v>
+        <v>8066.245661115528</v>
       </c>
       <c r="E93">
         <v>14737.489</v>
@@ -8913,37 +8913,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M93">
-        <v>5304.99540965574</v>
+        <v>4961.45357465574</v>
       </c>
       <c r="N93">
-        <v>-3451.254593329209</v>
+        <v>-3107.712758329209</v>
       </c>
       <c r="O93">
-        <v>-690.2509186658419</v>
+        <v>-621.542551665842</v>
       </c>
       <c r="P93">
-        <v>-2761.003674663368</v>
+        <v>-2486.170206663367</v>
       </c>
       <c r="Q93">
-        <v>-1307.703674663368</v>
+        <v>-1032.870206663368</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.5835380724782593</v>
+        <v>0.5808644683780461</v>
       </c>
       <c r="T93">
-        <v>8.316386258223782</v>
+        <v>8.277277154915872</v>
       </c>
       <c r="U93">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V93">
-        <v>0.06988661339659204</v>
+        <v>0.07472571448802304</v>
       </c>
       <c r="W93">
-        <v>0.2154430731728976</v>
+        <v>0.2004430731728976</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3494330669829603</v>
+        <v>0.3736285724401153</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8962,13 +8962,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2504299328880477</v>
+        <v>0.2363893085190285</v>
       </c>
       <c r="C94">
-        <v>-13019.29273066809</v>
+        <v>-12524.04353542604</v>
       </c>
       <c r="D94">
-        <v>7506.175269331913</v>
+        <v>8001.424464573961</v>
       </c>
       <c r="E94">
         <v>14989.168</v>
@@ -8995,37 +8995,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M94">
-        <v>5363.2920625091</v>
+        <v>5015.9750425091</v>
       </c>
       <c r="N94">
-        <v>-3509.551246182569</v>
+        <v>-3162.234226182569</v>
       </c>
       <c r="O94">
-        <v>-701.9102492365139</v>
+        <v>-632.4468452365138</v>
       </c>
       <c r="P94">
-        <v>-2807.640996946056</v>
+        <v>-2529.787380946055</v>
       </c>
       <c r="Q94">
-        <v>-1354.340996946056</v>
+        <v>-1076.487380946055</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.650755331538042</v>
+        <v>0.6477475269253019</v>
       </c>
       <c r="T94">
-        <v>9.355934540501758</v>
+        <v>9.311936799280359</v>
       </c>
       <c r="U94">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V94">
-        <v>0.06912697629445518</v>
+        <v>0.07391347846097931</v>
       </c>
       <c r="W94">
-        <v>0.2156190286576135</v>
+        <v>0.2006190286576135</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3456348814722758</v>
+        <v>0.3695673923048967</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9044,13 +9044,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2522882426657153</v>
+        <v>0.2380976182966961</v>
       </c>
       <c r="C95">
-        <v>-13332.02586499091</v>
+        <v>-12839.51021752365</v>
       </c>
       <c r="D95">
-        <v>7445.121135009093</v>
+        <v>7937.636782476352</v>
       </c>
       <c r="E95">
         <v>15240.847</v>
@@ -9077,37 +9077,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M95">
-        <v>5421.58871536246</v>
+        <v>5070.49651036246</v>
       </c>
       <c r="N95">
-        <v>-3567.847899035929</v>
+        <v>-3216.755694035929</v>
       </c>
       <c r="O95">
-        <v>-713.5695798071858</v>
+        <v>-643.3511388071859</v>
       </c>
       <c r="P95">
-        <v>-2854.278319228743</v>
+        <v>-2573.404555228743</v>
       </c>
       <c r="Q95">
-        <v>-1400.978319228743</v>
+        <v>-1120.104555228743</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.7371775217577624</v>
+        <v>0.7337400307717737</v>
       </c>
       <c r="T95">
-        <v>10.6924966177163</v>
+        <v>10.64221348489184</v>
       </c>
       <c r="U95">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V95">
-        <v>0.06838367547408468</v>
+        <v>0.07311870987537737</v>
       </c>
       <c r="W95">
-        <v>0.2157912001534107</v>
+        <v>0.2007912001534107</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3419183773704234</v>
+        <v>0.3655935493768869</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9126,13 +9126,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2541465524433829</v>
+        <v>0.2398059280743637</v>
       </c>
       <c r="C96">
-        <v>-13643.77380192667</v>
+        <v>-13153.96790734347</v>
       </c>
       <c r="D96">
-        <v>7385.052198073337</v>
+        <v>7874.858092656538</v>
       </c>
       <c r="E96">
         <v>15492.526</v>
@@ -9159,37 +9159,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M96">
-        <v>5479.885368215821</v>
+        <v>5125.01797821582</v>
       </c>
       <c r="N96">
-        <v>-3626.14455188929</v>
+        <v>-3271.277161889289</v>
       </c>
       <c r="O96">
-        <v>-725.228910377858</v>
+        <v>-654.2554323778579</v>
       </c>
       <c r="P96">
-        <v>-2900.915641511432</v>
+        <v>-2617.021729511432</v>
       </c>
       <c r="Q96">
-        <v>-1447.615641511432</v>
+        <v>-1163.721729511432</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.8524071087173896</v>
+        <v>0.8483967025670694</v>
       </c>
       <c r="T96">
-        <v>12.47457938733568</v>
+        <v>12.41591573237381</v>
       </c>
       <c r="U96">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V96">
-        <v>0.0676561895647859</v>
+        <v>0.07234085125968187</v>
       </c>
       <c r="W96">
-        <v>0.2159597084258931</v>
+        <v>0.2009597084258931</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3382809478239295</v>
+        <v>0.3617042562984094</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9208,13 +9208,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2560048622210505</v>
+        <v>0.2415142378520312</v>
       </c>
       <c r="C97">
-        <v>-13954.56019700938</v>
+        <v>-13467.44035735689</v>
       </c>
       <c r="D97">
-        <v>7325.944802990621</v>
+        <v>7813.064642643113</v>
       </c>
       <c r="E97">
         <v>15744.205</v>
@@ -9241,37 +9241,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M97">
-        <v>5538.18202106918</v>
+        <v>5179.53944606918</v>
       </c>
       <c r="N97">
-        <v>-3684.441204742649</v>
+        <v>-3325.79862974265</v>
       </c>
       <c r="O97">
-        <v>-736.88824094853</v>
+        <v>-665.15972594853</v>
       </c>
       <c r="P97">
-        <v>-2947.552963794119</v>
+        <v>-2660.63890379412</v>
       </c>
       <c r="Q97">
-        <v>-1494.25296379412</v>
+        <v>-1207.33890379412</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>1.013728530460868</v>
+        <v>1.008916043080484</v>
       </c>
       <c r="T97">
-        <v>14.96949526480283</v>
+        <v>14.89909887884859</v>
       </c>
       <c r="U97">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V97">
-        <v>0.06694401914831448</v>
+        <v>0.07157936861484311</v>
       </c>
       <c r="W97">
-        <v>0.216124669155797</v>
+        <v>0.2011246691557969</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3347200957415724</v>
+        <v>0.3578968430742155</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9290,13 +9290,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.257863171998718</v>
+        <v>0.2432225476296988</v>
       </c>
       <c r="C98">
-        <v>-14264.40795446356</v>
+        <v>-13779.95058030414</v>
       </c>
       <c r="D98">
-        <v>7267.776045536438</v>
+        <v>7752.233419695863</v>
       </c>
       <c r="E98">
         <v>15995.884</v>
@@ -9323,37 +9323,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M98">
-        <v>5596.478673922539</v>
+        <v>5234.060913922539</v>
       </c>
       <c r="N98">
-        <v>-3742.737857596008</v>
+        <v>-3380.320097596008</v>
       </c>
       <c r="O98">
-        <v>-748.5475715192017</v>
+        <v>-676.0640195192017</v>
       </c>
       <c r="P98">
-        <v>-2994.190286076807</v>
+        <v>-2704.256078076806</v>
       </c>
       <c r="Q98">
-        <v>-1540.890286076807</v>
+        <v>-1250.956078076806</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>1.255710663076082</v>
+        <v>1.249695053850602</v>
       </c>
       <c r="T98">
-        <v>18.71186908100349</v>
+        <v>18.62387359856069</v>
       </c>
       <c r="U98">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V98">
-        <v>0.06624668561551954</v>
+        <v>0.07083375019177184</v>
       </c>
       <c r="W98">
-        <v>0.2162861932038278</v>
+        <v>0.2012861932038278</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3312334280775977</v>
+        <v>0.3541687509588592</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9372,13 +9372,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2597214817763856</v>
+        <v>0.2449308574073664</v>
       </c>
       <c r="C99">
-        <v>-14573.33925679661</v>
+        <v>-14091.5208777689</v>
       </c>
       <c r="D99">
-        <v>7210.523743203389</v>
+        <v>7692.342122231098</v>
       </c>
       <c r="E99">
         <v>16247.563</v>
@@ -9405,37 +9405,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M99">
-        <v>5654.775326775899</v>
+        <v>5288.582381775899</v>
       </c>
       <c r="N99">
-        <v>-3801.034510449368</v>
+        <v>-3434.841565449368</v>
       </c>
       <c r="O99">
-        <v>-760.2069020898737</v>
+        <v>-686.9683130898737</v>
       </c>
       <c r="P99">
-        <v>-3040.827608359495</v>
+        <v>-2747.873252359494</v>
       </c>
       <c r="Q99">
-        <v>-1587.527608359495</v>
+        <v>-1294.573252359495</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.659014217434777</v>
+        <v>1.650993405134137</v>
       </c>
       <c r="T99">
-        <v>24.94915877467132</v>
+        <v>24.83183146474759</v>
       </c>
       <c r="U99">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V99">
-        <v>0.06556373009371007</v>
+        <v>0.07010350534443398</v>
       </c>
       <c r="W99">
-        <v>0.2164443868591157</v>
+        <v>0.2014443868591157</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3278186504685503</v>
+        <v>0.35051752672217</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9454,13 +9454,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2615797915540532</v>
+        <v>0.246639167185034</v>
       </c>
       <c r="C100">
-        <v>-14881.37559300345</v>
+        <v>-14402.17286743857</v>
       </c>
       <c r="D100">
-        <v>7154.166406996548</v>
+        <v>7633.369132561429</v>
       </c>
       <c r="E100">
         <v>16499.242</v>
@@ -9487,37 +9487,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M100">
-        <v>5713.071979629259</v>
+        <v>5343.103849629259</v>
       </c>
       <c r="N100">
-        <v>-3859.331163302728</v>
+        <v>-3489.363033302728</v>
       </c>
       <c r="O100">
-        <v>-771.8662326605456</v>
+        <v>-697.8726066605456</v>
       </c>
       <c r="P100">
-        <v>-3087.464930642182</v>
+        <v>-2791.490426642182</v>
       </c>
       <c r="Q100">
-        <v>-1634.164930642183</v>
+        <v>-1338.190426642182</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>2.465621326152164</v>
+        <v>2.453590107701205</v>
       </c>
       <c r="T100">
-        <v>37.42373816200698</v>
+        <v>37.24774719712138</v>
       </c>
       <c r="U100">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V100">
-        <v>0.06489471243969261</v>
+        <v>0.06938816345316426</v>
       </c>
       <c r="W100">
-        <v>0.216599352072459</v>
+        <v>0.201599352072459</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3244735621984631</v>
+        <v>0.3469408172658213</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9536,13 +9536,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2634381013317207</v>
+        <v>0.2483474769627016</v>
       </c>
       <c r="C101">
-        <v>-15188.53778545876</v>
+        <v>-14711.9275091201</v>
       </c>
       <c r="D101">
-        <v>7098.683214541239</v>
+        <v>7575.293490879904</v>
       </c>
       <c r="E101">
         <v>16750.921</v>
@@ -9569,37 +9569,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M101">
-        <v>5771.368632482619</v>
+        <v>5397.625317482619</v>
       </c>
       <c r="N101">
-        <v>-3917.627816156088</v>
+        <v>-3543.884501156088</v>
       </c>
       <c r="O101">
-        <v>-783.5255632312176</v>
+        <v>-708.7769002312176</v>
       </c>
       <c r="P101">
-        <v>-3134.10225292487</v>
+        <v>-2835.10760092487</v>
       </c>
       <c r="Q101">
-        <v>-1680.80225292487</v>
+        <v>-1381.80760092487</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>4.885442652304328</v>
+        <v>4.861380215402409</v>
       </c>
       <c r="T101">
-        <v>74.84747632401395</v>
+        <v>74.49549439424277</v>
       </c>
       <c r="U101">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V101">
-        <v>0.06423921029383713</v>
+        <v>0.06868727291323329</v>
       </c>
       <c r="W101">
-        <v>0.2167511866754317</v>
+        <v>0.2017511866754317</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.3211960514691857</v>
+        <v>0.3434363645661666</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/kazakhstan/kazakhstan_oilfield_svcs_equip.xlsx
+++ b/research/traditional_assets/database/data/kazakhstan/kazakhstan_oilfield_svcs_equip.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09746933780179359</v>
+        <v>0.09743704694832407</v>
       </c>
       <c r="C2">
-        <v>25720.9399046332</v>
+        <v>25479.38840929598</v>
       </c>
       <c r="D2">
-        <v>23091.9399046332</v>
+        <v>23102.06740929598</v>
       </c>
       <c r="E2">
-        <v>-8165.300000000001</v>
+        <v>-7913.621000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>251.679</v>
       </c>
       <c r="G2">
         <v>2629</v>
@@ -1451,28 +1451,28 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>16.64377835335978</v>
       </c>
       <c r="N2">
-        <v>1853.740816326531</v>
+        <v>1837.097037973171</v>
       </c>
       <c r="O2">
-        <v>370.7481632653062</v>
+        <v>367.4194075946342</v>
       </c>
       <c r="P2">
-        <v>1482.992653061224</v>
+        <v>1469.677630378537</v>
       </c>
       <c r="Q2">
-        <v>2936.292653061224</v>
+        <v>2922.977630378537</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09746933780179359</v>
+        <v>0.09788686780423234</v>
       </c>
       <c r="T2">
-        <v>0.7993082229751833</v>
+        <v>0.8057672793224576</v>
       </c>
       <c r="U2">
         <v>0.06613097776675758</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>111.377403433898</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09743704694832407</v>
+        <v>0.09740475609485454</v>
       </c>
       <c r="C3">
-        <v>25479.38840929598</v>
+        <v>25237.84580115955</v>
       </c>
       <c r="D3">
-        <v>23102.06740929598</v>
+        <v>23112.20380115955</v>
       </c>
       <c r="E3">
-        <v>-7913.621000000001</v>
+        <v>-7661.942000000001</v>
       </c>
       <c r="F3">
-        <v>251.679</v>
+        <v>503.3580000000001</v>
       </c>
       <c r="G3">
         <v>2629</v>
@@ -1533,28 +1533,28 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M3">
-        <v>16.64377835335978</v>
+        <v>33.28755670671956</v>
       </c>
       <c r="N3">
-        <v>1837.097037973171</v>
+        <v>1820.453259619811</v>
       </c>
       <c r="O3">
-        <v>367.4194075946342</v>
+        <v>364.0906519239622</v>
       </c>
       <c r="P3">
-        <v>1469.677630378537</v>
+        <v>1456.362607695849</v>
       </c>
       <c r="Q3">
-        <v>2922.977630378537</v>
+        <v>2909.662607695849</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09788686780423234</v>
+        <v>0.098312918827129</v>
       </c>
       <c r="T3">
-        <v>0.8057672793224576</v>
+        <v>0.8123581531462067</v>
       </c>
       <c r="U3">
         <v>0.06613097776675758</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>111.377403433898</v>
+        <v>55.68870171694899</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09740475609485454</v>
+        <v>0.09737246524138501</v>
       </c>
       <c r="C4">
-        <v>25237.84580115955</v>
+        <v>24996.31209192724</v>
       </c>
       <c r="D4">
-        <v>23112.20380115955</v>
+        <v>23122.34909192724</v>
       </c>
       <c r="E4">
-        <v>-7661.942000000001</v>
+        <v>-7410.263000000001</v>
       </c>
       <c r="F4">
-        <v>503.3580000000001</v>
+        <v>755.037</v>
       </c>
       <c r="G4">
         <v>2629</v>
@@ -1615,28 +1615,28 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M4">
-        <v>33.28755670671956</v>
+        <v>49.93133506007935</v>
       </c>
       <c r="N4">
-        <v>1820.453259619811</v>
+        <v>1803.809481266451</v>
       </c>
       <c r="O4">
-        <v>364.0906519239622</v>
+        <v>360.7618962532903</v>
       </c>
       <c r="P4">
-        <v>1456.362607695849</v>
+        <v>1443.047585013161</v>
       </c>
       <c r="Q4">
-        <v>2909.662607695849</v>
+        <v>2896.347585013161</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.098312918827129</v>
+        <v>0.0987477544071988</v>
       </c>
       <c r="T4">
-        <v>0.8123581531462067</v>
+        <v>0.8190849212756002</v>
       </c>
       <c r="U4">
         <v>0.06613097776675758</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>55.68870171694899</v>
+        <v>37.12580114463266</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09737246524138501</v>
+        <v>0.09734017438791548</v>
       </c>
       <c r="C5">
-        <v>24996.31209192724</v>
+        <v>24754.78729332293</v>
       </c>
       <c r="D5">
-        <v>23122.34909192724</v>
+        <v>23132.50329332293</v>
       </c>
       <c r="E5">
-        <v>-7410.263000000001</v>
+        <v>-7158.584000000001</v>
       </c>
       <c r="F5">
-        <v>755.037</v>
+        <v>1006.716</v>
       </c>
       <c r="G5">
         <v>2629</v>
@@ -1697,28 +1697,28 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M5">
-        <v>49.93133506007935</v>
+        <v>66.57511341343913</v>
       </c>
       <c r="N5">
-        <v>1803.809481266451</v>
+        <v>1787.165702913092</v>
       </c>
       <c r="O5">
-        <v>360.7618962532903</v>
+        <v>357.4331405826183</v>
       </c>
       <c r="P5">
-        <v>1443.047585013161</v>
+        <v>1429.732562330473</v>
       </c>
       <c r="Q5">
-        <v>2896.347585013161</v>
+        <v>2883.032562330473</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.0987477544071988</v>
+        <v>0.09919164906185338</v>
       </c>
       <c r="T5">
-        <v>0.8190849212756002</v>
+        <v>0.8259518304076895</v>
       </c>
       <c r="U5">
         <v>0.06613097776675758</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>37.12580114463266</v>
+        <v>27.8443508584745</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09734017438791548</v>
+        <v>0.09730788353444596</v>
       </c>
       <c r="C6">
-        <v>24754.78729332293</v>
+        <v>24513.27141709112</v>
       </c>
       <c r="D6">
-        <v>23132.50329332293</v>
+        <v>23142.66641709112</v>
       </c>
       <c r="E6">
-        <v>-7158.584000000001</v>
+        <v>-6906.905000000001</v>
       </c>
       <c r="F6">
-        <v>1006.716</v>
+        <v>1258.395</v>
       </c>
       <c r="G6">
         <v>2629</v>
@@ -1779,28 +1779,28 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M6">
-        <v>66.57511341343913</v>
+        <v>83.21889176679892</v>
       </c>
       <c r="N6">
-        <v>1787.165702913092</v>
+        <v>1770.521924559732</v>
       </c>
       <c r="O6">
-        <v>357.4331405826183</v>
+        <v>354.1043849119464</v>
       </c>
       <c r="P6">
-        <v>1429.732562330473</v>
+        <v>1416.417539647785</v>
       </c>
       <c r="Q6">
-        <v>2883.032562330473</v>
+        <v>2869.717539647785</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09919164906185338</v>
+        <v>0.09964488886713227</v>
       </c>
       <c r="T6">
-        <v>0.8259518304076895</v>
+        <v>0.8329633060478225</v>
       </c>
       <c r="U6">
         <v>0.06613097776675758</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>27.8443508584745</v>
+        <v>22.27548068677959</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09730788353444596</v>
+        <v>0.09727559268097644</v>
       </c>
       <c r="C7">
-        <v>24513.27141709112</v>
+        <v>24271.76447499694</v>
       </c>
       <c r="D7">
-        <v>23142.66641709112</v>
+        <v>23152.83847499694</v>
       </c>
       <c r="E7">
-        <v>-6906.905000000001</v>
+        <v>-6655.226000000001</v>
       </c>
       <c r="F7">
-        <v>1258.395</v>
+        <v>1510.074</v>
       </c>
       <c r="G7">
         <v>2629</v>
@@ -1861,28 +1861,28 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M7">
-        <v>83.21889176679892</v>
+        <v>99.86267012015871</v>
       </c>
       <c r="N7">
-        <v>1770.521924559732</v>
+        <v>1753.878146206372</v>
       </c>
       <c r="O7">
-        <v>354.1043849119464</v>
+        <v>350.7756292412744</v>
       </c>
       <c r="P7">
-        <v>1416.417539647785</v>
+        <v>1403.102516965097</v>
       </c>
       <c r="Q7">
-        <v>2869.717539647785</v>
+        <v>2856.402516965098</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09964488886713227</v>
+        <v>0.1001077720725235</v>
       </c>
       <c r="T7">
-        <v>0.8329633060478225</v>
+        <v>0.8401239620207247</v>
       </c>
       <c r="U7">
         <v>0.06613097776675758</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>22.27548068677959</v>
+        <v>18.56290057231633</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09727559268097644</v>
+        <v>0.09724330182750691</v>
       </c>
       <c r="C8">
-        <v>24271.76447499694</v>
+        <v>24030.26647882622</v>
       </c>
       <c r="D8">
-        <v>23152.83847499694</v>
+        <v>23163.01947882622</v>
       </c>
       <c r="E8">
-        <v>-6655.226000000001</v>
+        <v>-6403.547000000001</v>
       </c>
       <c r="F8">
-        <v>1510.074</v>
+        <v>1761.753</v>
       </c>
       <c r="G8">
         <v>2629</v>
@@ -1943,28 +1943,28 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M8">
-        <v>99.8626701201587</v>
+        <v>116.5064484735185</v>
       </c>
       <c r="N8">
-        <v>1753.878146206372</v>
+        <v>1737.234367853012</v>
       </c>
       <c r="O8">
-        <v>350.7756292412744</v>
+        <v>347.4468735706025</v>
       </c>
       <c r="P8">
-        <v>1403.102516965097</v>
+        <v>1389.78749428241</v>
       </c>
       <c r="Q8">
-        <v>2856.402516965098</v>
+        <v>2843.087494282409</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1001077720725235</v>
+        <v>0.10058060975545</v>
       </c>
       <c r="T8">
-        <v>0.8401239620207247</v>
+        <v>0.8474386105951944</v>
       </c>
       <c r="U8">
         <v>0.06613097776675758</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>18.56290057231633</v>
+        <v>15.911057633414</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0972433018275069</v>
+        <v>0.09721101097403738</v>
       </c>
       <c r="C9">
-        <v>24030.26647882622</v>
+        <v>23788.77744038554</v>
       </c>
       <c r="D9">
-        <v>23163.01947882622</v>
+        <v>23173.20944038554</v>
       </c>
       <c r="E9">
-        <v>-6403.547</v>
+        <v>-6151.868</v>
       </c>
       <c r="F9">
-        <v>1761.753</v>
+        <v>2013.432</v>
       </c>
       <c r="G9">
         <v>2629</v>
@@ -2025,28 +2025,28 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M9">
-        <v>116.5064484735185</v>
+        <v>133.1502268268783</v>
       </c>
       <c r="N9">
-        <v>1737.234367853012</v>
+        <v>1720.590589499652</v>
       </c>
       <c r="O9">
-        <v>347.4468735706025</v>
+        <v>344.1181178999305</v>
       </c>
       <c r="P9">
-        <v>1389.78749428241</v>
+        <v>1376.472471599722</v>
       </c>
       <c r="Q9">
-        <v>2843.087494282409</v>
+        <v>2829.772471599722</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.10058060975545</v>
+        <v>0.1010637265184401</v>
       </c>
       <c r="T9">
-        <v>0.8474386105951944</v>
+        <v>0.8549122732691091</v>
       </c>
       <c r="U9">
         <v>0.06613097776675758</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>15.911057633414</v>
+        <v>13.92217542923725</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09721101097403738</v>
+        <v>0.09717872012056784</v>
       </c>
       <c r="C10">
-        <v>23788.77744038554</v>
+        <v>23547.29737150225</v>
       </c>
       <c r="D10">
-        <v>23173.20944038554</v>
+        <v>23183.40837150225</v>
       </c>
       <c r="E10">
-        <v>-6151.868</v>
+        <v>-5900.189000000001</v>
       </c>
       <c r="F10">
-        <v>2013.432</v>
+        <v>2265.111</v>
       </c>
       <c r="G10">
         <v>2629</v>
@@ -2107,28 +2107,28 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M10">
-        <v>133.1502268268783</v>
+        <v>149.794005180238</v>
       </c>
       <c r="N10">
-        <v>1720.590589499652</v>
+        <v>1703.946811146293</v>
       </c>
       <c r="O10">
-        <v>344.1181178999305</v>
+        <v>340.7893622292586</v>
       </c>
       <c r="P10">
-        <v>1376.472471599722</v>
+        <v>1363.157448917034</v>
       </c>
       <c r="Q10">
-        <v>2829.772471599722</v>
+        <v>2816.457448917034</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1010637265184401</v>
+        <v>0.1015574612322652</v>
       </c>
       <c r="T10">
-        <v>0.8549122732691091</v>
+        <v>0.8625501922655274</v>
       </c>
       <c r="U10">
         <v>0.06613097776675758</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>13.92217542923725</v>
+        <v>12.37526704821089</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09717872012056784</v>
+        <v>0.09714642926709832</v>
       </c>
       <c r="C11">
-        <v>23547.29737150225</v>
+        <v>23305.82628402455</v>
       </c>
       <c r="D11">
-        <v>23183.40837150225</v>
+        <v>23193.61628402455</v>
       </c>
       <c r="E11">
-        <v>-5900.189000000001</v>
+        <v>-5648.510000000001</v>
       </c>
       <c r="F11">
-        <v>2265.111</v>
+        <v>2516.79</v>
       </c>
       <c r="G11">
         <v>2629</v>
@@ -2189,28 +2189,28 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M11">
-        <v>149.794005180238</v>
+        <v>166.4377835335978</v>
       </c>
       <c r="N11">
-        <v>1703.946811146293</v>
+        <v>1687.303032792933</v>
       </c>
       <c r="O11">
-        <v>340.7893622292586</v>
+        <v>337.4606065585866</v>
       </c>
       <c r="P11">
-        <v>1363.157448917034</v>
+        <v>1349.842426234346</v>
       </c>
       <c r="Q11">
-        <v>2816.457448917034</v>
+        <v>2803.142426234346</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1015574612322652</v>
+        <v>0.1020621678286197</v>
       </c>
       <c r="T11">
-        <v>0.8625501922655274</v>
+        <v>0.8703578427951996</v>
       </c>
       <c r="U11">
         <v>0.06613097776675758</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>12.37526704821089</v>
+        <v>11.1377403433898</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09714642926709832</v>
+        <v>0.09711413841362881</v>
       </c>
       <c r="C12">
-        <v>23305.82628402455</v>
+        <v>23064.36418982148</v>
       </c>
       <c r="D12">
-        <v>23193.61628402455</v>
+        <v>23203.83318982148</v>
       </c>
       <c r="E12">
-        <v>-5648.51</v>
+        <v>-5396.831000000001</v>
       </c>
       <c r="F12">
-        <v>2516.79</v>
+        <v>2768.469</v>
       </c>
       <c r="G12">
         <v>2629</v>
@@ -2271,28 +2271,28 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M12">
-        <v>166.4377835335978</v>
+        <v>183.0815618869576</v>
       </c>
       <c r="N12">
-        <v>1687.303032792933</v>
+        <v>1670.659254439573</v>
       </c>
       <c r="O12">
-        <v>337.4606065585866</v>
+        <v>334.1318508879147</v>
       </c>
       <c r="P12">
-        <v>1349.842426234346</v>
+        <v>1336.527403551658</v>
       </c>
       <c r="Q12">
-        <v>2803.142426234346</v>
+        <v>2789.827403551658</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1020621678286197</v>
+        <v>0.1025782161462406</v>
       </c>
       <c r="T12">
-        <v>0.8703578427951998</v>
+        <v>0.8783409461457632</v>
       </c>
       <c r="U12">
         <v>0.06613097776675758</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.1377403433898</v>
+        <v>10.12521849399073</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09711413841362881</v>
+        <v>0.09708184756015928</v>
       </c>
       <c r="C13">
-        <v>23064.36418982148</v>
+        <v>22822.91110078305</v>
       </c>
       <c r="D13">
-        <v>23203.83318982148</v>
+        <v>23214.05910078305</v>
       </c>
       <c r="E13">
-        <v>-5396.831000000001</v>
+        <v>-5145.152000000001</v>
       </c>
       <c r="F13">
-        <v>2768.469</v>
+        <v>3020.148</v>
       </c>
       <c r="G13">
         <v>2629</v>
@@ -2353,28 +2353,28 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M13">
-        <v>183.0815618869576</v>
+        <v>199.7253402403174</v>
       </c>
       <c r="N13">
-        <v>1670.659254439573</v>
+        <v>1654.015476086213</v>
       </c>
       <c r="O13">
-        <v>334.1318508879147</v>
+        <v>330.8030952172427</v>
       </c>
       <c r="P13">
-        <v>1336.527403551658</v>
+        <v>1323.212380868971</v>
       </c>
       <c r="Q13">
-        <v>2789.827403551658</v>
+        <v>2776.51238086897</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1025782161462406</v>
+        <v>0.1031059928347165</v>
       </c>
       <c r="T13">
-        <v>0.8783409461457632</v>
+        <v>0.8865054836633852</v>
       </c>
       <c r="U13">
         <v>0.06613097776675758</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>10.12521849399073</v>
+        <v>9.281450286158165</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09708184756015928</v>
+        <v>0.09720555670668973</v>
       </c>
       <c r="C14">
-        <v>22822.91110078305</v>
+        <v>22532.10451803639</v>
       </c>
       <c r="D14">
-        <v>23214.05910078305</v>
+        <v>23174.9315180364</v>
       </c>
       <c r="E14">
-        <v>-5145.152000000001</v>
+        <v>-4893.473000000001</v>
       </c>
       <c r="F14">
-        <v>3020.148</v>
+        <v>3271.827</v>
       </c>
       <c r="G14">
         <v>2629</v>
@@ -2435,45 +2435,45 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M14">
-        <v>199.7253402403174</v>
+        <v>221.2768590936772</v>
       </c>
       <c r="N14">
-        <v>1654.015476086213</v>
+        <v>1632.463957232854</v>
       </c>
       <c r="O14">
-        <v>330.8030952172427</v>
+        <v>326.4927914465707</v>
       </c>
       <c r="P14">
-        <v>1323.212380868971</v>
+        <v>1305.971165786283</v>
       </c>
       <c r="Q14">
-        <v>2776.51238086897</v>
+        <v>2759.271165786283</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1031059928347165</v>
+        <v>0.1036459023206287</v>
       </c>
       <c r="T14">
-        <v>0.8865054836633852</v>
+        <v>0.8948577116986535</v>
       </c>
       <c r="U14">
-        <v>0.06613097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V14">
         <v>0.2</v>
       </c>
       <c r="W14">
-        <v>0.05290478221340607</v>
+        <v>0.05410478221340607</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y14">
-        <v>9.281450286158165</v>
+        <v>8.377472564999454</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09720555670668973</v>
+        <v>0.09718526585322024</v>
       </c>
       <c r="C15">
-        <v>22532.10451803639</v>
+        <v>22286.83420379862</v>
       </c>
       <c r="D15">
-        <v>23174.9315180364</v>
+        <v>23181.34020379862</v>
       </c>
       <c r="E15">
-        <v>-4893.473000000001</v>
+        <v>-4641.794000000001</v>
       </c>
       <c r="F15">
-        <v>3271.827</v>
+        <v>3523.506</v>
       </c>
       <c r="G15">
         <v>2629</v>
@@ -2517,28 +2517,28 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M15">
-        <v>221.2768590936772</v>
+        <v>238.298155947037</v>
       </c>
       <c r="N15">
-        <v>1632.463957232854</v>
+        <v>1615.442660379494</v>
       </c>
       <c r="O15">
-        <v>326.4927914465707</v>
+        <v>323.0885320758987</v>
       </c>
       <c r="P15">
-        <v>1305.971165786283</v>
+        <v>1292.354128303595</v>
       </c>
       <c r="Q15">
-        <v>2759.271165786283</v>
+        <v>2745.654128303595</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1036459023206287</v>
+        <v>0.104198367841097</v>
       </c>
       <c r="T15">
-        <v>0.8948577116986535</v>
+        <v>0.9034041775952073</v>
       </c>
       <c r="U15">
         <v>0.06763097776675758</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>8.377472564999454</v>
+        <v>7.779081667499493</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09718526585322024</v>
+        <v>0.0971649749997507</v>
       </c>
       <c r="C16">
-        <v>22286.83420379862</v>
+        <v>22041.5674349965</v>
       </c>
       <c r="D16">
-        <v>23181.34020379862</v>
+        <v>23187.7524349965</v>
       </c>
       <c r="E16">
-        <v>-4641.794000000001</v>
+        <v>-4390.115</v>
       </c>
       <c r="F16">
-        <v>3523.506</v>
+        <v>3775.185000000001</v>
       </c>
       <c r="G16">
         <v>2629</v>
@@ -2599,28 +2599,28 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M16">
-        <v>238.298155947037</v>
+        <v>255.3194528003968</v>
       </c>
       <c r="N16">
-        <v>1615.442660379494</v>
+        <v>1598.421363526134</v>
       </c>
       <c r="O16">
-        <v>323.0885320758987</v>
+        <v>319.6842727052268</v>
       </c>
       <c r="P16">
-        <v>1292.354128303595</v>
+        <v>1278.737090820907</v>
       </c>
       <c r="Q16">
-        <v>2745.654128303595</v>
+        <v>2732.037090820907</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.104198367841097</v>
+        <v>0.1047638325502821</v>
       </c>
       <c r="T16">
-        <v>0.9034041775952073</v>
+        <v>0.9121517368069739</v>
       </c>
       <c r="U16">
         <v>0.06763097776675758</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>7.779081667499493</v>
+        <v>7.260476222999526</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0971649749997507</v>
+        <v>0.09714468414628116</v>
       </c>
       <c r="C17">
-        <v>22041.5674349965</v>
+        <v>21796.30421457295</v>
       </c>
       <c r="D17">
-        <v>23187.7524349965</v>
+        <v>23194.16821457295</v>
       </c>
       <c r="E17">
-        <v>-4390.115000000002</v>
+        <v>-4138.436000000001</v>
       </c>
       <c r="F17">
-        <v>3775.185</v>
+        <v>4026.864</v>
       </c>
       <c r="G17">
         <v>2629</v>
@@ -2681,28 +2681,28 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M17">
-        <v>255.3194528003967</v>
+        <v>272.3407496537565</v>
       </c>
       <c r="N17">
-        <v>1598.421363526134</v>
+        <v>1581.400066672774</v>
       </c>
       <c r="O17">
-        <v>319.6842727052268</v>
+        <v>316.2800133345548</v>
       </c>
       <c r="P17">
-        <v>1278.737090820907</v>
+        <v>1265.120053338219</v>
       </c>
       <c r="Q17">
-        <v>2732.037090820907</v>
+        <v>2718.420053338219</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1047638325502821</v>
+        <v>0.105342760704924</v>
       </c>
       <c r="T17">
-        <v>0.9121517368069739</v>
+        <v>0.9211075712380683</v>
       </c>
       <c r="U17">
         <v>0.06763097776675758</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>7.260476222999528</v>
+        <v>6.806696459062057</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09714468414628116</v>
+        <v>0.09735559329281164</v>
       </c>
       <c r="C18">
-        <v>21796.30421457295</v>
+        <v>21478.11054280756</v>
       </c>
       <c r="D18">
-        <v>23194.16821457295</v>
+        <v>23127.65354280756</v>
       </c>
       <c r="E18">
-        <v>-4138.436000000001</v>
+        <v>-3886.757000000001</v>
       </c>
       <c r="F18">
-        <v>4026.864</v>
+        <v>4278.543000000001</v>
       </c>
       <c r="G18">
         <v>2629</v>
@@ -2763,45 +2763,45 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M18">
-        <v>272.3407496537565</v>
+        <v>296.6355696071163</v>
       </c>
       <c r="N18">
-        <v>1581.400066672774</v>
+        <v>1557.105246719414</v>
       </c>
       <c r="O18">
-        <v>316.2800133345548</v>
+        <v>311.4210493438829</v>
       </c>
       <c r="P18">
-        <v>1265.120053338219</v>
+        <v>1245.684197375532</v>
       </c>
       <c r="Q18">
-        <v>2718.420053338219</v>
+        <v>2698.984197375531</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.105342760704924</v>
+        <v>0.1059356389355815</v>
       </c>
       <c r="T18">
-        <v>0.9211075712380683</v>
+        <v>0.9302792089084664</v>
       </c>
       <c r="U18">
-        <v>0.06763097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V18">
         <v>0.2</v>
       </c>
       <c r="W18">
-        <v>0.05410478221340607</v>
+        <v>0.05546478221340606</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y18">
-        <v>6.806696459062057</v>
+        <v>6.249219602294315</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09735559329281164</v>
+        <v>0.09734890243934212</v>
       </c>
       <c r="C19">
-        <v>21478.11054280756</v>
+        <v>21228.53578555614</v>
       </c>
       <c r="D19">
-        <v>23127.65354280756</v>
+        <v>23129.75778555614</v>
       </c>
       <c r="E19">
-        <v>-3886.757000000001</v>
+        <v>-3635.078</v>
       </c>
       <c r="F19">
-        <v>4278.543000000001</v>
+        <v>4530.222000000001</v>
       </c>
       <c r="G19">
         <v>2629</v>
@@ -2845,28 +2845,28 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M19">
-        <v>296.6355696071163</v>
+        <v>314.0847207604761</v>
       </c>
       <c r="N19">
-        <v>1557.105246719414</v>
+        <v>1539.656095566055</v>
       </c>
       <c r="O19">
-        <v>311.4210493438829</v>
+        <v>307.9312191132109</v>
       </c>
       <c r="P19">
-        <v>1245.684197375532</v>
+        <v>1231.724876452844</v>
       </c>
       <c r="Q19">
-        <v>2698.984197375531</v>
+        <v>2685.024876452843</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1059356389355815</v>
+        <v>0.1065429776108891</v>
       </c>
       <c r="T19">
-        <v>0.9302792089084664</v>
+        <v>0.9396745450586302</v>
       </c>
       <c r="U19">
         <v>0.06933097776675758</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>6.249219602294315</v>
+        <v>5.902040735500185</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09734890243934212</v>
+        <v>0.0973422115858726</v>
       </c>
       <c r="C20">
-        <v>21228.53578555615</v>
+        <v>20978.96141124373</v>
       </c>
       <c r="D20">
-        <v>23129.75778555614</v>
+        <v>23131.86241124373</v>
       </c>
       <c r="E20">
-        <v>-3635.078000000001</v>
+        <v>-3383.399</v>
       </c>
       <c r="F20">
-        <v>4530.222</v>
+        <v>4781.901000000001</v>
       </c>
       <c r="G20">
         <v>2629</v>
@@ -2927,28 +2927,28 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M20">
-        <v>314.084720760476</v>
+        <v>331.5338719138359</v>
       </c>
       <c r="N20">
-        <v>1539.656095566055</v>
+        <v>1522.206944412695</v>
       </c>
       <c r="O20">
-        <v>307.9312191132109</v>
+        <v>304.441388882539</v>
       </c>
       <c r="P20">
-        <v>1231.724876452844</v>
+        <v>1217.765555530156</v>
       </c>
       <c r="Q20">
-        <v>2685.024876452843</v>
+        <v>2671.065555530156</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.106542977610889</v>
+        <v>0.1071653123028709</v>
       </c>
       <c r="T20">
-        <v>0.9396745450586301</v>
+        <v>0.9493018648174401</v>
       </c>
       <c r="U20">
         <v>0.06933097776675758</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.902040735500186</v>
+        <v>5.591407012579123</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.0973422115858726</v>
+        <v>0.09746352073240307</v>
       </c>
       <c r="C21">
-        <v>20978.96141124373</v>
+        <v>20689.18367872932</v>
       </c>
       <c r="D21">
-        <v>23131.86241124373</v>
+        <v>23093.76367872932</v>
       </c>
       <c r="E21">
-        <v>-3383.399</v>
+        <v>-3131.72</v>
       </c>
       <c r="F21">
-        <v>4781.901000000001</v>
+        <v>5033.580000000001</v>
       </c>
       <c r="G21">
         <v>2629</v>
@@ -3009,45 +3009,45 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M21">
-        <v>331.5338719138359</v>
+        <v>353.0098870671957</v>
       </c>
       <c r="N21">
-        <v>1522.206944412695</v>
+        <v>1500.730929259335</v>
       </c>
       <c r="O21">
-        <v>304.441388882539</v>
+        <v>300.146185851867</v>
       </c>
       <c r="P21">
-        <v>1217.765555530156</v>
+        <v>1200.584743407468</v>
       </c>
       <c r="Q21">
-        <v>2671.065555530156</v>
+        <v>2653.884743407468</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1071653123028709</v>
+        <v>0.1078032053621523</v>
       </c>
       <c r="T21">
-        <v>0.9493018648174401</v>
+        <v>0.9591698675702199</v>
       </c>
       <c r="U21">
-        <v>0.06933097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V21">
         <v>0.2</v>
       </c>
       <c r="W21">
-        <v>0.05546478221340606</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y21">
-        <v>5.591407012579123</v>
+        <v>5.251243334081659</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09746352073240307</v>
+        <v>0.09746322987893354</v>
       </c>
       <c r="C22">
-        <v>20689.18367872932</v>
+        <v>20437.59587499623</v>
       </c>
       <c r="D22">
-        <v>23093.76367872932</v>
+        <v>23093.85487499624</v>
       </c>
       <c r="E22">
-        <v>-3131.72</v>
+        <v>-2880.041</v>
       </c>
       <c r="F22">
-        <v>5033.580000000001</v>
+        <v>5285.259000000001</v>
       </c>
       <c r="G22">
         <v>2629</v>
@@ -3091,28 +3091,28 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M22">
-        <v>353.0098870671957</v>
+        <v>370.6603814205555</v>
       </c>
       <c r="N22">
-        <v>1500.730929259335</v>
+        <v>1483.080434905975</v>
       </c>
       <c r="O22">
-        <v>300.146185851867</v>
+        <v>296.6160869811951</v>
       </c>
       <c r="P22">
-        <v>1200.584743407468</v>
+        <v>1186.46434792478</v>
       </c>
       <c r="Q22">
-        <v>2653.884743407468</v>
+        <v>2639.76434792478</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1078032053621523</v>
+        <v>0.1084572476128079</v>
       </c>
       <c r="T22">
-        <v>0.9591698675702199</v>
+        <v>0.9692876931775009</v>
       </c>
       <c r="U22">
         <v>0.07013097776675759</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.251243334081659</v>
+        <v>5.001184127696818</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09746322987893354</v>
+        <v>0.097462939025464</v>
       </c>
       <c r="C23">
-        <v>20437.59587499624</v>
+        <v>20186.00807198341</v>
       </c>
       <c r="D23">
-        <v>23093.85487499624</v>
+        <v>23093.94607198341</v>
       </c>
       <c r="E23">
-        <v>-2880.041000000001</v>
+        <v>-2628.362000000001</v>
       </c>
       <c r="F23">
-        <v>5285.259</v>
+        <v>5536.938</v>
       </c>
       <c r="G23">
         <v>2629</v>
@@ -3173,28 +3173,28 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M23">
-        <v>370.6603814205554</v>
+        <v>388.3108757739152</v>
       </c>
       <c r="N23">
-        <v>1483.080434905975</v>
+        <v>1465.429940552615</v>
       </c>
       <c r="O23">
-        <v>296.6160869811951</v>
+        <v>293.0859881105231</v>
       </c>
       <c r="P23">
-        <v>1186.46434792478</v>
+        <v>1172.343952442092</v>
       </c>
       <c r="Q23">
-        <v>2639.76434792478</v>
+        <v>2625.643952442092</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1084572476128079</v>
+        <v>0.1091280601775829</v>
       </c>
       <c r="T23">
-        <v>0.9692876931775009</v>
+        <v>0.9796649502106094</v>
       </c>
       <c r="U23">
         <v>0.07013097776675759</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.001184127696819</v>
+        <v>4.773857576437873</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.097462939025464</v>
+        <v>0.09746264817199449</v>
       </c>
       <c r="C24">
-        <v>20186.00807198341</v>
+        <v>19934.42026969085</v>
       </c>
       <c r="D24">
-        <v>23093.94607198341</v>
+        <v>23094.03726969085</v>
       </c>
       <c r="E24">
-        <v>-2628.362000000001</v>
+        <v>-2376.683000000001</v>
       </c>
       <c r="F24">
-        <v>5536.938</v>
+        <v>5788.617</v>
       </c>
       <c r="G24">
         <v>2629</v>
@@ -3255,28 +3255,28 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M24">
-        <v>388.3108757739152</v>
+        <v>405.961370127275</v>
       </c>
       <c r="N24">
-        <v>1465.429940552615</v>
+        <v>1447.779446199256</v>
       </c>
       <c r="O24">
-        <v>293.0859881105231</v>
+        <v>289.5558892398512</v>
       </c>
       <c r="P24">
-        <v>1172.343952442092</v>
+        <v>1158.223556959405</v>
       </c>
       <c r="Q24">
-        <v>2625.643952442092</v>
+        <v>2611.523556959404</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1091280601775829</v>
+        <v>0.1098162964453391</v>
       </c>
       <c r="T24">
-        <v>0.9796649502106094</v>
+        <v>0.990311746387435</v>
       </c>
       <c r="U24">
         <v>0.07013097776675759</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.773857576437873</v>
+        <v>4.566298551375356</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09746264817199449</v>
+        <v>0.09746235731852496</v>
       </c>
       <c r="C25">
-        <v>19934.42026969085</v>
+        <v>19682.83246811858</v>
       </c>
       <c r="D25">
-        <v>23094.03726969085</v>
+        <v>23094.12846811858</v>
       </c>
       <c r="E25">
-        <v>-2376.683000000001</v>
+        <v>-2125.004</v>
       </c>
       <c r="F25">
-        <v>5788.617</v>
+        <v>6040.296000000001</v>
       </c>
       <c r="G25">
         <v>2629</v>
@@ -3337,28 +3337,28 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M25">
-        <v>405.961370127275</v>
+        <v>423.6118644806348</v>
       </c>
       <c r="N25">
-        <v>1447.779446199256</v>
+        <v>1430.128951845896</v>
       </c>
       <c r="O25">
-        <v>289.5558892398512</v>
+        <v>286.0257903691792</v>
       </c>
       <c r="P25">
-        <v>1158.223556959405</v>
+        <v>1144.103161476717</v>
       </c>
       <c r="Q25">
-        <v>2611.523556959404</v>
+        <v>2597.403161476716</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1098162964453391</v>
+        <v>0.1105226441938257</v>
       </c>
       <c r="T25">
-        <v>0.990311746387435</v>
+        <v>1.001238721411019</v>
       </c>
       <c r="U25">
         <v>0.07013097776675759</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.566298551375356</v>
+        <v>4.376036111734716</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09746235731852496</v>
+        <v>0.09766206646505543</v>
       </c>
       <c r="C26">
-        <v>19682.83246811858</v>
+        <v>19368.70284544978</v>
       </c>
       <c r="D26">
-        <v>23094.12846811858</v>
+        <v>23031.67784544978</v>
       </c>
       <c r="E26">
-        <v>-2125.004000000001</v>
+        <v>-1873.325000000001</v>
       </c>
       <c r="F26">
-        <v>6040.296</v>
+        <v>6291.975</v>
       </c>
       <c r="G26">
         <v>2629</v>
@@ -3419,45 +3419,45 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M26">
-        <v>423.6118644806348</v>
+        <v>447.5543338339946</v>
       </c>
       <c r="N26">
-        <v>1430.128951845896</v>
+        <v>1406.186482492536</v>
       </c>
       <c r="O26">
-        <v>286.0257903691792</v>
+        <v>281.2372964985072</v>
       </c>
       <c r="P26">
-        <v>1144.103161476717</v>
+        <v>1124.949185994029</v>
       </c>
       <c r="Q26">
-        <v>2597.403161476716</v>
+        <v>2578.249185994029</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1105226441938257</v>
+        <v>0.1112478278822719</v>
       </c>
       <c r="T26">
-        <v>1.001238721411019</v>
+        <v>1.012457082435232</v>
       </c>
       <c r="U26">
-        <v>0.07013097776675759</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V26">
         <v>0.2</v>
       </c>
       <c r="W26">
-        <v>0.05610478221340607</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y26">
-        <v>4.376036111734717</v>
+        <v>4.141934679631802</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09766206646505543</v>
+        <v>0.09766977561158591</v>
       </c>
       <c r="C27">
-        <v>19368.70284544978</v>
+        <v>19114.61990455487</v>
       </c>
       <c r="D27">
-        <v>23031.67784544978</v>
+        <v>23029.27390455487</v>
       </c>
       <c r="E27">
-        <v>-1873.325000000001</v>
+        <v>-1621.646000000001</v>
       </c>
       <c r="F27">
-        <v>6291.975</v>
+        <v>6543.654</v>
       </c>
       <c r="G27">
         <v>2629</v>
@@ -3501,28 +3501,28 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M27">
-        <v>447.5543338339946</v>
+        <v>465.4565071873544</v>
       </c>
       <c r="N27">
-        <v>1406.186482492536</v>
+        <v>1388.284309139176</v>
       </c>
       <c r="O27">
-        <v>281.2372964985072</v>
+        <v>277.6568618278353</v>
       </c>
       <c r="P27">
-        <v>1124.949185994029</v>
+        <v>1110.627447311341</v>
       </c>
       <c r="Q27">
-        <v>2578.249185994029</v>
+        <v>2563.927447311341</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1112478278822719</v>
+        <v>0.1119926111298653</v>
       </c>
       <c r="T27">
-        <v>1.012457082435232</v>
+        <v>1.023978642406046</v>
       </c>
       <c r="U27">
         <v>0.07113097776675759</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.141934679631802</v>
+        <v>3.982629499645963</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09766977561158591</v>
+        <v>0.09767748475811637</v>
       </c>
       <c r="C28">
-        <v>19114.61990455487</v>
+        <v>18860.53746543224</v>
       </c>
       <c r="D28">
-        <v>23029.27390455487</v>
+        <v>23026.87046543224</v>
       </c>
       <c r="E28">
-        <v>-1621.646000000001</v>
+        <v>-1369.967000000001</v>
       </c>
       <c r="F28">
-        <v>6543.654</v>
+        <v>6795.333000000001</v>
       </c>
       <c r="G28">
         <v>2629</v>
@@ -3583,28 +3583,28 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M28">
-        <v>465.4565071873544</v>
+        <v>483.3586805407141</v>
       </c>
       <c r="N28">
-        <v>1388.284309139176</v>
+        <v>1370.382135785816</v>
       </c>
       <c r="O28">
-        <v>277.6568618278353</v>
+        <v>274.0764271571633</v>
       </c>
       <c r="P28">
-        <v>1110.627447311341</v>
+        <v>1096.305708628653</v>
       </c>
       <c r="Q28">
-        <v>2563.927447311341</v>
+        <v>2549.605708628653</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1119926111298653</v>
+        <v>0.1127577993979407</v>
       </c>
       <c r="T28">
-        <v>1.023978642406046</v>
+        <v>1.035815861554142</v>
       </c>
       <c r="U28">
         <v>0.07113097776675759</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.982629499645963</v>
+        <v>3.835124703362779</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09767748475811637</v>
+        <v>0.09768519390464685</v>
       </c>
       <c r="C29">
-        <v>18860.53746543224</v>
+        <v>18606.4555279248</v>
       </c>
       <c r="D29">
-        <v>23026.87046543224</v>
+        <v>23024.4675279248</v>
       </c>
       <c r="E29">
-        <v>-1369.967000000001</v>
+        <v>-1118.288</v>
       </c>
       <c r="F29">
-        <v>6795.333000000001</v>
+        <v>7047.012000000001</v>
       </c>
       <c r="G29">
         <v>2629</v>
@@ -3665,28 +3665,28 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M29">
-        <v>483.3586805407141</v>
+        <v>501.2608538940739</v>
       </c>
       <c r="N29">
-        <v>1370.382135785816</v>
+        <v>1352.479962432457</v>
       </c>
       <c r="O29">
-        <v>274.0764271571633</v>
+        <v>270.4959924864913</v>
       </c>
       <c r="P29">
-        <v>1096.305708628653</v>
+        <v>1081.983969945965</v>
       </c>
       <c r="Q29">
-        <v>2549.605708628653</v>
+        <v>2535.283969945966</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1127577993979407</v>
+        <v>0.1135442428956849</v>
       </c>
       <c r="T29">
-        <v>1.035815861554142</v>
+        <v>1.04798189234524</v>
       </c>
       <c r="U29">
         <v>0.07113097776675759</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.835124703362779</v>
+        <v>3.698155963956965</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09768519390464685</v>
+        <v>0.09769290305117732</v>
       </c>
       <c r="C30">
-        <v>18606.4555279248</v>
+        <v>18352.37409187553</v>
       </c>
       <c r="D30">
-        <v>23024.4675279248</v>
+        <v>23022.06509187553</v>
       </c>
       <c r="E30">
-        <v>-1118.288</v>
+        <v>-866.6089999999995</v>
       </c>
       <c r="F30">
-        <v>7047.012000000001</v>
+        <v>7298.691000000002</v>
       </c>
       <c r="G30">
         <v>2629</v>
@@ -3747,28 +3747,28 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M30">
-        <v>501.2608538940739</v>
+        <v>519.1630272474338</v>
       </c>
       <c r="N30">
-        <v>1352.479962432457</v>
+        <v>1334.577789079097</v>
       </c>
       <c r="O30">
-        <v>270.4959924864913</v>
+        <v>266.9155578158194</v>
       </c>
       <c r="P30">
-        <v>1081.983969945965</v>
+        <v>1067.662231263278</v>
       </c>
       <c r="Q30">
-        <v>2535.283969945966</v>
+        <v>2520.962231263277</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1135442428956849</v>
+        <v>0.1143528397313938</v>
       </c>
       <c r="T30">
-        <v>1.04798189234524</v>
+        <v>1.060490628229046</v>
       </c>
       <c r="U30">
         <v>0.07113097776675759</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.698155963956965</v>
+        <v>3.570633344510173</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09769290305117732</v>
+        <v>0.0977006121977078</v>
       </c>
       <c r="C31">
-        <v>18352.37409187553</v>
+        <v>18098.29315712748</v>
       </c>
       <c r="D31">
-        <v>23022.06509187553</v>
+        <v>23019.66315712748</v>
       </c>
       <c r="E31">
-        <v>-866.6090000000013</v>
+        <v>-614.9300000000012</v>
       </c>
       <c r="F31">
-        <v>7298.691</v>
+        <v>7550.37</v>
       </c>
       <c r="G31">
         <v>2629</v>
@@ -3829,28 +3829,28 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M31">
-        <v>519.1630272474337</v>
+        <v>537.0652006007934</v>
       </c>
       <c r="N31">
-        <v>1334.577789079097</v>
+        <v>1316.675615725737</v>
       </c>
       <c r="O31">
-        <v>266.9155578158194</v>
+        <v>263.3351231451475</v>
       </c>
       <c r="P31">
-        <v>1067.662231263278</v>
+        <v>1053.34049258059</v>
       </c>
       <c r="Q31">
-        <v>2520.962231263277</v>
+        <v>2506.64049258059</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1143528397313938</v>
+        <v>0.1151845393338371</v>
       </c>
       <c r="T31">
-        <v>1.060490628229046</v>
+        <v>1.073356756566675</v>
       </c>
       <c r="U31">
         <v>0.07113097776675759</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.570633344510174</v>
+        <v>3.451612233026502</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0977006121977078</v>
+        <v>0.09770832134423826</v>
       </c>
       <c r="C32">
-        <v>18098.29315712748</v>
+        <v>17844.21272352376</v>
       </c>
       <c r="D32">
-        <v>23019.66315712748</v>
+        <v>23017.26172352376</v>
       </c>
       <c r="E32">
-        <v>-614.9300000000012</v>
+        <v>-363.2510000000011</v>
       </c>
       <c r="F32">
-        <v>7550.37</v>
+        <v>7802.049</v>
       </c>
       <c r="G32">
         <v>2629</v>
@@ -3911,28 +3911,28 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M32">
-        <v>537.0652006007934</v>
+        <v>554.9673739541532</v>
       </c>
       <c r="N32">
-        <v>1316.675615725737</v>
+        <v>1298.773442372377</v>
       </c>
       <c r="O32">
-        <v>263.3351231451475</v>
+        <v>259.7546884744755</v>
       </c>
       <c r="P32">
-        <v>1053.34049258059</v>
+        <v>1039.018753897902</v>
       </c>
       <c r="Q32">
-        <v>2506.64049258059</v>
+        <v>2492.318753897902</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1151845393338371</v>
+        <v>0.1160403461711339</v>
       </c>
       <c r="T32">
-        <v>1.073356756566675</v>
+        <v>1.086595816160467</v>
       </c>
       <c r="U32">
         <v>0.07113097776675759</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.451612233026502</v>
+        <v>3.340269902928872</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09770832134423826</v>
+        <v>0.09771603049076874</v>
       </c>
       <c r="C33">
-        <v>17844.21272352376</v>
+        <v>17590.13279090754</v>
       </c>
       <c r="D33">
-        <v>23017.26172352376</v>
+        <v>23014.86079090754</v>
       </c>
       <c r="E33">
-        <v>-363.2510000000011</v>
+        <v>-111.5720000000001</v>
       </c>
       <c r="F33">
-        <v>7802.049</v>
+        <v>8053.728000000001</v>
       </c>
       <c r="G33">
         <v>2629</v>
@@ -3993,28 +3993,28 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M33">
-        <v>554.9673739541532</v>
+        <v>572.8695473075131</v>
       </c>
       <c r="N33">
-        <v>1298.773442372377</v>
+        <v>1280.871269019018</v>
       </c>
       <c r="O33">
-        <v>259.7546884744755</v>
+        <v>256.1742538038035</v>
       </c>
       <c r="P33">
-        <v>1039.018753897902</v>
+        <v>1024.697015215214</v>
       </c>
       <c r="Q33">
-        <v>2492.318753897902</v>
+        <v>2477.997015215214</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1160403461711339</v>
+        <v>0.116921323797763</v>
       </c>
       <c r="T33">
-        <v>1.086595816160467</v>
+        <v>1.100224259859958</v>
       </c>
       <c r="U33">
         <v>0.07113097776675759</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.340269902928872</v>
+        <v>3.235886468462344</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09771603049076874</v>
+        <v>0.09772373963729922</v>
       </c>
       <c r="C34">
-        <v>17590.13279090754</v>
+        <v>17336.05335912207</v>
       </c>
       <c r="D34">
-        <v>23014.86079090754</v>
+        <v>23012.46035912207</v>
       </c>
       <c r="E34">
-        <v>-111.5720000000001</v>
+        <v>140.107</v>
       </c>
       <c r="F34">
-        <v>8053.728000000001</v>
+        <v>8305.407000000001</v>
       </c>
       <c r="G34">
         <v>2629</v>
@@ -4075,28 +4075,28 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M34">
-        <v>572.8695473075131</v>
+        <v>590.7717206608729</v>
       </c>
       <c r="N34">
-        <v>1280.871269019018</v>
+        <v>1262.969095665658</v>
       </c>
       <c r="O34">
-        <v>256.1742538038035</v>
+        <v>252.5938191331315</v>
       </c>
       <c r="P34">
-        <v>1024.697015215214</v>
+        <v>1010.375276532526</v>
       </c>
       <c r="Q34">
-        <v>2477.997015215214</v>
+        <v>2463.675276532526</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.116921323797763</v>
+        <v>0.1178285992639929</v>
       </c>
       <c r="T34">
-        <v>1.100224259859958</v>
+        <v>1.11425952277436</v>
       </c>
       <c r="U34">
         <v>0.07113097776675759</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.235886468462344</v>
+        <v>3.137829302751364</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09772373963729922</v>
+        <v>0.09773144878382968</v>
       </c>
       <c r="C35">
-        <v>17336.05335912207</v>
+        <v>17081.97442801065</v>
       </c>
       <c r="D35">
-        <v>23012.46035912207</v>
+        <v>23010.06042801066</v>
       </c>
       <c r="E35">
-        <v>140.107</v>
+        <v>391.7860000000001</v>
       </c>
       <c r="F35">
-        <v>8305.407000000001</v>
+        <v>8557.086000000001</v>
       </c>
       <c r="G35">
         <v>2629</v>
@@ -4157,28 +4157,28 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M35">
-        <v>590.7717206608729</v>
+        <v>608.6738940142327</v>
       </c>
       <c r="N35">
-        <v>1262.969095665658</v>
+        <v>1245.066922312298</v>
       </c>
       <c r="O35">
-        <v>252.5938191331315</v>
+        <v>249.0133844624596</v>
       </c>
       <c r="P35">
-        <v>1010.375276532526</v>
+        <v>996.0535378498383</v>
       </c>
       <c r="Q35">
-        <v>2463.675276532526</v>
+        <v>2449.353537849838</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1178285992639929</v>
+        <v>0.1187633679261691</v>
       </c>
       <c r="T35">
-        <v>1.11425952277436</v>
+        <v>1.128720096686168</v>
       </c>
       <c r="U35">
         <v>0.07113097776675759</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.137829302751364</v>
+        <v>3.045540205611618</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09773144878382968</v>
+        <v>0.09843915793036015</v>
       </c>
       <c r="C36">
-        <v>17081.97442801065</v>
+        <v>16612.09081924655</v>
       </c>
       <c r="D36">
-        <v>23010.06042801066</v>
+        <v>22791.85581924655</v>
       </c>
       <c r="E36">
-        <v>391.7860000000001</v>
+        <v>643.4650000000001</v>
       </c>
       <c r="F36">
-        <v>8557.086000000001</v>
+        <v>8808.765000000001</v>
       </c>
       <c r="G36">
         <v>2629</v>
@@ -4239,45 +4239,45 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M36">
-        <v>608.6738940142327</v>
+        <v>648.5979798675924</v>
       </c>
       <c r="N36">
-        <v>1245.066922312298</v>
+        <v>1205.142836458938</v>
       </c>
       <c r="O36">
-        <v>249.0133844624596</v>
+        <v>241.0285672917877</v>
       </c>
       <c r="P36">
-        <v>996.0535378498383</v>
+        <v>964.1142691671506</v>
       </c>
       <c r="Q36">
-        <v>2449.353537849838</v>
+        <v>2417.41426916715</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1187633679261691</v>
+        <v>0.1197268987010278</v>
       </c>
       <c r="T36">
-        <v>1.128720096686168</v>
+        <v>1.143625611333724</v>
       </c>
       <c r="U36">
-        <v>0.07113097776675759</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V36">
         <v>0.2</v>
       </c>
       <c r="W36">
-        <v>0.05690478221340607</v>
+        <v>0.05890478221340606</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y36">
-        <v>3.045540205611618</v>
+        <v>2.858073681797408</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09843915793036015</v>
+        <v>0.09846686707689063</v>
       </c>
       <c r="C37">
-        <v>16612.09081924655</v>
+        <v>16351.9525476278</v>
       </c>
       <c r="D37">
-        <v>22791.85581924655</v>
+        <v>22783.3965476278</v>
       </c>
       <c r="E37">
-        <v>643.4650000000001</v>
+        <v>895.1440000000002</v>
       </c>
       <c r="F37">
-        <v>8808.765000000001</v>
+        <v>9060.444000000001</v>
       </c>
       <c r="G37">
         <v>2629</v>
@@ -4321,28 +4321,28 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M37">
-        <v>648.5979798675924</v>
+        <v>667.1293507209522</v>
       </c>
       <c r="N37">
-        <v>1205.142836458938</v>
+        <v>1186.611465605578</v>
       </c>
       <c r="O37">
-        <v>241.0285672917877</v>
+        <v>237.3222931211157</v>
       </c>
       <c r="P37">
-        <v>964.1142691671506</v>
+        <v>949.2891724844627</v>
       </c>
       <c r="Q37">
-        <v>2417.41426916715</v>
+        <v>2402.589172484463</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1197268987010278</v>
+        <v>0.1207205398126007</v>
       </c>
       <c r="T37">
-        <v>1.143625611333724</v>
+        <v>1.158996923314016</v>
       </c>
       <c r="U37">
         <v>0.07363097776675757</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.858073681797408</v>
+        <v>2.778682746191924</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09846686707689063</v>
+        <v>0.09849457622342112</v>
       </c>
       <c r="C38">
-        <v>16351.9525476278</v>
+        <v>16091.82055305181</v>
       </c>
       <c r="D38">
-        <v>22783.3965476278</v>
+        <v>22774.94355305181</v>
       </c>
       <c r="E38">
-        <v>895.1439999999984</v>
+        <v>1146.822999999999</v>
       </c>
       <c r="F38">
-        <v>9060.444</v>
+        <v>9312.123</v>
       </c>
       <c r="G38">
         <v>2629</v>
@@ -4403,28 +4403,28 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M38">
-        <v>667.1293507209521</v>
+        <v>685.6607215743118</v>
       </c>
       <c r="N38">
-        <v>1186.611465605579</v>
+        <v>1168.080094752219</v>
       </c>
       <c r="O38">
-        <v>237.3222931211157</v>
+        <v>233.6160189504438</v>
       </c>
       <c r="P38">
-        <v>949.2891724844628</v>
+        <v>934.4640758017752</v>
       </c>
       <c r="Q38">
-        <v>2402.589172484463</v>
+        <v>2387.764075801775</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1207205398126007</v>
+        <v>0.1217457250864458</v>
       </c>
       <c r="T38">
-        <v>1.158996923314016</v>
+        <v>1.174856213452412</v>
       </c>
       <c r="U38">
         <v>0.07363097776675757</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.778682746191925</v>
+        <v>2.703583212511062</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09849457622342112</v>
+        <v>0.09852228536995158</v>
       </c>
       <c r="C39">
-        <v>16091.82055305181</v>
+        <v>15831.69482853452</v>
       </c>
       <c r="D39">
-        <v>22774.94355305181</v>
+        <v>22766.49682853452</v>
       </c>
       <c r="E39">
-        <v>1146.822999999999</v>
+        <v>1398.502</v>
       </c>
       <c r="F39">
-        <v>9312.123</v>
+        <v>9563.802000000001</v>
       </c>
       <c r="G39">
         <v>2629</v>
@@ -4485,28 +4485,28 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M39">
-        <v>685.6607215743118</v>
+        <v>704.1920924276717</v>
       </c>
       <c r="N39">
-        <v>1168.080094752219</v>
+        <v>1149.548723898859</v>
       </c>
       <c r="O39">
-        <v>233.6160189504438</v>
+        <v>229.9097447797718</v>
       </c>
       <c r="P39">
-        <v>934.4640758017752</v>
+        <v>919.6389791190871</v>
       </c>
       <c r="Q39">
-        <v>2387.764075801775</v>
+        <v>2372.938979119087</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1217457250864458</v>
+        <v>0.1228039808529956</v>
       </c>
       <c r="T39">
-        <v>1.174856213452412</v>
+        <v>1.191227093595273</v>
       </c>
       <c r="U39">
         <v>0.07363097776675757</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.703583212511062</v>
+        <v>2.632436285866033</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09852228536995158</v>
+        <v>0.09854999451648205</v>
       </c>
       <c r="C40">
-        <v>15831.69482853452</v>
+        <v>15571.57536710225</v>
       </c>
       <c r="D40">
-        <v>22766.49682853452</v>
+        <v>22758.05636710225</v>
       </c>
       <c r="E40">
-        <v>1398.502</v>
+        <v>1650.181</v>
       </c>
       <c r="F40">
-        <v>9563.802000000001</v>
+        <v>9815.481000000002</v>
       </c>
       <c r="G40">
         <v>2629</v>
@@ -4567,28 +4567,28 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M40">
-        <v>704.1920924276717</v>
+        <v>722.7234632810315</v>
       </c>
       <c r="N40">
-        <v>1149.548723898859</v>
+        <v>1131.017353045499</v>
       </c>
       <c r="O40">
-        <v>229.9097447797718</v>
+        <v>226.2034706090998</v>
       </c>
       <c r="P40">
-        <v>919.6389791190871</v>
+        <v>904.8138824363992</v>
       </c>
       <c r="Q40">
-        <v>2372.938979119087</v>
+        <v>2358.113882436399</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1228039808529956</v>
+        <v>0.1238969335299241</v>
       </c>
       <c r="T40">
-        <v>1.191227093595273</v>
+        <v>1.208134723906753</v>
       </c>
       <c r="U40">
         <v>0.07363097776675757</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.632436285866033</v>
+        <v>2.564937919561776</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09854999451648205</v>
+        <v>0.09857770366301254</v>
       </c>
       <c r="C41">
-        <v>15571.57536710225</v>
+        <v>15311.46216179163</v>
       </c>
       <c r="D41">
-        <v>22758.05636710225</v>
+        <v>22749.62216179163</v>
       </c>
       <c r="E41">
-        <v>1650.181</v>
+        <v>1901.860000000001</v>
       </c>
       <c r="F41">
-        <v>9815.481000000002</v>
+        <v>10067.16</v>
       </c>
       <c r="G41">
         <v>2629</v>
@@ -4649,28 +4649,28 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M41">
-        <v>722.7234632810315</v>
+        <v>741.2548341343913</v>
       </c>
       <c r="N41">
-        <v>1131.017353045499</v>
+        <v>1112.485982192139</v>
       </c>
       <c r="O41">
-        <v>226.2034706090998</v>
+        <v>222.4971964384279</v>
       </c>
       <c r="P41">
-        <v>904.8138824363992</v>
+        <v>889.9887857537115</v>
       </c>
       <c r="Q41">
-        <v>2358.113882436399</v>
+        <v>2343.288785753712</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1238969335299241</v>
+        <v>0.1250263179627502</v>
       </c>
       <c r="T41">
-        <v>1.208134723906753</v>
+        <v>1.225605941895281</v>
       </c>
       <c r="U41">
         <v>0.07363097776675757</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.564937919561776</v>
+        <v>2.500814471572732</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09857770366301254</v>
+        <v>0.099753412809543</v>
       </c>
       <c r="C42">
-        <v>15311.46216179163</v>
+        <v>14707.58760749582</v>
       </c>
       <c r="D42">
-        <v>22749.62216179163</v>
+        <v>22397.42660749582</v>
       </c>
       <c r="E42">
-        <v>1901.860000000001</v>
+        <v>2153.539000000001</v>
       </c>
       <c r="F42">
-        <v>10067.16</v>
+        <v>10318.839</v>
       </c>
       <c r="G42">
         <v>2629</v>
@@ -4731,45 +4731,45 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M42">
-        <v>741.2548341343913</v>
+        <v>795.9021414877511</v>
       </c>
       <c r="N42">
-        <v>1112.485982192139</v>
+        <v>1057.83867483878</v>
       </c>
       <c r="O42">
-        <v>222.4971964384279</v>
+        <v>211.5677349677559</v>
       </c>
       <c r="P42">
-        <v>889.9887857537115</v>
+        <v>846.2709398710236</v>
       </c>
       <c r="Q42">
-        <v>2343.288785753712</v>
+        <v>2299.570939871024</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1250263179627502</v>
+        <v>0.1261939866136382</v>
       </c>
       <c r="T42">
-        <v>1.225605941895281</v>
+        <v>1.243669404561387</v>
       </c>
       <c r="U42">
-        <v>0.07363097776675757</v>
+        <v>0.07713097776675758</v>
       </c>
       <c r="V42">
         <v>0.2</v>
       </c>
       <c r="W42">
-        <v>0.05890478221340606</v>
+        <v>0.06170478221340606</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y42">
-        <v>2.500814471572732</v>
+        <v>2.329106456305545</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.099753412809543</v>
+        <v>0.09980912195607347</v>
       </c>
       <c r="C43">
-        <v>14707.58760749582</v>
+        <v>14439.49077020624</v>
       </c>
       <c r="D43">
-        <v>22397.42660749582</v>
+        <v>22381.00877020624</v>
       </c>
       <c r="E43">
-        <v>2153.539000000001</v>
+        <v>2405.218000000001</v>
       </c>
       <c r="F43">
-        <v>10318.839</v>
+        <v>10570.518</v>
       </c>
       <c r="G43">
         <v>2629</v>
@@ -4813,28 +4813,28 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M43">
-        <v>795.9021414877511</v>
+        <v>815.3143888411109</v>
       </c>
       <c r="N43">
-        <v>1057.83867483878</v>
+        <v>1038.42642748542</v>
       </c>
       <c r="O43">
-        <v>211.5677349677559</v>
+        <v>207.685285497084</v>
       </c>
       <c r="P43">
-        <v>846.2709398710236</v>
+        <v>830.7411419883358</v>
       </c>
       <c r="Q43">
-        <v>2299.570939871024</v>
+        <v>2284.041141988336</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1261939866136382</v>
+        <v>0.1274019197007637</v>
       </c>
       <c r="T43">
-        <v>1.243669404561387</v>
+        <v>1.262355745250462</v>
       </c>
       <c r="U43">
         <v>0.07713097776675758</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.329106456305545</v>
+        <v>2.273651540679222</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09980912195607347</v>
+        <v>0.100828031102604</v>
       </c>
       <c r="C44">
-        <v>14439.49077020624</v>
+        <v>13891.72254583645</v>
       </c>
       <c r="D44">
-        <v>22381.00877020624</v>
+        <v>22084.91954583645</v>
       </c>
       <c r="E44">
-        <v>2405.217999999999</v>
+        <v>2656.896999999999</v>
       </c>
       <c r="F44">
-        <v>10570.518</v>
+        <v>10822.197</v>
       </c>
       <c r="G44">
         <v>2629</v>
@@ -4895,45 +4895,45 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M44">
-        <v>815.3143888411108</v>
+        <v>865.0287877944706</v>
       </c>
       <c r="N44">
-        <v>1038.42642748542</v>
+        <v>988.71202853206</v>
       </c>
       <c r="O44">
-        <v>207.685285497084</v>
+        <v>197.742405706412</v>
       </c>
       <c r="P44">
-        <v>830.7411419883359</v>
+        <v>790.969622825648</v>
       </c>
       <c r="Q44">
-        <v>2284.041141988336</v>
+        <v>2244.269622825648</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1274019197007637</v>
+        <v>0.1286522364049813</v>
       </c>
       <c r="T44">
-        <v>1.262355745250462</v>
+        <v>1.281697747016347</v>
       </c>
       <c r="U44">
-        <v>0.07713097776675758</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V44">
         <v>0.2</v>
       </c>
       <c r="W44">
-        <v>0.06170478221340606</v>
+        <v>0.06394478221340608</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y44">
-        <v>2.273651540679223</v>
+        <v>2.142981646949507</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.100828031102604</v>
+        <v>0.1009061402491344</v>
       </c>
       <c r="C45">
-        <v>13891.72254583645</v>
+        <v>13617.66844639208</v>
       </c>
       <c r="D45">
-        <v>22084.91954583645</v>
+        <v>22062.54444639208</v>
       </c>
       <c r="E45">
-        <v>2656.896999999999</v>
+        <v>2908.575999999999</v>
       </c>
       <c r="F45">
-        <v>10822.197</v>
+        <v>11073.876</v>
       </c>
       <c r="G45">
         <v>2629</v>
@@ -4977,28 +4977,28 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M45">
-        <v>865.0287877944706</v>
+        <v>885.1457363478305</v>
       </c>
       <c r="N45">
-        <v>988.71202853206</v>
+        <v>968.5950799787001</v>
       </c>
       <c r="O45">
-        <v>197.742405706412</v>
+        <v>193.7190159957401</v>
       </c>
       <c r="P45">
-        <v>790.969622825648</v>
+        <v>774.8760639829601</v>
       </c>
       <c r="Q45">
-        <v>2244.269622825648</v>
+        <v>2228.17606398296</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1286522364049813</v>
+        <v>0.1299472072772067</v>
       </c>
       <c r="T45">
-        <v>1.281697747016347</v>
+        <v>1.301730534559584</v>
       </c>
       <c r="U45">
         <v>0.07993097776675759</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.142981646949507</v>
+        <v>2.094277518609746</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1009061402491344</v>
+        <v>0.1009842493956649</v>
       </c>
       <c r="C46">
-        <v>13617.66844639208</v>
+        <v>13343.65963924449</v>
       </c>
       <c r="D46">
-        <v>22062.54444639208</v>
+        <v>22040.21463924449</v>
       </c>
       <c r="E46">
-        <v>2908.575999999999</v>
+        <v>3160.254999999999</v>
       </c>
       <c r="F46">
-        <v>11073.876</v>
+        <v>11325.555</v>
       </c>
       <c r="G46">
         <v>2629</v>
@@ -5059,28 +5059,28 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M46">
-        <v>885.1457363478305</v>
+        <v>905.2626849011903</v>
       </c>
       <c r="N46">
-        <v>968.5950799787001</v>
+        <v>948.4781314253404</v>
       </c>
       <c r="O46">
-        <v>193.7190159957401</v>
+        <v>189.6956262850681</v>
       </c>
       <c r="P46">
-        <v>774.8760639829601</v>
+        <v>758.7825051402723</v>
       </c>
       <c r="Q46">
-        <v>2228.17606398296</v>
+        <v>2212.082505140272</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1299472072772067</v>
+        <v>0.1312892679993312</v>
       </c>
       <c r="T46">
-        <v>1.301730534559584</v>
+        <v>1.322491787104394</v>
       </c>
       <c r="U46">
         <v>0.07993097776675759</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.094277518609746</v>
+        <v>2.047738018196196</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1009842493956649</v>
+        <v>0.1010623585421954</v>
       </c>
       <c r="C47">
-        <v>13343.65963924449</v>
+        <v>13069.69598700986</v>
       </c>
       <c r="D47">
-        <v>22040.21463924449</v>
+        <v>22017.92998700986</v>
       </c>
       <c r="E47">
-        <v>3160.254999999999</v>
+        <v>3411.933999999999</v>
       </c>
       <c r="F47">
-        <v>11325.555</v>
+        <v>11577.234</v>
       </c>
       <c r="G47">
         <v>2629</v>
@@ -5141,28 +5141,28 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M47">
-        <v>905.2626849011903</v>
+        <v>925.37963345455</v>
       </c>
       <c r="N47">
-        <v>948.4781314253404</v>
+        <v>928.3611828719806</v>
       </c>
       <c r="O47">
-        <v>189.6956262850681</v>
+        <v>185.6722365743962</v>
       </c>
       <c r="P47">
-        <v>758.7825051402723</v>
+        <v>742.6889462975845</v>
       </c>
       <c r="Q47">
-        <v>2212.082505140272</v>
+        <v>2195.988946297584</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1312892679993312</v>
+        <v>0.132681034674127</v>
       </c>
       <c r="T47">
-        <v>1.322491787104394</v>
+        <v>1.344021974928642</v>
       </c>
       <c r="U47">
         <v>0.07993097776675759</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.047738018196196</v>
+        <v>2.003221974322366</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1010623585421954</v>
+        <v>0.1040732676887259</v>
       </c>
       <c r="C48">
-        <v>13069.69598700986</v>
+        <v>11992.06043822411</v>
       </c>
       <c r="D48">
-        <v>22017.92998700986</v>
+        <v>21191.97343822411</v>
       </c>
       <c r="E48">
-        <v>3411.933999999999</v>
+        <v>3663.613000000001</v>
       </c>
       <c r="F48">
-        <v>11577.234</v>
+        <v>11828.913</v>
       </c>
       <c r="G48">
         <v>2629</v>
@@ -5223,45 +5223,45 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M48">
-        <v>925.37963345455</v>
+        <v>1037.76210340791</v>
       </c>
       <c r="N48">
-        <v>928.3611828719806</v>
+        <v>815.9787129186207</v>
       </c>
       <c r="O48">
-        <v>185.6722365743962</v>
+        <v>163.1957425837242</v>
       </c>
       <c r="P48">
-        <v>742.6889462975845</v>
+        <v>652.7829703348965</v>
       </c>
       <c r="Q48">
-        <v>2195.988946297584</v>
+        <v>2106.082970334896</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.132681034674127</v>
+        <v>0.1341253208460849</v>
       </c>
       <c r="T48">
-        <v>1.344021974928642</v>
+        <v>1.366364622670785</v>
       </c>
       <c r="U48">
-        <v>0.07993097776675759</v>
+        <v>0.08773097776675759</v>
       </c>
       <c r="V48">
         <v>0.2</v>
       </c>
       <c r="W48">
-        <v>0.06394478221340608</v>
+        <v>0.07018478221340607</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y48">
-        <v>2.003221974322366</v>
+        <v>1.786286866940916</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1040732676887259</v>
+        <v>0.1057113768352563</v>
       </c>
       <c r="C49">
-        <v>11992.06043822411</v>
+        <v>11316.52094823443</v>
       </c>
       <c r="D49">
-        <v>21191.97343822411</v>
+        <v>20768.11294823443</v>
       </c>
       <c r="E49">
-        <v>3663.613000000001</v>
+        <v>3915.292000000001</v>
       </c>
       <c r="F49">
-        <v>11828.913</v>
+        <v>12080.592</v>
       </c>
       <c r="G49">
         <v>2629</v>
@@ -5305,45 +5305,45 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M49">
-        <v>1037.76210340791</v>
+        <v>1106.95645696127</v>
       </c>
       <c r="N49">
-        <v>815.9787129186207</v>
+        <v>746.784359365261</v>
       </c>
       <c r="O49">
-        <v>163.1957425837242</v>
+        <v>149.3568718730522</v>
       </c>
       <c r="P49">
-        <v>652.7829703348965</v>
+        <v>597.4274874922088</v>
       </c>
       <c r="Q49">
-        <v>2106.082970334896</v>
+        <v>2050.727487492209</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1341253208460849</v>
+        <v>0.135625156486195</v>
       </c>
       <c r="T49">
-        <v>1.366364622670785</v>
+        <v>1.389566603018396</v>
       </c>
       <c r="U49">
-        <v>0.08773097776675759</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V49">
         <v>0.2</v>
       </c>
       <c r="W49">
-        <v>0.07018478221340607</v>
+        <v>0.07330478221340607</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y49">
-        <v>1.786286866940916</v>
+        <v>1.674628486666291</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1057113768352563</v>
+        <v>0.1058830859817868</v>
       </c>
       <c r="C50">
-        <v>11316.52094823443</v>
+        <v>11021.39196573967</v>
       </c>
       <c r="D50">
-        <v>20768.11294823443</v>
+        <v>20724.66296573967</v>
       </c>
       <c r="E50">
-        <v>3915.291999999999</v>
+        <v>4166.971</v>
       </c>
       <c r="F50">
-        <v>12080.592</v>
+        <v>12332.271</v>
       </c>
       <c r="G50">
         <v>2629</v>
@@ -5387,28 +5387,28 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M50">
-        <v>1106.956456961269</v>
+        <v>1130.018049814629</v>
       </c>
       <c r="N50">
-        <v>746.7843593652613</v>
+        <v>723.7227665119015</v>
       </c>
       <c r="O50">
-        <v>149.3568718730523</v>
+        <v>144.7445533023803</v>
       </c>
       <c r="P50">
-        <v>597.427487492209</v>
+        <v>578.9782132095212</v>
       </c>
       <c r="Q50">
-        <v>2050.727487492209</v>
+        <v>2032.278213209521</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.135625156486195</v>
+        <v>0.137183809210231</v>
       </c>
       <c r="T50">
-        <v>1.389566603018396</v>
+        <v>1.413678464948265</v>
       </c>
       <c r="U50">
         <v>0.09163097776675758</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.674628486666292</v>
+        <v>1.640452395101673</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1058830859817868</v>
+        <v>0.1060547951283173</v>
       </c>
       <c r="C51">
-        <v>11021.39196573967</v>
+        <v>10726.44441132748</v>
       </c>
       <c r="D51">
-        <v>20724.66296573967</v>
+        <v>20681.39441132748</v>
       </c>
       <c r="E51">
-        <v>4166.971</v>
+        <v>4418.65</v>
       </c>
       <c r="F51">
-        <v>12332.271</v>
+        <v>12583.95</v>
       </c>
       <c r="G51">
         <v>2629</v>
@@ -5469,28 +5469,28 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M51">
-        <v>1130.018049814629</v>
+        <v>1153.079642667989</v>
       </c>
       <c r="N51">
-        <v>723.7227665119015</v>
+        <v>700.6611736585417</v>
       </c>
       <c r="O51">
-        <v>144.7445533023803</v>
+        <v>140.1322347317083</v>
       </c>
       <c r="P51">
-        <v>578.9782132095212</v>
+        <v>560.5289389268333</v>
       </c>
       <c r="Q51">
-        <v>2032.278213209521</v>
+        <v>2013.828938926833</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.137183809210231</v>
+        <v>0.1388048080432285</v>
       </c>
       <c r="T51">
-        <v>1.413678464948265</v>
+        <v>1.43875480135533</v>
       </c>
       <c r="U51">
         <v>0.09163097776675758</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.640452395101673</v>
+        <v>1.60764334719964</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1060547951283173</v>
+        <v>0.1062265042748478</v>
       </c>
       <c r="C52">
-        <v>10726.44441132748</v>
+        <v>10431.6771510191</v>
       </c>
       <c r="D52">
-        <v>20681.39441132748</v>
+        <v>20638.3061510191</v>
       </c>
       <c r="E52">
-        <v>4418.65</v>
+        <v>4670.329</v>
       </c>
       <c r="F52">
-        <v>12583.95</v>
+        <v>12835.629</v>
       </c>
       <c r="G52">
         <v>2629</v>
@@ -5551,28 +5551,28 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M52">
-        <v>1153.079642667989</v>
+        <v>1176.141235521349</v>
       </c>
       <c r="N52">
-        <v>700.6611736585417</v>
+        <v>677.5995808051819</v>
       </c>
       <c r="O52">
-        <v>140.1322347317083</v>
+        <v>135.5199161610364</v>
       </c>
       <c r="P52">
-        <v>560.5289389268333</v>
+        <v>542.0796646441455</v>
       </c>
       <c r="Q52">
-        <v>2013.828938926833</v>
+        <v>1995.379664644146</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1388048080432285</v>
+        <v>0.1404919700938993</v>
       </c>
       <c r="T52">
-        <v>1.43875480135533</v>
+        <v>1.464854661697377</v>
       </c>
       <c r="U52">
         <v>0.09163097776675758</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.60764334719964</v>
+        <v>1.576120928627098</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1062265042748478</v>
+        <v>0.1063982134213782</v>
       </c>
       <c r="C53">
-        <v>10431.6771510191</v>
+        <v>10137.08906026645</v>
       </c>
       <c r="D53">
-        <v>20638.3061510191</v>
+        <v>20595.39706026645</v>
       </c>
       <c r="E53">
-        <v>4670.329</v>
+        <v>4922.008</v>
       </c>
       <c r="F53">
-        <v>12835.629</v>
+        <v>13087.308</v>
       </c>
       <c r="G53">
         <v>2629</v>
@@ -5633,28 +5633,28 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M53">
-        <v>1176.141235521349</v>
+        <v>1199.202828374709</v>
       </c>
       <c r="N53">
-        <v>677.5995808051819</v>
+        <v>654.5379879518221</v>
       </c>
       <c r="O53">
-        <v>135.5199161610364</v>
+        <v>130.9075975903644</v>
       </c>
       <c r="P53">
-        <v>542.0796646441455</v>
+        <v>523.6303903614577</v>
       </c>
       <c r="Q53">
-        <v>1995.379664644146</v>
+        <v>1976.930390361458</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1404919700938993</v>
+        <v>0.142249430563348</v>
       </c>
       <c r="T53">
-        <v>1.464854661697377</v>
+        <v>1.492042016220342</v>
       </c>
       <c r="U53">
         <v>0.09163097776675758</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.576120928627098</v>
+        <v>1.545810910768885</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1063982134213782</v>
+        <v>0.1065699225679087</v>
       </c>
       <c r="C54">
-        <v>10137.08906026645</v>
+        <v>9842.679023854202</v>
       </c>
       <c r="D54">
-        <v>20595.39706026645</v>
+        <v>20552.6660238542</v>
       </c>
       <c r="E54">
-        <v>4922.008</v>
+        <v>5173.687</v>
       </c>
       <c r="F54">
-        <v>13087.308</v>
+        <v>13338.987</v>
       </c>
       <c r="G54">
         <v>2629</v>
@@ -5715,28 +5715,28 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M54">
-        <v>1199.202828374709</v>
+        <v>1222.264421228068</v>
       </c>
       <c r="N54">
-        <v>654.5379879518221</v>
+        <v>631.4763950984623</v>
       </c>
       <c r="O54">
-        <v>130.9075975903644</v>
+        <v>126.2952790196925</v>
       </c>
       <c r="P54">
-        <v>523.6303903614577</v>
+        <v>505.1811160787698</v>
       </c>
       <c r="Q54">
-        <v>1976.930390361458</v>
+        <v>1958.48111607877</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.142249430563348</v>
+        <v>0.1440816765846882</v>
       </c>
       <c r="T54">
-        <v>1.492042016220342</v>
+        <v>1.520386279446413</v>
       </c>
       <c r="U54">
         <v>0.09163097776675758</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.545810910768885</v>
+        <v>1.516644667169472</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1065699225679087</v>
+        <v>0.1128760317144392</v>
       </c>
       <c r="C55">
-        <v>9842.679023854202</v>
+        <v>8135.817549631025</v>
       </c>
       <c r="D55">
-        <v>20552.6660238542</v>
+        <v>19097.48354963103</v>
       </c>
       <c r="E55">
-        <v>5173.687</v>
+        <v>5425.366</v>
       </c>
       <c r="F55">
-        <v>13338.987</v>
+        <v>13590.666</v>
       </c>
       <c r="G55">
         <v>2629</v>
@@ -5797,45 +5797,45 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M55">
-        <v>1222.264421228068</v>
+        <v>1438.313471281428</v>
       </c>
       <c r="N55">
-        <v>631.4763950984623</v>
+        <v>415.4273450451024</v>
       </c>
       <c r="O55">
-        <v>126.2952790196925</v>
+        <v>83.08546900902047</v>
       </c>
       <c r="P55">
-        <v>505.1811160787698</v>
+        <v>332.3418760360819</v>
       </c>
       <c r="Q55">
-        <v>1958.48111607877</v>
+        <v>1785.641876036082</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1440816765846882</v>
+        <v>0.1459935854765215</v>
       </c>
       <c r="T55">
-        <v>1.520386279446413</v>
+        <v>1.549962901943182</v>
       </c>
       <c r="U55">
-        <v>0.09163097776675758</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V55">
         <v>0.2</v>
       </c>
       <c r="W55">
-        <v>0.07330478221340607</v>
+        <v>0.08466478221340606</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y55">
-        <v>1.516644667169472</v>
+        <v>1.288829489078614</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1128760317144392</v>
+        <v>0.1131613408609696</v>
       </c>
       <c r="C56">
-        <v>8135.817549631025</v>
+        <v>7823.158092517737</v>
       </c>
       <c r="D56">
-        <v>19097.48354963103</v>
+        <v>19036.50309251774</v>
       </c>
       <c r="E56">
-        <v>5425.366</v>
+        <v>5677.045</v>
       </c>
       <c r="F56">
-        <v>13590.666</v>
+        <v>13842.345</v>
       </c>
       <c r="G56">
         <v>2629</v>
@@ -5879,28 +5879,28 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M56">
-        <v>1438.313471281428</v>
+        <v>1464.948905934788</v>
       </c>
       <c r="N56">
-        <v>415.4273450451024</v>
+        <v>388.7919103917425</v>
       </c>
       <c r="O56">
-        <v>83.08546900902047</v>
+        <v>77.7583820783485</v>
       </c>
       <c r="P56">
-        <v>332.3418760360819</v>
+        <v>311.033528313394</v>
       </c>
       <c r="Q56">
-        <v>1785.641876036082</v>
+        <v>1764.333528313394</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1459935854765215</v>
+        <v>0.1479904680968807</v>
       </c>
       <c r="T56">
-        <v>1.549962901943182</v>
+        <v>1.580854040995363</v>
       </c>
       <c r="U56">
         <v>0.1058309777667576</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.288829489078614</v>
+        <v>1.265396225640821</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1131613408609696</v>
+        <v>0.1267097482093424</v>
       </c>
       <c r="C57">
-        <v>7823.158092517737</v>
+        <v>5065.017641306033</v>
       </c>
       <c r="D57">
-        <v>19036.50309251774</v>
+        <v>16530.04164130603</v>
       </c>
       <c r="E57">
-        <v>5677.045</v>
+        <v>5928.724</v>
       </c>
       <c r="F57">
-        <v>13842.345</v>
+        <v>14094.024</v>
       </c>
       <c r="G57">
         <v>2629</v>
@@ -5961,45 +5961,45 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M57">
-        <v>1464.948905934788</v>
+        <v>1894.673426988148</v>
       </c>
       <c r="N57">
-        <v>388.7919103917425</v>
+        <v>-40.93261066161722</v>
       </c>
       <c r="O57">
-        <v>77.7583820783485</v>
+        <v>-8.186522132323445</v>
       </c>
       <c r="P57">
-        <v>311.033528313394</v>
+        <v>-32.74608852929377</v>
       </c>
       <c r="Q57">
-        <v>1764.333528313394</v>
+        <v>1420.553911470706</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1479904680968807</v>
+        <v>0.1503622587281154</v>
       </c>
       <c r="T57">
-        <v>1.580854040995363</v>
+        <v>1.617544887740754</v>
       </c>
       <c r="U57">
-        <v>0.1058309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V57">
-        <v>0.2</v>
+        <v>0.1956791909277278</v>
       </c>
       <c r="W57">
-        <v>0.08466478221340606</v>
+        <v>0.1081256328017351</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y57">
-        <v>1.265396225640821</v>
+        <v>0.978395954638639</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1267097482093424</v>
+        <v>0.12759605798701</v>
       </c>
       <c r="C58">
-        <v>5065.017641306033</v>
+        <v>4672.175799047674</v>
       </c>
       <c r="D58">
-        <v>16530.04164130603</v>
+        <v>16388.87879904768</v>
       </c>
       <c r="E58">
-        <v>5928.724</v>
+        <v>6180.403000000002</v>
       </c>
       <c r="F58">
-        <v>14094.024</v>
+        <v>14345.703</v>
       </c>
       <c r="G58">
         <v>2629</v>
@@ -6043,37 +6043,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M58">
-        <v>1894.673426988148</v>
+        <v>1928.506881041508</v>
       </c>
       <c r="N58">
-        <v>-40.93261066161722</v>
+        <v>-74.76606471497735</v>
       </c>
       <c r="O58">
-        <v>-8.186522132323445</v>
+        <v>-14.95321294299547</v>
       </c>
       <c r="P58">
-        <v>-32.74608852929377</v>
+        <v>-59.81285177198188</v>
       </c>
       <c r="Q58">
-        <v>1420.553911470706</v>
+        <v>1393.487148228018</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1503622587281154</v>
+        <v>0.152793939163653</v>
       </c>
       <c r="T58">
-        <v>1.617544887740754</v>
+        <v>1.655162210711469</v>
       </c>
       <c r="U58">
         <v>0.1344309777667576</v>
       </c>
       <c r="V58">
-        <v>0.1956791909277278</v>
+        <v>0.1922462226658378</v>
       </c>
       <c r="W58">
-        <v>0.1081256328017351</v>
+        <v>0.1085871300818232</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.978395954638639</v>
+        <v>0.9612311133291891</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.12759605798701</v>
+        <v>0.1284823677646776</v>
       </c>
       <c r="C59">
-        <v>4672.175799047674</v>
+        <v>4281.724539671812</v>
       </c>
       <c r="D59">
-        <v>16388.87879904768</v>
+        <v>16250.10653967181</v>
       </c>
       <c r="E59">
-        <v>6180.403000000002</v>
+        <v>6432.082000000002</v>
       </c>
       <c r="F59">
-        <v>14345.703</v>
+        <v>14597.382</v>
       </c>
       <c r="G59">
         <v>2629</v>
@@ -6125,37 +6125,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M59">
-        <v>1928.506881041508</v>
+        <v>1962.340335094868</v>
       </c>
       <c r="N59">
-        <v>-74.76606471497735</v>
+        <v>-108.599518768337</v>
       </c>
       <c r="O59">
-        <v>-14.95321294299547</v>
+        <v>-21.71990375366741</v>
       </c>
       <c r="P59">
-        <v>-59.81285177198188</v>
+        <v>-86.87961501466961</v>
       </c>
       <c r="Q59">
-        <v>1393.487148228018</v>
+        <v>1366.42038498533</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.152793939163653</v>
+        <v>0.1553414139056448</v>
       </c>
       <c r="T59">
-        <v>1.655162210711469</v>
+        <v>1.694570834776028</v>
       </c>
       <c r="U59">
         <v>0.1344309777667576</v>
       </c>
       <c r="V59">
-        <v>0.1922462226658378</v>
+        <v>0.1889316326198751</v>
       </c>
       <c r="W59">
-        <v>0.1085871300818232</v>
+        <v>0.1090327136625979</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.9612311133291891</v>
+        <v>0.9446581630993754</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1284823677646776</v>
+        <v>0.1293686775423452</v>
       </c>
       <c r="C60">
-        <v>4281.724539671815</v>
+        <v>3893.603646529389</v>
       </c>
       <c r="D60">
-        <v>16250.10653967181</v>
+        <v>16113.66464652939</v>
       </c>
       <c r="E60">
-        <v>6432.081999999999</v>
+        <v>6683.760999999999</v>
       </c>
       <c r="F60">
-        <v>14597.382</v>
+        <v>14849.061</v>
       </c>
       <c r="G60">
         <v>2629</v>
@@ -6207,37 +6207,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M60">
-        <v>1962.340335094867</v>
+        <v>1996.173789148227</v>
       </c>
       <c r="N60">
-        <v>-108.5995187683366</v>
+        <v>-142.4329728216965</v>
       </c>
       <c r="O60">
-        <v>-21.71990375366731</v>
+        <v>-28.4865945643393</v>
       </c>
       <c r="P60">
-        <v>-86.87961501466926</v>
+        <v>-113.9463782573572</v>
       </c>
       <c r="Q60">
-        <v>1366.420384985331</v>
+        <v>1339.353621742643</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1553414139056447</v>
+        <v>0.1580131557082214</v>
       </c>
       <c r="T60">
-        <v>1.694570834776027</v>
+        <v>1.735901830746174</v>
       </c>
       <c r="U60">
         <v>0.1344309777667576</v>
       </c>
       <c r="V60">
-        <v>0.1889316326198751</v>
+        <v>0.1857294015585213</v>
       </c>
       <c r="W60">
-        <v>0.1090327136625979</v>
+        <v>0.1094631927152108</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.9446581630993757</v>
+        <v>0.9286470077926066</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1293686775423452</v>
+        <v>0.1302549873200127</v>
       </c>
       <c r="C61">
-        <v>3893.603646529389</v>
+        <v>3507.75490853673</v>
       </c>
       <c r="D61">
-        <v>16113.66464652939</v>
+        <v>15979.49490853673</v>
       </c>
       <c r="E61">
-        <v>6683.760999999999</v>
+        <v>6935.439999999999</v>
       </c>
       <c r="F61">
-        <v>14849.061</v>
+        <v>15100.74</v>
       </c>
       <c r="G61">
         <v>2629</v>
@@ -6289,37 +6289,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M61">
-        <v>1996.173789148227</v>
+        <v>2030.007243201587</v>
       </c>
       <c r="N61">
-        <v>-142.4329728216965</v>
+        <v>-176.2664268750561</v>
       </c>
       <c r="O61">
-        <v>-28.4865945643393</v>
+        <v>-35.25328537501123</v>
       </c>
       <c r="P61">
-        <v>-113.9463782573572</v>
+        <v>-141.0131415000449</v>
       </c>
       <c r="Q61">
-        <v>1339.353621742643</v>
+        <v>1312.286858499955</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1580131557082214</v>
+        <v>0.160818484600927</v>
       </c>
       <c r="T61">
-        <v>1.735901830746174</v>
+        <v>1.779299376514829</v>
       </c>
       <c r="U61">
         <v>0.1344309777667576</v>
       </c>
       <c r="V61">
-        <v>0.1857294015585213</v>
+        <v>0.182633911532546</v>
       </c>
       <c r="W61">
-        <v>0.1094631927152108</v>
+        <v>0.1098793224660699</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.9286470077926066</v>
+        <v>0.9131695576627299</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1302549873200127</v>
+        <v>0.1311412970976803</v>
       </c>
       <c r="C62">
-        <v>3507.75490853673</v>
+        <v>3124.122037368785</v>
       </c>
       <c r="D62">
-        <v>15979.49490853673</v>
+        <v>15847.54103736878</v>
       </c>
       <c r="E62">
-        <v>6935.439999999999</v>
+        <v>7187.118999999999</v>
       </c>
       <c r="F62">
-        <v>15100.74</v>
+        <v>15352.419</v>
       </c>
       <c r="G62">
         <v>2629</v>
@@ -6371,37 +6371,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M62">
-        <v>2030.007243201587</v>
+        <v>2063.840697254946</v>
       </c>
       <c r="N62">
-        <v>-176.2664268750561</v>
+        <v>-210.0998809284158</v>
       </c>
       <c r="O62">
-        <v>-35.25328537501123</v>
+        <v>-42.01997618568316</v>
       </c>
       <c r="P62">
-        <v>-141.0131415000449</v>
+        <v>-168.0799047427327</v>
       </c>
       <c r="Q62">
-        <v>1312.286858499955</v>
+        <v>1285.220095257267</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.160818484600927</v>
+        <v>0.1637676765137712</v>
       </c>
       <c r="T62">
-        <v>1.779299376514829</v>
+        <v>1.824922437451107</v>
       </c>
       <c r="U62">
         <v>0.1344309777667576</v>
       </c>
       <c r="V62">
-        <v>0.182633911532546</v>
+        <v>0.1796399129828321</v>
       </c>
       <c r="W62">
-        <v>0.1098793224660699</v>
+        <v>0.1102818086185402</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.9131695576627299</v>
+        <v>0.8981995649141605</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1311412970976803</v>
+        <v>0.1320276068753479</v>
       </c>
       <c r="C63">
-        <v>3124.122037368785</v>
+        <v>2742.650588721453</v>
       </c>
       <c r="D63">
-        <v>15847.54103736878</v>
+        <v>15717.74858872145</v>
       </c>
       <c r="E63">
-        <v>7187.118999999999</v>
+        <v>7438.797999999999</v>
       </c>
       <c r="F63">
-        <v>15352.419</v>
+        <v>15604.098</v>
       </c>
       <c r="G63">
         <v>2629</v>
@@ -6453,37 +6453,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M63">
-        <v>2063.840697254946</v>
+        <v>2097.674151308307</v>
       </c>
       <c r="N63">
-        <v>-210.0998809284158</v>
+        <v>-243.9333349817759</v>
       </c>
       <c r="O63">
-        <v>-42.01997618568316</v>
+        <v>-48.78666699635519</v>
       </c>
       <c r="P63">
-        <v>-168.0799047427327</v>
+        <v>-195.1466679854207</v>
       </c>
       <c r="Q63">
-        <v>1285.220095257267</v>
+        <v>1258.153332014579</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1637676765137712</v>
+        <v>0.1668720890536073</v>
       </c>
       <c r="T63">
-        <v>1.824922437451107</v>
+        <v>1.872946712120873</v>
       </c>
       <c r="U63">
         <v>0.1344309777667576</v>
       </c>
       <c r="V63">
-        <v>0.1796399129828321</v>
+        <v>0.1767424950314961</v>
       </c>
       <c r="W63">
-        <v>0.1102818086185402</v>
+        <v>0.1106713113467373</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8981995649141605</v>
+        <v>0.8837124751574804</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1320276068753479</v>
+        <v>0.1329139166530155</v>
       </c>
       <c r="C64">
-        <v>2742.650588721453</v>
+        <v>2363.287887411807</v>
       </c>
       <c r="D64">
-        <v>15717.74858872145</v>
+        <v>15590.06488741181</v>
       </c>
       <c r="E64">
-        <v>7438.797999999999</v>
+        <v>7690.477000000001</v>
       </c>
       <c r="F64">
-        <v>15604.098</v>
+        <v>15855.777</v>
       </c>
       <c r="G64">
         <v>2629</v>
@@ -6535,37 +6535,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M64">
-        <v>2097.674151308307</v>
+        <v>2131.507605361666</v>
       </c>
       <c r="N64">
-        <v>-243.9333349817759</v>
+        <v>-277.7667890351356</v>
       </c>
       <c r="O64">
-        <v>-48.78666699635519</v>
+        <v>-55.55335780702713</v>
       </c>
       <c r="P64">
-        <v>-195.1466679854207</v>
+        <v>-222.2134312281085</v>
       </c>
       <c r="Q64">
-        <v>1258.153332014579</v>
+        <v>1231.086568771892</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1668720890536073</v>
+        <v>0.1701443076766778</v>
       </c>
       <c r="T64">
-        <v>1.872946712120873</v>
+        <v>1.923566893529545</v>
       </c>
       <c r="U64">
         <v>0.1344309777667576</v>
       </c>
       <c r="V64">
-        <v>0.1767424950314961</v>
+        <v>0.1739370586024247</v>
       </c>
       <c r="W64">
-        <v>0.1106713113467373</v>
+        <v>0.1110484489089598</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8837124751574804</v>
+        <v>0.8696852930121236</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1329139166530155</v>
+        <v>0.1338002264306831</v>
       </c>
       <c r="C65">
-        <v>2363.287887411807</v>
+        <v>1985.982956099433</v>
       </c>
       <c r="D65">
-        <v>15590.06488741181</v>
+        <v>15464.43895609944</v>
       </c>
       <c r="E65">
-        <v>7690.477000000001</v>
+        <v>7942.156000000001</v>
       </c>
       <c r="F65">
-        <v>15855.777</v>
+        <v>16107.456</v>
       </c>
       <c r="G65">
         <v>2629</v>
@@ -6617,37 +6617,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M65">
-        <v>2131.507605361666</v>
+        <v>2165.341059415026</v>
       </c>
       <c r="N65">
-        <v>-277.7667890351356</v>
+        <v>-311.6002430884957</v>
       </c>
       <c r="O65">
-        <v>-55.55335780702713</v>
+        <v>-62.32004861769915</v>
       </c>
       <c r="P65">
-        <v>-222.2134312281085</v>
+        <v>-249.2801944707966</v>
       </c>
       <c r="Q65">
-        <v>1231.086568771892</v>
+        <v>1204.019805529203</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1701443076766778</v>
+        <v>0.1735983162232522</v>
       </c>
       <c r="T65">
-        <v>1.923566893529545</v>
+        <v>1.976999307238699</v>
       </c>
       <c r="U65">
         <v>0.1344309777667576</v>
       </c>
       <c r="V65">
-        <v>0.1739370586024247</v>
+        <v>0.1712192920617618</v>
       </c>
       <c r="W65">
-        <v>0.1110484489089598</v>
+        <v>0.1114138009223629</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8696852930121236</v>
+        <v>0.856096460308809</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1338002264306831</v>
+        <v>0.1346865362083506</v>
       </c>
       <c r="C66">
-        <v>1985.982956099433</v>
+        <v>1610.686447426593</v>
       </c>
       <c r="D66">
-        <v>15464.43895609944</v>
+        <v>15340.8214474266</v>
       </c>
       <c r="E66">
-        <v>7942.156000000001</v>
+        <v>8193.835000000001</v>
       </c>
       <c r="F66">
-        <v>16107.456</v>
+        <v>16359.135</v>
       </c>
       <c r="G66">
         <v>2629</v>
@@ -6699,37 +6699,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M66">
-        <v>2165.341059415026</v>
+        <v>2199.174513468386</v>
       </c>
       <c r="N66">
-        <v>-311.6002430884957</v>
+        <v>-345.4336971418554</v>
       </c>
       <c r="O66">
-        <v>-62.32004861769915</v>
+        <v>-69.08673942837109</v>
       </c>
       <c r="P66">
-        <v>-249.2801944707966</v>
+        <v>-276.3469577134844</v>
       </c>
       <c r="Q66">
-        <v>1204.019805529203</v>
+        <v>1176.953042286515</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1735983162232522</v>
+        <v>0.1772496966867737</v>
       </c>
       <c r="T66">
-        <v>1.976999307238699</v>
+        <v>2.033485001731234</v>
       </c>
       <c r="U66">
         <v>0.1344309777667576</v>
       </c>
       <c r="V66">
-        <v>0.1712192920617618</v>
+        <v>0.1685851491069655</v>
       </c>
       <c r="W66">
-        <v>0.1114138009223629</v>
+        <v>0.1117679113353536</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.856096460308809</v>
+        <v>0.8429257455348274</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1346865362083506</v>
+        <v>0.1355728459860182</v>
       </c>
       <c r="C67">
-        <v>1610.686447426593</v>
+        <v>1237.350579387174</v>
       </c>
       <c r="D67">
-        <v>15340.8214474266</v>
+        <v>15219.16457938718</v>
       </c>
       <c r="E67">
-        <v>8193.835000000001</v>
+        <v>8445.514000000001</v>
       </c>
       <c r="F67">
-        <v>16359.135</v>
+        <v>16610.814</v>
       </c>
       <c r="G67">
         <v>2629</v>
@@ -6781,37 +6781,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M67">
-        <v>2199.174513468386</v>
+        <v>2233.007967521746</v>
       </c>
       <c r="N67">
-        <v>-345.4336971418554</v>
+        <v>-379.2671511952151</v>
       </c>
       <c r="O67">
-        <v>-69.08673942837109</v>
+        <v>-75.85343023904302</v>
       </c>
       <c r="P67">
-        <v>-276.3469577134844</v>
+        <v>-303.4137209561721</v>
       </c>
       <c r="Q67">
-        <v>1176.953042286515</v>
+        <v>1149.886279043828</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1772496966867737</v>
+        <v>0.1811158642363847</v>
       </c>
       <c r="T67">
-        <v>2.033485001731234</v>
+        <v>2.093293384135094</v>
       </c>
       <c r="U67">
         <v>0.1344309777667576</v>
       </c>
       <c r="V67">
-        <v>0.1685851491069655</v>
+        <v>0.1660308286659509</v>
       </c>
       <c r="W67">
-        <v>0.1117679113353536</v>
+        <v>0.1121112911297688</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8429257455348274</v>
+        <v>0.8301541433297543</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1355728459860182</v>
+        <v>0.1364591557636858</v>
       </c>
       <c r="C68">
-        <v>1237.350579387174</v>
+        <v>865.9290737467491</v>
       </c>
       <c r="D68">
-        <v>15219.16457938718</v>
+        <v>15099.42207374675</v>
       </c>
       <c r="E68">
-        <v>8445.514000000001</v>
+        <v>8697.193000000001</v>
       </c>
       <c r="F68">
-        <v>16610.814</v>
+        <v>16862.493</v>
       </c>
       <c r="G68">
         <v>2629</v>
@@ -6863,37 +6863,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M68">
-        <v>2233.007967521746</v>
+        <v>2266.841421575106</v>
       </c>
       <c r="N68">
-        <v>-379.2671511952151</v>
+        <v>-413.1006052485752</v>
       </c>
       <c r="O68">
-        <v>-75.85343023904302</v>
+        <v>-82.62012104971505</v>
       </c>
       <c r="P68">
-        <v>-303.4137209561721</v>
+        <v>-330.4804841988602</v>
       </c>
       <c r="Q68">
-        <v>1149.886279043828</v>
+        <v>1122.81951580114</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1811158642363847</v>
+        <v>0.1852163449708206</v>
       </c>
       <c r="T68">
-        <v>2.093293384135094</v>
+        <v>2.156726516987672</v>
       </c>
       <c r="U68">
         <v>0.1344309777667576</v>
       </c>
       <c r="V68">
-        <v>0.1660308286659509</v>
+        <v>0.1635527565963098</v>
       </c>
       <c r="W68">
-        <v>0.1121112911297688</v>
+        <v>0.1124444207810671</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8301541433297543</v>
+        <v>0.8177637829815489</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1364591557636858</v>
+        <v>0.1373454655413534</v>
       </c>
       <c r="C69">
-        <v>865.9290737467491</v>
+        <v>496.3770973469109</v>
       </c>
       <c r="D69">
-        <v>15099.42207374675</v>
+        <v>14981.54909734691</v>
       </c>
       <c r="E69">
-        <v>8697.193000000001</v>
+        <v>8948.872000000001</v>
       </c>
       <c r="F69">
-        <v>16862.493</v>
+        <v>17114.172</v>
       </c>
       <c r="G69">
         <v>2629</v>
@@ -6945,37 +6945,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M69">
-        <v>2266.841421575106</v>
+        <v>2300.674875628466</v>
       </c>
       <c r="N69">
-        <v>-413.1006052485752</v>
+        <v>-446.9340593019349</v>
       </c>
       <c r="O69">
-        <v>-82.62012104971505</v>
+        <v>-89.38681186038698</v>
       </c>
       <c r="P69">
-        <v>-330.4804841988602</v>
+        <v>-357.5472474415479</v>
       </c>
       <c r="Q69">
-        <v>1122.81951580114</v>
+        <v>1095.752752558452</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1852163449708206</v>
+        <v>0.1895731057511587</v>
       </c>
       <c r="T69">
-        <v>2.156726516987672</v>
+        <v>2.224124220643537</v>
       </c>
       <c r="U69">
         <v>0.1344309777667576</v>
       </c>
       <c r="V69">
-        <v>0.1635527565963098</v>
+        <v>0.1611475689993052</v>
       </c>
       <c r="W69">
-        <v>0.1124444207810671</v>
+        <v>0.1127677525014449</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8177637829815489</v>
+        <v>0.8057378449965261</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1373454655413534</v>
+        <v>0.1586715490370706</v>
       </c>
       <c r="C70">
-        <v>496.3770973469109</v>
+        <v>-2124.381344470705</v>
       </c>
       <c r="D70">
-        <v>14981.54909734691</v>
+        <v>12612.4696555293</v>
       </c>
       <c r="E70">
-        <v>8948.872000000001</v>
+        <v>9200.551000000001</v>
       </c>
       <c r="F70">
-        <v>17114.172</v>
+        <v>17365.851</v>
       </c>
       <c r="G70">
         <v>2629</v>
@@ -7027,45 +7027,45 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M70">
-        <v>2300.674875628466</v>
+        <v>2824.225327881825</v>
       </c>
       <c r="N70">
-        <v>-446.9340593019349</v>
+        <v>-970.4845115552946</v>
       </c>
       <c r="O70">
-        <v>-89.38681186038698</v>
+        <v>-194.0969023110589</v>
       </c>
       <c r="P70">
-        <v>-357.5472474415479</v>
+        <v>-776.3876092442357</v>
       </c>
       <c r="Q70">
-        <v>1095.752752558452</v>
+        <v>676.9123907557642</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1895731057511587</v>
+        <v>0.1973779598658725</v>
       </c>
       <c r="T70">
-        <v>2.224124220643537</v>
+        <v>2.344862831557103</v>
       </c>
       <c r="U70">
-        <v>0.1344309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V70">
-        <v>0.1611475689993052</v>
+        <v>0.1312742859449419</v>
       </c>
       <c r="W70">
-        <v>0.1127677525014449</v>
+        <v>0.1412817122878988</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y70">
-        <v>0.8057378449965261</v>
+        <v>0.6563714297247096</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1586715490370706</v>
+        <v>0.1988064934103418</v>
       </c>
       <c r="C71">
-        <v>-2124.381344470705</v>
+        <v>-5268.693818991298</v>
       </c>
       <c r="D71">
-        <v>12612.4696555293</v>
+        <v>9719.836181008704</v>
       </c>
       <c r="E71">
-        <v>9200.551000000001</v>
+        <v>9452.230000000001</v>
       </c>
       <c r="F71">
-        <v>17365.851</v>
+        <v>17617.53</v>
       </c>
       <c r="G71">
         <v>2629</v>
@@ -7109,45 +7109,45 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M71">
-        <v>2824.225327881825</v>
+        <v>3816.502749735185</v>
       </c>
       <c r="N71">
-        <v>-970.4845115552946</v>
+        <v>-1962.761933408655</v>
       </c>
       <c r="O71">
-        <v>-194.0969023110589</v>
+        <v>-392.5523866817309</v>
       </c>
       <c r="P71">
-        <v>-776.3876092442357</v>
+        <v>-1570.209546726924</v>
       </c>
       <c r="Q71">
-        <v>676.9123907557642</v>
+        <v>-116.9095467269237</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1973779598658725</v>
+        <v>0.2063193405134138</v>
       </c>
       <c r="T71">
-        <v>2.344862831557103</v>
+        <v>2.483183146474761</v>
       </c>
       <c r="U71">
-        <v>0.1626309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V71">
-        <v>0.1312742859449419</v>
+        <v>0.09714342883442995</v>
       </c>
       <c r="W71">
-        <v>0.1412817122878988</v>
+        <v>0.1955867017947396</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y71">
-        <v>0.6563714297247096</v>
+        <v>0.4857171441721497</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1988064934103418</v>
+        <v>0.2005148031880094</v>
       </c>
       <c r="C72">
-        <v>-5268.693818991298</v>
+        <v>-5614.340210682067</v>
       </c>
       <c r="D72">
-        <v>9719.836181008704</v>
+        <v>9625.868789317936</v>
       </c>
       <c r="E72">
-        <v>9452.230000000001</v>
+        <v>9703.909000000001</v>
       </c>
       <c r="F72">
-        <v>17617.53</v>
+        <v>17869.209</v>
       </c>
       <c r="G72">
         <v>2629</v>
@@ -7191,37 +7191,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M72">
-        <v>3816.502749735185</v>
+        <v>3871.024217588545</v>
       </c>
       <c r="N72">
-        <v>-1962.761933408655</v>
+        <v>-2017.283401262014</v>
       </c>
       <c r="O72">
-        <v>-392.5523866817309</v>
+        <v>-403.4566802524029</v>
       </c>
       <c r="P72">
-        <v>-1570.209546726924</v>
+        <v>-1613.826721009611</v>
       </c>
       <c r="Q72">
-        <v>-116.9095467269237</v>
+        <v>-160.5267210096115</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2063193405134138</v>
+        <v>0.2118544901862902</v>
       </c>
       <c r="T72">
-        <v>2.483183146474761</v>
+        <v>2.568810151525616</v>
       </c>
       <c r="U72">
         <v>0.2166309777667576</v>
       </c>
       <c r="V72">
-        <v>0.09714342883442995</v>
+        <v>0.09577521152690276</v>
       </c>
       <c r="W72">
-        <v>0.1955867017947396</v>
+        <v>0.1958831000478666</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4857171441721497</v>
+        <v>0.4788760576345138</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2005148031880094</v>
+        <v>0.202223112965677</v>
       </c>
       <c r="C73">
-        <v>-5614.340210682059</v>
+        <v>-5958.187122561405</v>
       </c>
       <c r="D73">
-        <v>9625.868789317939</v>
+        <v>9533.700877438594</v>
       </c>
       <c r="E73">
-        <v>9703.908999999998</v>
+        <v>9955.587999999998</v>
       </c>
       <c r="F73">
-        <v>17869.209</v>
+        <v>18120.888</v>
       </c>
       <c r="G73">
         <v>2629</v>
@@ -7273,37 +7273,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M73">
-        <v>3871.024217588544</v>
+        <v>3925.545685441904</v>
       </c>
       <c r="N73">
-        <v>-2017.283401262014</v>
+        <v>-2071.804869115374</v>
       </c>
       <c r="O73">
-        <v>-403.4566802524027</v>
+        <v>-414.3609738230747</v>
       </c>
       <c r="P73">
-        <v>-1613.826721009611</v>
+        <v>-1657.443895292299</v>
       </c>
       <c r="Q73">
-        <v>-160.5267210096108</v>
+        <v>-204.1438952922988</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2118544901862901</v>
+        <v>0.2177850076929433</v>
       </c>
       <c r="T73">
-        <v>2.568810151525614</v>
+        <v>2.660553371222958</v>
       </c>
       <c r="U73">
         <v>0.2166309777667576</v>
       </c>
       <c r="V73">
-        <v>0.09577521152690277</v>
+        <v>0.0944450002556958</v>
       </c>
       <c r="W73">
-        <v>0.1958831000478666</v>
+        <v>0.1961712650161845</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.4788760576345139</v>
+        <v>0.4722250012784789</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.202223112965677</v>
+        <v>0.2039314227433446</v>
       </c>
       <c r="C74">
-        <v>-5958.187122561405</v>
+        <v>-6300.285754568715</v>
       </c>
       <c r="D74">
-        <v>9533.700877438594</v>
+        <v>9443.281245431284</v>
       </c>
       <c r="E74">
-        <v>9955.587999999998</v>
+        <v>10207.267</v>
       </c>
       <c r="F74">
-        <v>18120.888</v>
+        <v>18372.567</v>
       </c>
       <c r="G74">
         <v>2629</v>
@@ -7355,37 +7355,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M74">
-        <v>3925.545685441904</v>
+        <v>3980.067153295264</v>
       </c>
       <c r="N74">
-        <v>-2071.804869115374</v>
+        <v>-2126.326336968733</v>
       </c>
       <c r="O74">
-        <v>-414.3609738230747</v>
+        <v>-425.2652673937466</v>
       </c>
       <c r="P74">
-        <v>-1657.443895292299</v>
+        <v>-1701.061069574986</v>
       </c>
       <c r="Q74">
-        <v>-204.1438952922988</v>
+        <v>-247.7610695749863</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2177850076929433</v>
+        <v>0.224154822792682</v>
       </c>
       <c r="T74">
-        <v>2.660553371222958</v>
+        <v>2.759092384971956</v>
       </c>
       <c r="U74">
         <v>0.2166309777667576</v>
       </c>
       <c r="V74">
-        <v>0.0944450002556958</v>
+        <v>0.09315123312890544</v>
       </c>
       <c r="W74">
-        <v>0.1961712650161845</v>
+        <v>0.1964515350538636</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.4722250012784789</v>
+        <v>0.4657561656445273</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2039314227433446</v>
+        <v>0.2056397325210121</v>
       </c>
       <c r="C75">
-        <v>-6300.285754568715</v>
+        <v>-6640.685382527954</v>
       </c>
       <c r="D75">
-        <v>9443.281245431284</v>
+        <v>9354.560617472045</v>
       </c>
       <c r="E75">
-        <v>10207.267</v>
+        <v>10458.946</v>
       </c>
       <c r="F75">
-        <v>18372.567</v>
+        <v>18624.246</v>
       </c>
       <c r="G75">
         <v>2629</v>
@@ -7437,37 +7437,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M75">
-        <v>3980.067153295264</v>
+        <v>4034.588621148624</v>
       </c>
       <c r="N75">
-        <v>-2126.326336968733</v>
+        <v>-2180.847804822093</v>
       </c>
       <c r="O75">
-        <v>-425.2652673937466</v>
+        <v>-436.1695609644187</v>
       </c>
       <c r="P75">
-        <v>-1701.061069574986</v>
+        <v>-1744.678243857674</v>
       </c>
       <c r="Q75">
-        <v>-247.7610695749863</v>
+        <v>-291.3782438576745</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.224154822792682</v>
+        <v>0.2310146236693236</v>
       </c>
       <c r="T75">
-        <v>2.759092384971956</v>
+        <v>2.865211322855493</v>
       </c>
       <c r="U75">
         <v>0.2166309777667576</v>
       </c>
       <c r="V75">
-        <v>0.09315123312890544</v>
+        <v>0.09189243268121754</v>
       </c>
       <c r="W75">
-        <v>0.1964515350538636</v>
+        <v>0.1967242302256595</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.4657561656445273</v>
+        <v>0.4594621634060876</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2056397325210121</v>
+        <v>0.2073480422986797</v>
       </c>
       <c r="C76">
-        <v>-6640.685382527954</v>
+        <v>-6979.43344769272</v>
       </c>
       <c r="D76">
-        <v>9354.560617472045</v>
+        <v>9267.491552307283</v>
       </c>
       <c r="E76">
-        <v>10458.946</v>
+        <v>10710.625</v>
       </c>
       <c r="F76">
-        <v>18624.246</v>
+        <v>18875.925</v>
       </c>
       <c r="G76">
         <v>2629</v>
@@ -7519,37 +7519,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M76">
-        <v>4034.588621148624</v>
+        <v>4089.110089001984</v>
       </c>
       <c r="N76">
-        <v>-2180.847804822093</v>
+        <v>-2235.369272675453</v>
       </c>
       <c r="O76">
-        <v>-436.1695609644187</v>
+        <v>-447.0738545350907</v>
       </c>
       <c r="P76">
-        <v>-1744.678243857674</v>
+        <v>-1788.295418140363</v>
       </c>
       <c r="Q76">
-        <v>-291.3782438576745</v>
+        <v>-334.9954181403627</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2310146236693236</v>
+        <v>0.2384232086160966</v>
       </c>
       <c r="T76">
-        <v>2.865211322855493</v>
+        <v>2.979819775769713</v>
       </c>
       <c r="U76">
         <v>0.2166309777667576</v>
       </c>
       <c r="V76">
-        <v>0.09189243268121754</v>
+        <v>0.09066720024546794</v>
       </c>
       <c r="W76">
-        <v>0.1967242302256595</v>
+        <v>0.1969896535262075</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.4594621634060876</v>
+        <v>0.4533360012273397</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2073480422986797</v>
+        <v>0.2090563520763473</v>
       </c>
       <c r="C77">
-        <v>-6979.43344769272</v>
+        <v>-7316.57564133668</v>
       </c>
       <c r="D77">
-        <v>9267.491552307283</v>
+        <v>9182.028358663323</v>
       </c>
       <c r="E77">
-        <v>10710.625</v>
+        <v>10962.304</v>
       </c>
       <c r="F77">
-        <v>18875.925</v>
+        <v>19127.604</v>
       </c>
       <c r="G77">
         <v>2629</v>
@@ -7601,37 +7601,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M77">
-        <v>4089.110089001984</v>
+        <v>4143.631556855344</v>
       </c>
       <c r="N77">
-        <v>-2235.369272675453</v>
+        <v>-2289.890740528813</v>
       </c>
       <c r="O77">
-        <v>-447.0738545350907</v>
+        <v>-457.9781481057626</v>
       </c>
       <c r="P77">
-        <v>-1788.295418140363</v>
+        <v>-1831.91259242305</v>
       </c>
       <c r="Q77">
-        <v>-334.9954181403627</v>
+        <v>-378.6125924230503</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2384232086160966</v>
+        <v>0.2464491756417672</v>
       </c>
       <c r="T77">
-        <v>2.979819775769713</v>
+        <v>3.103978933093452</v>
       </c>
       <c r="U77">
         <v>0.2166309777667576</v>
       </c>
       <c r="V77">
-        <v>0.09066720024546794</v>
+        <v>0.0894742107685539</v>
       </c>
       <c r="W77">
-        <v>0.1969896535262075</v>
+        <v>0.1972480920030568</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.4533360012273397</v>
+        <v>0.4473710538427695</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2090563520763473</v>
+        <v>0.2107646618540149</v>
       </c>
       <c r="C78">
-        <v>-7316.57564133668</v>
+        <v>-7652.15598470632</v>
       </c>
       <c r="D78">
-        <v>9182.028358663323</v>
+        <v>9098.127015293683</v>
       </c>
       <c r="E78">
-        <v>10962.304</v>
+        <v>11213.983</v>
       </c>
       <c r="F78">
-        <v>19127.604</v>
+        <v>19379.283</v>
       </c>
       <c r="G78">
         <v>2629</v>
@@ -7683,37 +7683,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M78">
-        <v>4143.631556855344</v>
+        <v>4198.153024708704</v>
       </c>
       <c r="N78">
-        <v>-2289.890740528813</v>
+        <v>-2344.412208382173</v>
       </c>
       <c r="O78">
-        <v>-457.9781481057626</v>
+        <v>-468.8824416764346</v>
       </c>
       <c r="P78">
-        <v>-1831.91259242305</v>
+        <v>-1875.529766705738</v>
       </c>
       <c r="Q78">
-        <v>-378.6125924230503</v>
+        <v>-422.2297667057385</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2464491756417672</v>
+        <v>0.2551730528435832</v>
       </c>
       <c r="T78">
-        <v>3.103978933093452</v>
+        <v>3.238934538880123</v>
       </c>
       <c r="U78">
         <v>0.2166309777667576</v>
       </c>
       <c r="V78">
-        <v>0.0894742107685539</v>
+        <v>0.08831220803129994</v>
       </c>
       <c r="W78">
-        <v>0.1972480920030568</v>
+        <v>0.1974998177921958</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4473710538427695</v>
+        <v>0.4415610401564998</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2107646618540149</v>
+        <v>0.2124729716316824</v>
       </c>
       <c r="C79">
-        <v>-7652.15598470632</v>
+        <v>-7986.216904629937</v>
       </c>
       <c r="D79">
-        <v>9098.127015293683</v>
+        <v>9015.745095370066</v>
       </c>
       <c r="E79">
-        <v>11213.983</v>
+        <v>11465.662</v>
       </c>
       <c r="F79">
-        <v>19379.283</v>
+        <v>19630.962</v>
       </c>
       <c r="G79">
         <v>2629</v>
@@ -7765,37 +7765,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M79">
-        <v>4198.153024708704</v>
+        <v>4252.674492562063</v>
       </c>
       <c r="N79">
-        <v>-2344.412208382173</v>
+        <v>-2398.933676235532</v>
       </c>
       <c r="O79">
-        <v>-468.8824416764346</v>
+        <v>-479.7867352471065</v>
       </c>
       <c r="P79">
-        <v>-1875.529766705738</v>
+        <v>-1919.146940988426</v>
       </c>
       <c r="Q79">
-        <v>-422.2297667057385</v>
+        <v>-465.846940988426</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2551730528435832</v>
+        <v>0.2646900097910188</v>
       </c>
       <c r="T79">
-        <v>3.238934538880123</v>
+        <v>3.386158836101947</v>
       </c>
       <c r="U79">
         <v>0.2166309777667576</v>
       </c>
       <c r="V79">
-        <v>0.08831220803129994</v>
+        <v>0.08718000023602687</v>
       </c>
       <c r="W79">
-        <v>0.1974998177921958</v>
+        <v>0.1977450890739209</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4415610401564998</v>
+        <v>0.4359000011801344</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2124729716316824</v>
+        <v>0.21418128140935</v>
       </c>
       <c r="C80">
-        <v>-7986.216904629937</v>
+        <v>-8318.79930505574</v>
       </c>
       <c r="D80">
-        <v>9015.745095370066</v>
+        <v>8934.841694944264</v>
       </c>
       <c r="E80">
-        <v>11465.662</v>
+        <v>11717.341</v>
       </c>
       <c r="F80">
-        <v>19630.962</v>
+        <v>19882.641</v>
       </c>
       <c r="G80">
         <v>2629</v>
@@ -7847,37 +7847,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M80">
-        <v>4252.674492562063</v>
+        <v>4307.195960415424</v>
       </c>
       <c r="N80">
-        <v>-2398.933676235532</v>
+        <v>-2453.455144088893</v>
       </c>
       <c r="O80">
-        <v>-479.7867352471065</v>
+        <v>-490.6910288177785</v>
       </c>
       <c r="P80">
-        <v>-1919.146940988426</v>
+        <v>-1962.764115271114</v>
       </c>
       <c r="Q80">
-        <v>-465.846940988426</v>
+        <v>-509.4641152711142</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2646900097910188</v>
+        <v>0.2751133435905911</v>
       </c>
       <c r="T80">
-        <v>3.386158836101947</v>
+        <v>3.547404494963945</v>
       </c>
       <c r="U80">
         <v>0.2166309777667576</v>
       </c>
       <c r="V80">
-        <v>0.08718000023602687</v>
+        <v>0.08607645592924172</v>
       </c>
       <c r="W80">
-        <v>0.1977450890739209</v>
+        <v>0.1979841509561087</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4359000011801344</v>
+        <v>0.4303822796462086</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.21418128140935</v>
+        <v>0.2158895911870176</v>
       </c>
       <c r="C81">
-        <v>-8318.79930505574</v>
+        <v>-8649.94263477248</v>
       </c>
       <c r="D81">
-        <v>8934.841694944264</v>
+        <v>8855.377365227523</v>
       </c>
       <c r="E81">
-        <v>11717.341</v>
+        <v>11969.02</v>
       </c>
       <c r="F81">
-        <v>19882.641</v>
+        <v>20134.32</v>
       </c>
       <c r="G81">
         <v>2629</v>
@@ -7929,37 +7929,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M81">
-        <v>4307.195960415424</v>
+        <v>4361.717428268783</v>
       </c>
       <c r="N81">
-        <v>-2453.455144088893</v>
+        <v>-2507.976611942252</v>
       </c>
       <c r="O81">
-        <v>-490.6910288177785</v>
+        <v>-501.5953223884504</v>
       </c>
       <c r="P81">
-        <v>-1962.764115271114</v>
+        <v>-2006.381289553802</v>
       </c>
       <c r="Q81">
-        <v>-509.4641152711142</v>
+        <v>-553.0812895538018</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2751133435905911</v>
+        <v>0.2865790107701207</v>
       </c>
       <c r="T81">
-        <v>3.547404494963945</v>
+        <v>3.724774719712142</v>
       </c>
       <c r="U81">
         <v>0.2166309777667576</v>
       </c>
       <c r="V81">
-        <v>0.08607645592924172</v>
+        <v>0.0850005002301262</v>
       </c>
       <c r="W81">
-        <v>0.1979841509561087</v>
+        <v>0.1982172362912418</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4303822796462086</v>
+        <v>0.4250025011506311</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2158895911870176</v>
+        <v>0.2175979009646851</v>
       </c>
       <c r="C82">
-        <v>-8649.94263477248</v>
+        <v>-8979.684951548223</v>
       </c>
       <c r="D82">
-        <v>8855.377365227523</v>
+        <v>8777.314048451781</v>
       </c>
       <c r="E82">
-        <v>11969.02</v>
+        <v>12220.699</v>
       </c>
       <c r="F82">
-        <v>20134.32</v>
+        <v>20385.999</v>
       </c>
       <c r="G82">
         <v>2629</v>
@@ -8011,37 +8011,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M82">
-        <v>4361.717428268783</v>
+        <v>4416.238896122143</v>
       </c>
       <c r="N82">
-        <v>-2507.976611942252</v>
+        <v>-2562.498079795612</v>
       </c>
       <c r="O82">
-        <v>-501.5953223884504</v>
+        <v>-512.4996159591225</v>
       </c>
       <c r="P82">
-        <v>-2006.381289553802</v>
+        <v>-2049.99846383649</v>
       </c>
       <c r="Q82">
-        <v>-553.0812895538018</v>
+        <v>-596.69846383649</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2865790107701207</v>
+        <v>0.2992515902843376</v>
       </c>
       <c r="T82">
-        <v>3.724774719712142</v>
+        <v>3.920815494433834</v>
       </c>
       <c r="U82">
         <v>0.2166309777667576</v>
       </c>
       <c r="V82">
-        <v>0.0850005002301262</v>
+        <v>0.08395111133839624</v>
       </c>
       <c r="W82">
-        <v>0.1982172362912418</v>
+        <v>0.1984445664329149</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4250025011506311</v>
+        <v>0.4197555566919813</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2175979009646851</v>
+        <v>0.2193062107423528</v>
       </c>
       <c r="C83">
-        <v>-8979.684951548223</v>
+        <v>-9308.062982906298</v>
       </c>
       <c r="D83">
-        <v>8777.314048451781</v>
+        <v>8700.615017093705</v>
       </c>
       <c r="E83">
-        <v>12220.699</v>
+        <v>12472.378</v>
       </c>
       <c r="F83">
-        <v>20385.999</v>
+        <v>20637.678</v>
       </c>
       <c r="G83">
         <v>2629</v>
@@ -8093,37 +8093,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M83">
-        <v>4416.238896122143</v>
+        <v>4470.760363975503</v>
       </c>
       <c r="N83">
-        <v>-2562.498079795612</v>
+        <v>-2617.019547648972</v>
       </c>
       <c r="O83">
-        <v>-512.4996159591225</v>
+        <v>-523.4039095297943</v>
       </c>
       <c r="P83">
-        <v>-2049.99846383649</v>
+        <v>-2093.615638119177</v>
       </c>
       <c r="Q83">
-        <v>-596.69846383649</v>
+        <v>-640.3156381191773</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2992515902843376</v>
+        <v>0.3133322341890231</v>
       </c>
       <c r="T83">
-        <v>3.920815494433834</v>
+        <v>4.138638577457936</v>
       </c>
       <c r="U83">
         <v>0.2166309777667576</v>
       </c>
       <c r="V83">
-        <v>0.08395111133839624</v>
+        <v>0.0829273172976841</v>
       </c>
       <c r="W83">
-        <v>0.1984445664329149</v>
+        <v>0.1986663519369861</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4197555566919813</v>
+        <v>0.4146365864884205</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2193062107423528</v>
+        <v>0.2210145205200204</v>
       </c>
       <c r="C84">
-        <v>-9308.062982906298</v>
+        <v>-9635.112183742387</v>
       </c>
       <c r="D84">
-        <v>8700.615017093705</v>
+        <v>8625.244816257617</v>
       </c>
       <c r="E84">
-        <v>12472.378</v>
+        <v>12724.057</v>
       </c>
       <c r="F84">
-        <v>20637.678</v>
+        <v>20889.357</v>
       </c>
       <c r="G84">
         <v>2629</v>
@@ -8175,37 +8175,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M84">
-        <v>4470.760363975503</v>
+        <v>4525.281831828863</v>
       </c>
       <c r="N84">
-        <v>-2617.019547648972</v>
+        <v>-2671.541015502332</v>
       </c>
       <c r="O84">
-        <v>-523.4039095297943</v>
+        <v>-534.3082031004664</v>
       </c>
       <c r="P84">
-        <v>-2093.615638119177</v>
+        <v>-2137.232812401865</v>
       </c>
       <c r="Q84">
-        <v>-640.3156381191773</v>
+        <v>-683.9328124018655</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3133322341890231</v>
+        <v>0.3290694244354362</v>
       </c>
       <c r="T84">
-        <v>4.138638577457936</v>
+        <v>4.382087905543697</v>
       </c>
       <c r="U84">
         <v>0.2166309777667576</v>
       </c>
       <c r="V84">
-        <v>0.0829273172976841</v>
+        <v>0.08192819299289272</v>
       </c>
       <c r="W84">
-        <v>0.1986663519369861</v>
+        <v>0.1988827932120436</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4146365864884205</v>
+        <v>0.4096409649644636</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2210145205200204</v>
+        <v>0.2227228302976879</v>
       </c>
       <c r="C85">
-        <v>-9635.112183742387</v>
+        <v>-9960.866790972628</v>
       </c>
       <c r="D85">
-        <v>8625.244816257617</v>
+        <v>8551.169209027375</v>
       </c>
       <c r="E85">
-        <v>12724.057</v>
+        <v>12975.736</v>
       </c>
       <c r="F85">
-        <v>20889.357</v>
+        <v>21141.036</v>
       </c>
       <c r="G85">
         <v>2629</v>
@@ -8257,37 +8257,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M85">
-        <v>4525.281831828863</v>
+        <v>4579.803299682222</v>
       </c>
       <c r="N85">
-        <v>-2671.541015502332</v>
+        <v>-2726.062483355691</v>
       </c>
       <c r="O85">
-        <v>-534.3082031004664</v>
+        <v>-545.2124966711383</v>
       </c>
       <c r="P85">
-        <v>-2137.232812401865</v>
+        <v>-2180.849986684553</v>
       </c>
       <c r="Q85">
-        <v>-683.9328124018655</v>
+        <v>-727.5499866845532</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3290694244354362</v>
+        <v>0.346773763462651</v>
       </c>
       <c r="T85">
-        <v>4.382087905543697</v>
+        <v>4.655968399640179</v>
       </c>
       <c r="U85">
         <v>0.2166309777667576</v>
       </c>
       <c r="V85">
-        <v>0.08192819299289272</v>
+        <v>0.08095285736202495</v>
       </c>
       <c r="W85">
-        <v>0.1988827932120436</v>
+        <v>0.1990940811234093</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.4096409649644636</v>
+        <v>0.4047642868101248</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2227228302976879</v>
+        <v>0.2244311400753555</v>
       </c>
       <c r="C86">
-        <v>-9960.866790972621</v>
+        <v>-10285.35987538972</v>
       </c>
       <c r="D86">
-        <v>8551.169209027379</v>
+        <v>8478.35512461028</v>
       </c>
       <c r="E86">
-        <v>12975.736</v>
+        <v>13227.415</v>
       </c>
       <c r="F86">
-        <v>21141.036</v>
+        <v>21392.715</v>
       </c>
       <c r="G86">
         <v>2629</v>
@@ -8339,37 +8339,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M86">
-        <v>4579.803299682221</v>
+        <v>4634.324767535581</v>
       </c>
       <c r="N86">
-        <v>-2726.06248335569</v>
+        <v>-2780.583951209051</v>
       </c>
       <c r="O86">
-        <v>-545.2124966711381</v>
+        <v>-556.1167902418101</v>
       </c>
       <c r="P86">
-        <v>-2180.849986684552</v>
+        <v>-2224.46716096724</v>
       </c>
       <c r="Q86">
-        <v>-727.5499866845523</v>
+        <v>-771.1671609672405</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3467737634626508</v>
+        <v>0.3668386810268275</v>
       </c>
       <c r="T86">
-        <v>4.655968399640176</v>
+        <v>4.966366292949521</v>
       </c>
       <c r="U86">
         <v>0.2166309777667576</v>
       </c>
       <c r="V86">
-        <v>0.08095285736202497</v>
+        <v>0.08000047080482467</v>
       </c>
       <c r="W86">
-        <v>0.1990940811234093</v>
+        <v>0.1993003975545075</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.4047642868101249</v>
+        <v>0.4000023540241233</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2244311400753555</v>
+        <v>0.2261394498530231</v>
       </c>
       <c r="C87">
-        <v>-10285.35987538972</v>
+        <v>-10608.62339089206</v>
       </c>
       <c r="D87">
-        <v>8478.35512461028</v>
+        <v>8406.770609107938</v>
       </c>
       <c r="E87">
-        <v>13227.415</v>
+        <v>13479.094</v>
       </c>
       <c r="F87">
-        <v>21392.715</v>
+        <v>21644.394</v>
       </c>
       <c r="G87">
         <v>2629</v>
@@ -8421,37 +8421,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M87">
-        <v>4634.324767535581</v>
+        <v>4688.846235388941</v>
       </c>
       <c r="N87">
-        <v>-2780.583951209051</v>
+        <v>-2835.10541906241</v>
       </c>
       <c r="O87">
-        <v>-556.1167902418101</v>
+        <v>-567.0210838124821</v>
       </c>
       <c r="P87">
-        <v>-2224.46716096724</v>
+        <v>-2268.084335249928</v>
       </c>
       <c r="Q87">
-        <v>-771.1671609672405</v>
+        <v>-814.7843352499278</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3668386810268275</v>
+        <v>0.3897700153858867</v>
       </c>
       <c r="T87">
-        <v>4.966366292949521</v>
+        <v>5.321106742445917</v>
       </c>
       <c r="U87">
         <v>0.2166309777667576</v>
       </c>
       <c r="V87">
-        <v>0.08000047080482467</v>
+        <v>0.07907023277221042</v>
       </c>
       <c r="W87">
-        <v>0.1993003975545075</v>
+        <v>0.1995019159290685</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.4000023540241233</v>
+        <v>0.3953511638610522</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2261394498530231</v>
+        <v>0.2278477596306906</v>
       </c>
       <c r="C88">
-        <v>-10608.62339089206</v>
+        <v>-10930.6882212398</v>
       </c>
       <c r="D88">
-        <v>8406.770609107938</v>
+        <v>8336.384778760204</v>
       </c>
       <c r="E88">
-        <v>13479.094</v>
+        <v>13730.773</v>
       </c>
       <c r="F88">
-        <v>21644.394</v>
+        <v>21896.073</v>
       </c>
       <c r="G88">
         <v>2629</v>
@@ -8503,37 +8503,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M88">
-        <v>4688.846235388941</v>
+        <v>4743.367703242301</v>
       </c>
       <c r="N88">
-        <v>-2835.10541906241</v>
+        <v>-2889.62688691577</v>
       </c>
       <c r="O88">
-        <v>-567.0210838124821</v>
+        <v>-577.9253773831541</v>
       </c>
       <c r="P88">
-        <v>-2268.084335249928</v>
+        <v>-2311.701509532616</v>
       </c>
       <c r="Q88">
-        <v>-814.7843352499278</v>
+        <v>-858.401509532616</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3897700153858867</v>
+        <v>0.4162292473386472</v>
       </c>
       <c r="T88">
-        <v>5.321106742445917</v>
+        <v>5.730422645710987</v>
       </c>
       <c r="U88">
         <v>0.2166309777667576</v>
       </c>
       <c r="V88">
-        <v>0.07907023277221042</v>
+        <v>0.07816137952195513</v>
       </c>
       <c r="W88">
-        <v>0.1995019159290685</v>
+        <v>0.1996988016973178</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3953511638610522</v>
+        <v>0.3908068976097757</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2278477596306906</v>
+        <v>0.2295560694083582</v>
       </c>
       <c r="C89">
-        <v>-10930.6882212398</v>
+        <v>-11251.58422448162</v>
       </c>
       <c r="D89">
-        <v>8336.384778760204</v>
+        <v>8267.167775518385</v>
       </c>
       <c r="E89">
-        <v>13730.773</v>
+        <v>13982.452</v>
       </c>
       <c r="F89">
-        <v>21896.073</v>
+        <v>22147.752</v>
       </c>
       <c r="G89">
         <v>2629</v>
@@ -8585,37 +8585,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M89">
-        <v>4743.367703242301</v>
+        <v>4797.88917109566</v>
       </c>
       <c r="N89">
-        <v>-2889.62688691577</v>
+        <v>-2944.14835476913</v>
       </c>
       <c r="O89">
-        <v>-577.9253773831541</v>
+        <v>-588.8296709538259</v>
       </c>
       <c r="P89">
-        <v>-2311.701509532616</v>
+        <v>-2355.318683815304</v>
       </c>
       <c r="Q89">
-        <v>-858.401509532616</v>
+        <v>-902.0186838153038</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4162292473386472</v>
+        <v>0.4470983512835344</v>
       </c>
       <c r="T89">
-        <v>5.730422645710987</v>
+        <v>6.207957866186902</v>
       </c>
       <c r="U89">
         <v>0.2166309777667576</v>
       </c>
       <c r="V89">
-        <v>0.07816137952195513</v>
+        <v>0.07727318202738748</v>
       </c>
       <c r="W89">
-        <v>0.1996988016973178</v>
+        <v>0.199891212789016</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3908068976097757</v>
+        <v>0.3863659101369373</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2295560694083582</v>
+        <v>0.2312643791860258</v>
       </c>
       <c r="C90">
-        <v>-11251.58422448162</v>
+        <v>-11571.34027518654</v>
       </c>
       <c r="D90">
-        <v>8267.167775518385</v>
+        <v>8199.090724813463</v>
       </c>
       <c r="E90">
-        <v>13982.452</v>
+        <v>14234.131</v>
       </c>
       <c r="F90">
-        <v>22147.752</v>
+        <v>22399.431</v>
       </c>
       <c r="G90">
         <v>2629</v>
@@ -8667,37 +8667,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M90">
-        <v>4797.88917109566</v>
+        <v>4852.410638949021</v>
       </c>
       <c r="N90">
-        <v>-2944.14835476913</v>
+        <v>-2998.66982262249</v>
       </c>
       <c r="O90">
-        <v>-588.8296709538259</v>
+        <v>-599.733964524498</v>
       </c>
       <c r="P90">
-        <v>-2355.318683815304</v>
+        <v>-2398.935858097992</v>
       </c>
       <c r="Q90">
-        <v>-902.0186838153038</v>
+        <v>-945.635858097992</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4470983512835344</v>
+        <v>0.4835800195820376</v>
       </c>
       <c r="T90">
-        <v>6.207957866186902</v>
+        <v>6.772317672203894</v>
       </c>
       <c r="U90">
         <v>0.2166309777667576</v>
       </c>
       <c r="V90">
-        <v>0.07727318202738748</v>
+        <v>0.07640494402707974</v>
       </c>
       <c r="W90">
-        <v>0.199891212789016</v>
+        <v>0.2000793000359569</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3863659101369373</v>
+        <v>0.3820247201353987</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2312643791860258</v>
+        <v>0.2329726889636934</v>
       </c>
       <c r="C91">
-        <v>-11571.34027518654</v>
+        <v>-11889.98430460611</v>
       </c>
       <c r="D91">
-        <v>8199.090724813463</v>
+        <v>8132.125695393889</v>
       </c>
       <c r="E91">
-        <v>14234.131</v>
+        <v>14485.81</v>
       </c>
       <c r="F91">
-        <v>22399.431</v>
+        <v>22651.11</v>
       </c>
       <c r="G91">
         <v>2629</v>
@@ -8749,37 +8749,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M91">
-        <v>4852.410638949021</v>
+        <v>4906.93210680238</v>
       </c>
       <c r="N91">
-        <v>-2998.66982262249</v>
+        <v>-3053.191290475849</v>
       </c>
       <c r="O91">
-        <v>-599.733964524498</v>
+        <v>-610.6382580951698</v>
       </c>
       <c r="P91">
-        <v>-2398.935858097992</v>
+        <v>-2442.553032380679</v>
       </c>
       <c r="Q91">
-        <v>-945.635858097992</v>
+        <v>-989.2530323806793</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4835800195820376</v>
+        <v>0.5273580215402414</v>
       </c>
       <c r="T91">
-        <v>6.772317672203894</v>
+        <v>7.449549439424284</v>
       </c>
       <c r="U91">
         <v>0.2166309777667576</v>
       </c>
       <c r="V91">
-        <v>0.07640494402707974</v>
+        <v>0.07555600020455663</v>
       </c>
       <c r="W91">
-        <v>0.2000793000359569</v>
+        <v>0.2002632075662991</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3820247201353987</v>
+        <v>0.3777800010227832</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2329726889636934</v>
+        <v>0.2346809987413609</v>
       </c>
       <c r="C92">
-        <v>-11889.98430460611</v>
+        <v>-12207.54333888447</v>
       </c>
       <c r="D92">
-        <v>8132.125695393889</v>
+        <v>8066.245661115528</v>
       </c>
       <c r="E92">
-        <v>14485.81</v>
+        <v>14737.489</v>
       </c>
       <c r="F92">
-        <v>22651.11</v>
+        <v>22902.789</v>
       </c>
       <c r="G92">
         <v>2629</v>
@@ -8831,37 +8831,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M92">
-        <v>4906.93210680238</v>
+        <v>4961.45357465574</v>
       </c>
       <c r="N92">
-        <v>-3053.191290475849</v>
+        <v>-3107.712758329209</v>
       </c>
       <c r="O92">
-        <v>-610.6382580951698</v>
+        <v>-621.542551665842</v>
       </c>
       <c r="P92">
-        <v>-2442.553032380679</v>
+        <v>-2486.170206663367</v>
       </c>
       <c r="Q92">
-        <v>-989.2530323806793</v>
+        <v>-1032.870206663368</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5273580215402414</v>
+        <v>0.5808644683780461</v>
       </c>
       <c r="T92">
-        <v>7.449549439424284</v>
+        <v>8.277277154915872</v>
       </c>
       <c r="U92">
         <v>0.2166309777667576</v>
       </c>
       <c r="V92">
-        <v>0.07555600020455663</v>
+        <v>0.07472571448802304</v>
       </c>
       <c r="W92">
-        <v>0.2002632075662991</v>
+        <v>0.2004430731728976</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3777800010227832</v>
+        <v>0.3736285724401153</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2346809987413609</v>
+        <v>0.2363893085190285</v>
       </c>
       <c r="C93">
-        <v>-12207.54333888447</v>
+        <v>-12524.04353542604</v>
       </c>
       <c r="D93">
-        <v>8066.245661115528</v>
+        <v>8001.424464573961</v>
       </c>
       <c r="E93">
-        <v>14737.489</v>
+        <v>14989.168</v>
       </c>
       <c r="F93">
-        <v>22902.789</v>
+        <v>23154.468</v>
       </c>
       <c r="G93">
         <v>2629</v>
@@ -8913,37 +8913,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M93">
-        <v>4961.45357465574</v>
+        <v>5015.9750425091</v>
       </c>
       <c r="N93">
-        <v>-3107.712758329209</v>
+        <v>-3162.234226182569</v>
       </c>
       <c r="O93">
-        <v>-621.542551665842</v>
+        <v>-632.4468452365138</v>
       </c>
       <c r="P93">
-        <v>-2486.170206663367</v>
+        <v>-2529.787380946055</v>
       </c>
       <c r="Q93">
-        <v>-1032.870206663368</v>
+        <v>-1076.487380946055</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5808644683780461</v>
+        <v>0.6477475269253019</v>
       </c>
       <c r="T93">
-        <v>8.277277154915872</v>
+        <v>9.311936799280359</v>
       </c>
       <c r="U93">
         <v>0.2166309777667576</v>
       </c>
       <c r="V93">
-        <v>0.07472571448802304</v>
+        <v>0.07391347846097931</v>
       </c>
       <c r="W93">
-        <v>0.2004430731728976</v>
+        <v>0.2006190286576135</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3736285724401153</v>
+        <v>0.3695673923048967</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2363893085190285</v>
+        <v>0.2380976182966961</v>
       </c>
       <c r="C94">
-        <v>-12524.04353542604</v>
+        <v>-12839.51021752365</v>
       </c>
       <c r="D94">
-        <v>8001.424464573961</v>
+        <v>7937.636782476352</v>
       </c>
       <c r="E94">
-        <v>14989.168</v>
+        <v>15240.847</v>
       </c>
       <c r="F94">
-        <v>23154.468</v>
+        <v>23406.147</v>
       </c>
       <c r="G94">
         <v>2629</v>
@@ -8995,37 +8995,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M94">
-        <v>5015.9750425091</v>
+        <v>5070.49651036246</v>
       </c>
       <c r="N94">
-        <v>-3162.234226182569</v>
+        <v>-3216.755694035929</v>
       </c>
       <c r="O94">
-        <v>-632.4468452365138</v>
+        <v>-643.3511388071859</v>
       </c>
       <c r="P94">
-        <v>-2529.787380946055</v>
+        <v>-2573.404555228743</v>
       </c>
       <c r="Q94">
-        <v>-1076.487380946055</v>
+        <v>-1120.104555228743</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6477475269253019</v>
+        <v>0.7337400307717737</v>
       </c>
       <c r="T94">
-        <v>9.311936799280359</v>
+        <v>10.64221348489184</v>
       </c>
       <c r="U94">
         <v>0.2166309777667576</v>
       </c>
       <c r="V94">
-        <v>0.07391347846097931</v>
+        <v>0.07311870987537737</v>
       </c>
       <c r="W94">
-        <v>0.2006190286576135</v>
+        <v>0.2007912001534107</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3695673923048967</v>
+        <v>0.3655935493768869</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2380976182966961</v>
+        <v>0.2398059280743637</v>
       </c>
       <c r="C95">
-        <v>-12839.51021752365</v>
+        <v>-13153.96790734347</v>
       </c>
       <c r="D95">
-        <v>7937.636782476352</v>
+        <v>7874.858092656538</v>
       </c>
       <c r="E95">
-        <v>15240.847</v>
+        <v>15492.526</v>
       </c>
       <c r="F95">
-        <v>23406.147</v>
+        <v>23657.826</v>
       </c>
       <c r="G95">
         <v>2629</v>
@@ -9077,37 +9077,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M95">
-        <v>5070.49651036246</v>
+        <v>5125.01797821582</v>
       </c>
       <c r="N95">
-        <v>-3216.755694035929</v>
+        <v>-3271.277161889289</v>
       </c>
       <c r="O95">
-        <v>-643.3511388071859</v>
+        <v>-654.2554323778579</v>
       </c>
       <c r="P95">
-        <v>-2573.404555228743</v>
+        <v>-2617.021729511432</v>
       </c>
       <c r="Q95">
-        <v>-1120.104555228743</v>
+        <v>-1163.721729511432</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7337400307717737</v>
+        <v>0.8483967025670694</v>
       </c>
       <c r="T95">
-        <v>10.64221348489184</v>
+        <v>12.41591573237381</v>
       </c>
       <c r="U95">
         <v>0.2166309777667576</v>
       </c>
       <c r="V95">
-        <v>0.07311870987537737</v>
+        <v>0.07234085125968187</v>
       </c>
       <c r="W95">
-        <v>0.2007912001534107</v>
+        <v>0.2009597084258931</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3655935493768869</v>
+        <v>0.3617042562984094</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2398059280743637</v>
+        <v>0.2415142378520312</v>
       </c>
       <c r="C96">
-        <v>-13153.96790734347</v>
+        <v>-13467.44035735689</v>
       </c>
       <c r="D96">
-        <v>7874.858092656538</v>
+        <v>7813.064642643113</v>
       </c>
       <c r="E96">
-        <v>15492.526</v>
+        <v>15744.205</v>
       </c>
       <c r="F96">
-        <v>23657.826</v>
+        <v>23909.505</v>
       </c>
       <c r="G96">
         <v>2629</v>
@@ -9159,37 +9159,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M96">
-        <v>5125.01797821582</v>
+        <v>5179.53944606918</v>
       </c>
       <c r="N96">
-        <v>-3271.277161889289</v>
+        <v>-3325.79862974265</v>
       </c>
       <c r="O96">
-        <v>-654.2554323778579</v>
+        <v>-665.15972594853</v>
       </c>
       <c r="P96">
-        <v>-2617.021729511432</v>
+        <v>-2660.63890379412</v>
       </c>
       <c r="Q96">
-        <v>-1163.721729511432</v>
+        <v>-1207.33890379412</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8483967025670694</v>
+        <v>1.008916043080484</v>
       </c>
       <c r="T96">
-        <v>12.41591573237381</v>
+        <v>14.89909887884859</v>
       </c>
       <c r="U96">
         <v>0.2166309777667576</v>
       </c>
       <c r="V96">
-        <v>0.07234085125968187</v>
+        <v>0.07157936861484311</v>
       </c>
       <c r="W96">
-        <v>0.2009597084258931</v>
+        <v>0.2011246691557969</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3617042562984094</v>
+        <v>0.3578968430742155</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2415142378520312</v>
+        <v>0.2432225476296988</v>
       </c>
       <c r="C97">
-        <v>-13467.44035735689</v>
+        <v>-13779.95058030414</v>
       </c>
       <c r="D97">
-        <v>7813.064642643113</v>
+        <v>7752.23341969586</v>
       </c>
       <c r="E97">
-        <v>15744.205</v>
+        <v>15995.884</v>
       </c>
       <c r="F97">
-        <v>23909.505</v>
+        <v>24161.184</v>
       </c>
       <c r="G97">
         <v>2629</v>
@@ -9241,37 +9241,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M97">
-        <v>5179.53944606918</v>
+        <v>5234.06091392254</v>
       </c>
       <c r="N97">
-        <v>-3325.79862974265</v>
+        <v>-3380.320097596009</v>
       </c>
       <c r="O97">
-        <v>-665.15972594853</v>
+        <v>-676.0640195192018</v>
       </c>
       <c r="P97">
-        <v>-2660.63890379412</v>
+        <v>-2704.256078076807</v>
       </c>
       <c r="Q97">
-        <v>-1207.33890379412</v>
+        <v>-1250.956078076807</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.008916043080484</v>
+        <v>1.249695053850605</v>
       </c>
       <c r="T97">
-        <v>14.89909887884859</v>
+        <v>18.62387359856074</v>
       </c>
       <c r="U97">
         <v>0.2166309777667576</v>
       </c>
       <c r="V97">
-        <v>0.07157936861484311</v>
+        <v>0.07083375019177184</v>
       </c>
       <c r="W97">
-        <v>0.2011246691557969</v>
+        <v>0.2012861932038278</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3578968430742155</v>
+        <v>0.3541687509588591</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2432225476296988</v>
+        <v>0.2449308574073664</v>
       </c>
       <c r="C98">
-        <v>-13779.95058030414</v>
+        <v>-14091.5208777689</v>
       </c>
       <c r="D98">
-        <v>7752.233419695863</v>
+        <v>7692.342122231098</v>
       </c>
       <c r="E98">
-        <v>15995.884</v>
+        <v>16247.563</v>
       </c>
       <c r="F98">
-        <v>24161.184</v>
+        <v>24412.863</v>
       </c>
       <c r="G98">
         <v>2629</v>
@@ -9323,37 +9323,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M98">
-        <v>5234.060913922539</v>
+        <v>5288.582381775899</v>
       </c>
       <c r="N98">
-        <v>-3380.320097596008</v>
+        <v>-3434.841565449368</v>
       </c>
       <c r="O98">
-        <v>-676.0640195192017</v>
+        <v>-686.9683130898737</v>
       </c>
       <c r="P98">
-        <v>-2704.256078076806</v>
+        <v>-2747.873252359494</v>
       </c>
       <c r="Q98">
-        <v>-1250.956078076806</v>
+        <v>-1294.573252359495</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.249695053850602</v>
+        <v>1.650993405134137</v>
       </c>
       <c r="T98">
-        <v>18.62387359856069</v>
+        <v>24.83183146474759</v>
       </c>
       <c r="U98">
         <v>0.2166309777667576</v>
       </c>
       <c r="V98">
-        <v>0.07083375019177184</v>
+        <v>0.07010350534443398</v>
       </c>
       <c r="W98">
-        <v>0.2012861932038278</v>
+        <v>0.2014443868591157</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3541687509588592</v>
+        <v>0.35051752672217</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2449308574073664</v>
+        <v>0.246639167185034</v>
       </c>
       <c r="C99">
-        <v>-14091.5208777689</v>
+        <v>-14402.17286743857</v>
       </c>
       <c r="D99">
-        <v>7692.342122231098</v>
+        <v>7633.369132561429</v>
       </c>
       <c r="E99">
-        <v>16247.563</v>
+        <v>16499.242</v>
       </c>
       <c r="F99">
-        <v>24412.863</v>
+        <v>24664.542</v>
       </c>
       <c r="G99">
         <v>2629</v>
@@ -9405,37 +9405,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M99">
-        <v>5288.582381775899</v>
+        <v>5343.103849629259</v>
       </c>
       <c r="N99">
-        <v>-3434.841565449368</v>
+        <v>-3489.363033302728</v>
       </c>
       <c r="O99">
-        <v>-686.9683130898737</v>
+        <v>-697.8726066605456</v>
       </c>
       <c r="P99">
-        <v>-2747.873252359494</v>
+        <v>-2791.490426642182</v>
       </c>
       <c r="Q99">
-        <v>-1294.573252359495</v>
+        <v>-1338.190426642182</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.650993405134137</v>
+        <v>2.453590107701205</v>
       </c>
       <c r="T99">
-        <v>24.83183146474759</v>
+        <v>37.24774719712138</v>
       </c>
       <c r="U99">
         <v>0.2166309777667576</v>
       </c>
       <c r="V99">
-        <v>0.07010350534443398</v>
+        <v>0.06938816345316426</v>
       </c>
       <c r="W99">
-        <v>0.2014443868591157</v>
+        <v>0.201599352072459</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.35051752672217</v>
+        <v>0.3469408172658213</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.246639167185034</v>
+        <v>0.2483474769627016</v>
       </c>
       <c r="C100">
-        <v>-14402.17286743857</v>
+        <v>-14711.9275091201</v>
       </c>
       <c r="D100">
-        <v>7633.369132561429</v>
+        <v>7575.293490879904</v>
       </c>
       <c r="E100">
-        <v>16499.242</v>
+        <v>16750.921</v>
       </c>
       <c r="F100">
-        <v>24664.542</v>
+        <v>24916.221</v>
       </c>
       <c r="G100">
         <v>2629</v>
@@ -9487,37 +9487,37 @@
         <v>1853.740816326531</v>
       </c>
       <c r="M100">
-        <v>5343.103849629259</v>
+        <v>5397.625317482619</v>
       </c>
       <c r="N100">
-        <v>-3489.363033302728</v>
+        <v>-3543.884501156088</v>
       </c>
       <c r="O100">
-        <v>-697.8726066605456</v>
+        <v>-708.7769002312176</v>
       </c>
       <c r="P100">
-        <v>-2791.490426642182</v>
+        <v>-2835.10760092487</v>
       </c>
       <c r="Q100">
-        <v>-1338.190426642182</v>
+        <v>-1381.80760092487</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.453590107701205</v>
+        <v>4.861380215402409</v>
       </c>
       <c r="T100">
-        <v>37.24774719712138</v>
+        <v>74.49549439424277</v>
       </c>
       <c r="U100">
         <v>0.2166309777667576</v>
       </c>
       <c r="V100">
-        <v>0.06938816345316426</v>
+        <v>0.06868727291323329</v>
       </c>
       <c r="W100">
-        <v>0.201599352072459</v>
+        <v>0.2017511866754317</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3469408172658213</v>
+        <v>0.3434363645661666</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2483474769627016</v>
-      </c>
-      <c r="C101">
-        <v>-14711.9275091201</v>
-      </c>
-      <c r="D101">
-        <v>7575.293490879904</v>
-      </c>
-      <c r="E101">
-        <v>16750.921</v>
-      </c>
-      <c r="F101">
-        <v>24916.221</v>
-      </c>
-      <c r="G101">
-        <v>2629</v>
-      </c>
-      <c r="H101">
-        <v>17002.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>3307.040816326531</v>
-      </c>
-      <c r="K101">
-        <v>1453.3</v>
-      </c>
-      <c r="L101">
-        <v>1853.740816326531</v>
-      </c>
-      <c r="M101">
-        <v>5397.625317482619</v>
-      </c>
-      <c r="N101">
-        <v>-3543.884501156088</v>
-      </c>
-      <c r="O101">
-        <v>-708.7769002312176</v>
-      </c>
-      <c r="P101">
-        <v>-2835.10760092487</v>
-      </c>
-      <c r="Q101">
-        <v>-1381.80760092487</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.861380215402409</v>
-      </c>
-      <c r="T101">
-        <v>74.49549439424277</v>
-      </c>
-      <c r="U101">
-        <v>0.2166309777667576</v>
-      </c>
-      <c r="V101">
-        <v>0.06868727291323329</v>
-      </c>
-      <c r="W101">
-        <v>0.2017511866754317</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3434363645661666</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
